--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9338339606990348</v>
+        <v>0.9383617591999311</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9351876342341608</v>
+        <v>0.9178740605441984</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5701440923647152</v>
+        <v>0.406646069696403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6280436269846363</v>
+        <v>0.3174327722175003</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1087522214740644</v>
+        <v>0.0433896418601597</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8713937632298721</v>
+        <v>-6.293725879474102</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3478438882631019</v>
+        <v>-0.6116702626593182</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04041121400567417</v>
+        <v>0.04069983782270459</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08401198236798024</v>
+        <v>0.09990764559628819</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01760550965280544</v>
+        <v>0.02001601917880387</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01055402847992062</v>
+        <v>0.01837415119216067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01855234029923569</v>
+        <v>0.01661719010282851</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01385811735581234</v>
+        <v>0.03153848624671562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03083219869357141</v>
+        <v>0.03785888835658358</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002828944280945999</v>
+        <v>0.00263535721105772</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009109813237841618</v>
+        <v>0.01154335228446438</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003280107133636525</v>
+        <v>0.0004527713647735705</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002191238639665021</v>
+        <v>0.0004021083632903019</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007522808467005806</v>
+        <v>0.0006490536264515779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003386834694543516</v>
+        <v>0.001320013155246284</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00226280940204545</v>
+        <v>0.002833776000880639</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05318782079523469</v>
+        <v>0.05133573035477064</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09544534162462628</v>
+        <v>0.1074399938778125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01811106604713407</v>
+        <v>0.02127842486589575</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01480283297097221</v>
+        <v>0.02005263980852152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.027427738636289</v>
+        <v>0.02547653089515089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01840335484237457</v>
+        <v>0.03633198529183733</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03789635915277181</v>
+        <v>0.04365255084899811</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.38676328104426</v>
+        <v>60.16156846903237</v>
       </c>
       <c r="C6" t="n">
-        <v>47.49831411846501</v>
+        <v>47.10833712252131</v>
       </c>
       <c r="D6" t="n">
-        <v>34.76952837113242</v>
+        <v>38.87050439134849</v>
       </c>
       <c r="E6" t="n">
-        <v>28.57248946028653</v>
+        <v>55.43477398026939</v>
       </c>
       <c r="F6" t="n">
-        <v>329.850601288762</v>
+        <v>277.0681937888127</v>
       </c>
       <c r="G6" t="n">
-        <v>140.7320864840527</v>
+        <v>432.0495729160068</v>
       </c>
       <c r="H6" t="n">
-        <v>104.3016305006238</v>
+        <v>151.7821584446652</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02183007278695176</v>
+        <v>0.02033622228776106</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02582057899624088</v>
+        <v>0.03271812843586555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.12918637978994</v>
+        <v>0.1783231190464206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1117402986093857</v>
+        <v>0.2050516441890531</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6663045260698195</v>
+        <v>0.2874374449804682</v>
       </c>
       <c r="G7" t="n">
-        <v>1.12331041479516</v>
+        <v>4.378083546101807</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3463653785079162</v>
+        <v>0.8503250175068958</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-48.81066514275138</v>
+        <v>-37.44862887987202</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.19041841223712</v>
+        <v>-10.76987340499451</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.13478572451689</v>
+        <v>-30.20073964049666</v>
       </c>
       <c r="E8" t="n">
-        <v>-46.55524039486849</v>
+        <v>-30.912733671479</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.30881004854177</v>
+        <v>-72.07994258382223</v>
       </c>
       <c r="G8" t="n">
-        <v>-99.87577986752396</v>
+        <v>-70.19147649239204</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.64594993173993</v>
+        <v>-41.93389911217607</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-48.41621598807894</v>
+        <v>-35.87083226118226</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.60689947378101</v>
+        <v>-12.43579765117007</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.55126678606078</v>
+        <v>-31.86666388667222</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.97172145641238</v>
+        <v>-32.57865791765455</v>
       </c>
       <c r="F9" t="n">
-        <v>-81.33899674896577</v>
+        <v>-68.20068938551823</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.74588115260089</v>
+        <v>-65.67188163269975</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.43849693431662</v>
+        <v>-41.10408712248285</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9388590880175579</v>
+        <v>0.9388592283199081</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9488556317596593</v>
+        <v>0.9488556934252594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004622715888263351</v>
+        <v>0.004620976238046026</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07189847631763735</v>
+        <v>0.07189126256263167</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.856204208037366</v>
+        <v>-0.8562143141788643</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.389839803783826</v>
+        <v>-2.389844788162663</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2136346833063457</v>
+        <v>-0.2136386569659471</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03873997238346557</v>
+        <v>0.03873992244549219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07452937547969916</v>
+        <v>0.07452930670756128</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02486724380703724</v>
+        <v>0.02486726366939902</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01951828723739369</v>
+        <v>0.01951842127944229</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0256743962232336</v>
+        <v>0.02567445805382493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02031294355346859</v>
+        <v>0.02031296190742456</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03394036978071631</v>
+        <v>0.03394038901052405</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00261409380268027</v>
+        <v>0.002614087804020905</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007188684401989141</v>
+        <v>0.007188675734474938</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007595438546455499</v>
+        <v>0.0007595451821227316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005467554981618158</v>
+        <v>0.0005467597478695375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001259421939570106</v>
+        <v>0.001259428796518427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006134907191624216</v>
+        <v>0.0006134916212316444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002163665036034884</v>
+        <v>0.002163664814373031</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05112820946092548</v>
+        <v>0.05112815079797924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08478610972316834</v>
+        <v>0.08478605860915424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02755982319692109</v>
+        <v>0.02755984728046822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02338280347096592</v>
+        <v>0.02338289434329158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03548833526061917</v>
+        <v>0.03548843186896861</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02476874480393429</v>
+        <v>0.02476876301375675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04118567098608905</v>
+        <v>0.0411856909856031</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.59212257226492</v>
+        <v>48.59203404618206</v>
       </c>
       <c r="C6" t="n">
-        <v>47.29068414030635</v>
+        <v>47.29067983037687</v>
       </c>
       <c r="D6" t="n">
-        <v>51.50594079617111</v>
+        <v>51.50594868143621</v>
       </c>
       <c r="E6" t="n">
-        <v>47.36684726879541</v>
+        <v>47.36760104331478</v>
       </c>
       <c r="F6" t="n">
-        <v>512.1038912271149</v>
+        <v>512.1039749509657</v>
       </c>
       <c r="G6" t="n">
-        <v>239.2752425749979</v>
+        <v>239.2757401623423</v>
       </c>
       <c r="H6" t="n">
-        <v>157.6891214299418</v>
+        <v>157.6893297857697</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02017213925660882</v>
+        <v>0.02017209296684221</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02037538955349463</v>
+        <v>0.02037536498655463</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2991448659317729</v>
+        <v>0.2991453887560722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2788131859534221</v>
+        <v>0.2788153530547192</v>
       </c>
       <c r="F7" t="n">
-        <v>1.115485715537818</v>
+        <v>1.115491788822444</v>
       </c>
       <c r="G7" t="n">
-        <v>2.034762769277124</v>
+        <v>2.034765761167323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.62812567758504</v>
+        <v>0.6281276249589925</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-43.52154001725913</v>
+        <v>-43.52156066992131</v>
       </c>
       <c r="C8" t="n">
-        <v>-19.61148260042446</v>
+        <v>-19.61148983472682</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.09675497675975</v>
+        <v>-33.09674449039207</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.06905305426692</v>
+        <v>-35.06900641889275</v>
       </c>
       <c r="F8" t="n">
-        <v>-70.12522929690313</v>
+        <v>-70.12516396283733</v>
       </c>
       <c r="G8" t="n">
-        <v>-86.15249048102551</v>
+        <v>-86.15247136599913</v>
       </c>
       <c r="H8" t="n">
-        <v>-47.92942507110649</v>
+        <v>-47.92940612379491</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-42.53541713057804</v>
+        <v>-42.53543778324021</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.65268525428419</v>
+        <v>-20.65269248858655</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.13795763061948</v>
+        <v>-34.1379471442518</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.11025570812664</v>
+        <v>-36.11020907275248</v>
       </c>
       <c r="F9" t="n">
-        <v>-67.70069604796313</v>
+        <v>-67.70063071389734</v>
       </c>
       <c r="G9" t="n">
-        <v>-83.32774369371782</v>
+        <v>-83.32772457869144</v>
       </c>
       <c r="H9" t="n">
-        <v>-47.41079257754821</v>
+        <v>-47.41077363023663</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7164194035595318</v>
+        <v>0.4109252069551631</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4167091849296556</v>
+        <v>0.4323244136118698</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3267372707126928</v>
+        <v>-3.266818124996156</v>
       </c>
       <c r="E2" t="n">
-        <v>-22.47656505711054</v>
+        <v>-1.712897249395463</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.80666740689409</v>
+        <v>-1.319358320730304</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.73796226265359</v>
+        <v>-3.500244409617933</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.035800568146954</v>
+        <v>-1.49267808069547</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08801991176119055</v>
+        <v>0.1167226778913886</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2042649087185863</v>
+        <v>0.2050234523845794</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02745669272413179</v>
+        <v>0.04893076911857847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09005749203283635</v>
+        <v>0.03162959152156563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03280156481713575</v>
+        <v>0.0368313176303809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01896707094431381</v>
+        <v>0.02635239647228899</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07692794016636577</v>
+        <v>0.07758170083646367</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01212455384911962</v>
+        <v>0.02518602873074388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0819854409857068</v>
+        <v>0.07979061573468756</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001012395155871282</v>
+        <v>0.003255886524096401</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01383031995465377</v>
+        <v>0.001598199603390248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001225811556668363</v>
+        <v>0.001573668857232449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004955144003206233</v>
+        <v>0.0008144509295635246</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01844567265039007</v>
+        <v>0.01870314172995234</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1101115518423004</v>
+        <v>0.1587010672010238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2863309989954053</v>
+        <v>0.2824723273786081</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03181815764420187</v>
+        <v>0.05706037612999411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1176023807354841</v>
+        <v>0.0399774887078997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03501159174713944</v>
+        <v>0.03966949529843364</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02226015274701913</v>
+        <v>0.02853858667775131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1005224722852584</v>
+        <v>0.1010698902322851</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109.5226743825384</v>
+        <v>58.88611485235626</v>
       </c>
       <c r="C6" t="n">
-        <v>47.54588853902582</v>
+        <v>55.66704208994436</v>
       </c>
       <c r="D6" t="n">
-        <v>50.4634909500214</v>
+        <v>103.8481960415131</v>
       </c>
       <c r="E6" t="n">
-        <v>168.0821645698716</v>
+        <v>129.4778702528748</v>
       </c>
       <c r="F6" t="n">
-        <v>1834.026686266673</v>
+        <v>2347.573531265377</v>
       </c>
       <c r="G6" t="n">
-        <v>357.9087601210242</v>
+        <v>389.3828037372977</v>
       </c>
       <c r="H6" t="n">
-        <v>427.9249441381923</v>
+        <v>514.1392597065607</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0935613666265242</v>
+        <v>0.1943526580249718</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2323770532110981</v>
+        <v>0.2261561069307204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7974597156458355</v>
+        <v>2.564649116131429</v>
       </c>
       <c r="E7" t="n">
-        <v>14.10530148220284</v>
+        <v>1.629975829082025</v>
       </c>
       <c r="F7" t="n">
-        <v>1.08571658031579</v>
+        <v>1.393818128838308</v>
       </c>
       <c r="G7" t="n">
-        <v>1.643471077752603</v>
+        <v>2.701286877072149</v>
       </c>
       <c r="H7" t="n">
-        <v>2.992981212625782</v>
+        <v>1.451706452679934</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-31.71270374906027</v>
+        <v>-31.13319268290853</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.007281578618164</v>
+        <v>-13.17009627250696</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.37261788461191</v>
+        <v>-32.36374409662545</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.68535199247804</v>
+        <v>-36.63326518710531</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.44982590918876</v>
+        <v>-75.45214640887869</v>
       </c>
       <c r="G8" t="n">
-        <v>-90.92888385140115</v>
+        <v>-90.46895291169044</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.19277749422638</v>
+        <v>-46.5368995932859</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.92380543971539</v>
+        <v>-30.93596810557231</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.840243701705944</v>
+        <v>-13.3783368032789</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.20558000769969</v>
+        <v>-32.5719846273974</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.51831411556581</v>
+        <v>-36.84150571787725</v>
       </c>
       <c r="F9" t="n">
-        <v>-70.51019931003675</v>
+        <v>-74.96723975909069</v>
       </c>
       <c r="G9" t="n">
-        <v>-88.66908642155501</v>
+        <v>-89.90400355422889</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.77787149937976</v>
+        <v>-46.43317309457424</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9262636784662509</v>
+        <v>0.9272164543459296</v>
       </c>
       <c r="C2" t="n">
-        <v>0.930579736484216</v>
+        <v>0.9444132601205452</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7240680054686672</v>
+        <v>0.6535852862926024</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7590358078964731</v>
+        <v>0.7641929467615701</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3478270372622572</v>
+        <v>-0.3149781133768428</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.684738120495603</v>
+        <v>-1.720745585104758</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2178970117596245</v>
+        <v>0.208947374839841</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04908081572420945</v>
+        <v>0.04832502846962943</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0844063972683507</v>
+        <v>0.07148421067539686</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0124409743508812</v>
+        <v>0.01548673037864825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009532604085442091</v>
+        <v>0.008324325044225443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02131188718753587</v>
+        <v>0.02105402056711525</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01760227499765444</v>
+        <v>0.01769415654676505</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03239582560234563</v>
+        <v>0.03039474528029671</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003152613444973907</v>
+        <v>0.003111877292344605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009757484209654733</v>
+        <v>0.007813089567380332</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002105557903437512</v>
+        <v>0.0002643391316590615</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001419548330984246</v>
+        <v>0.0001389167020779213</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009144914843548782</v>
+        <v>0.0008922037127544129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004858819341454198</v>
+        <v>0.0004923985386568272</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002443830282761852</v>
+        <v>0.00211880415747886</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05614813839277226</v>
+        <v>0.05578420289243725</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09877997878950336</v>
+        <v>0.08839168268214115</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01451054066338506</v>
+        <v>0.01625850951529879</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01191447997599663</v>
+        <v>0.01178629297438008</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03024056025200059</v>
+        <v>0.02986977925520061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0220427297344367</v>
+        <v>0.02219005494938728</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03893940463468243</v>
+        <v>0.03738008704480753</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.98134143316457</v>
+        <v>45.88845376054349</v>
       </c>
       <c r="C6" t="n">
-        <v>48.24637362313415</v>
+        <v>50.12061579622965</v>
       </c>
       <c r="D6" t="n">
-        <v>25.62225290111378</v>
+        <v>31.31277067585181</v>
       </c>
       <c r="E6" t="n">
-        <v>29.0598302652293</v>
+        <v>24.09631401923784</v>
       </c>
       <c r="F6" t="n">
-        <v>365.1871411759072</v>
+        <v>361.6823645150346</v>
       </c>
       <c r="G6" t="n">
-        <v>202.1515110851036</v>
+        <v>201.3909893112998</v>
       </c>
       <c r="H6" t="n">
-        <v>119.3747417472754</v>
+        <v>119.0819180130329</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02432772587160647</v>
+        <v>0.02401337780086235</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02765631800149352</v>
+        <v>0.02214518466100269</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08292698741264047</v>
+        <v>0.1041094515043807</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07238862601422699</v>
+        <v>0.07083935766298352</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8099765104354513</v>
+        <v>0.7902359532239619</v>
       </c>
       <c r="G7" t="n">
-        <v>1.611523107005166</v>
+        <v>1.633136709016975</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4381332124567641</v>
+        <v>0.4407466723116943</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.83571154549799</v>
+        <v>-45.95276193531527</v>
       </c>
       <c r="C8" t="n">
-        <v>-23.77832406313146</v>
+        <v>-23.11172881285348</v>
       </c>
       <c r="D8" t="n">
-        <v>-46.7945594161732</v>
+        <v>-43.42966613747777</v>
       </c>
       <c r="E8" t="n">
-        <v>-49.1600097663909</v>
+        <v>-47.28981642054877</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.96570882377327</v>
+        <v>-78.26179288717289</v>
       </c>
       <c r="G8" t="n">
-        <v>-95.18408366664397</v>
+        <v>-93.01088770891809</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.11973288026847</v>
+        <v>-55.17610898371438</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.44126239082556</v>
+        <v>-45.36108820330661</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.19480512467535</v>
+        <v>-23.73645040516931</v>
       </c>
       <c r="D9" t="n">
-        <v>-47.21104047771709</v>
+        <v>-44.0543877297936</v>
       </c>
       <c r="E9" t="n">
-        <v>-49.57649082793479</v>
+        <v>-47.91453801286461</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.99589552419727</v>
+        <v>-76.80707293780888</v>
       </c>
       <c r="G9" t="n">
-        <v>-94.0541849517209</v>
+        <v>-91.31603963653347</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.91227988284516</v>
+        <v>-54.86492948757941</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5980619307460966</v>
+        <v>0.081584095289294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04439175597479084</v>
+        <v>0.7965009581940004</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.604044073955082</v>
+        <v>-2.089541075273007</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.218742863993887</v>
+        <v>-4.739642495344448</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.2575846951366</v>
+        <v>-47.7197350532606</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006438153506601374</v>
+        <v>0.1656967468262993</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.905246632143014</v>
+        <v>-8.917522803928078</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1050841470235887</v>
+        <v>0.124533456087522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2688386013995868</v>
+        <v>0.1326177249530655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03957566373214797</v>
+        <v>0.03441086586423938</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05167487666041548</v>
+        <v>0.05597767389585093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1091077837516211</v>
+        <v>0.1767961211653906</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01107178208457498</v>
+        <v>0.01031235950820824</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09755880910865582</v>
+        <v>0.08910803357904612</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01718495491528869</v>
+        <v>0.03926708396951449</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1343171558196664</v>
+        <v>0.02860315686716513</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002750142656397012</v>
+        <v>0.00235754017582663</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003074422659129208</v>
+        <v>0.003381290744316034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01238764712904452</v>
+        <v>0.03305600911280985</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001798140935914415</v>
+        <v>0.0001509915902862889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02831568954551955</v>
+        <v>0.01780267874331974</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1310913990896759</v>
+        <v>0.1981592389204059</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3664930501655747</v>
+        <v>0.1691246784687709</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05244180256624491</v>
+        <v>0.04855450726582065</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05544747658035673</v>
+        <v>0.05814886709400308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1112998074079399</v>
+        <v>0.1818131158987433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01340947775237505</v>
+        <v>0.01228786353628201</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1216971689270279</v>
+        <v>0.1113480451973376</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.1001084905144</v>
+        <v>51.91891311526455</v>
       </c>
       <c r="C6" t="n">
-        <v>80.3719594419539</v>
+        <v>34.84076199714097</v>
       </c>
       <c r="D6" t="n">
-        <v>53.27184963151466</v>
+        <v>44.98413026584216</v>
       </c>
       <c r="E6" t="n">
-        <v>114.9311690324554</v>
+        <v>137.3881143251949</v>
       </c>
       <c r="F6" t="n">
-        <v>6015.572610264428</v>
+        <v>11426.06654685645</v>
       </c>
       <c r="G6" t="n">
-        <v>59.93844655828023</v>
+        <v>72.3547320552197</v>
       </c>
       <c r="H6" t="n">
-        <v>1064.697690569858</v>
+        <v>1961.258866435853</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1326108892168731</v>
+        <v>0.303011730191872</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3807044822813293</v>
+        <v>0.08107192234881549</v>
       </c>
       <c r="D7" t="n">
-        <v>2.166276644092005</v>
+        <v>1.857025201409962</v>
       </c>
       <c r="E7" t="n">
-        <v>3.135549910119114</v>
+        <v>3.448519304248712</v>
       </c>
       <c r="F7" t="n">
-        <v>10.97189352306263</v>
+        <v>29.2781194447143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2981944238135336</v>
+        <v>0.2503966700653106</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84753831209758</v>
+        <v>5.869690712163163</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.57348892958271</v>
+        <v>-21.13631802174016</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.045308646582335</v>
+        <v>-13.32542912366165</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.37661496157397</v>
+        <v>-28.30081901136317</v>
       </c>
       <c r="E8" t="n">
-        <v>-28.70782889088116</v>
+        <v>-26.13698659220261</v>
       </c>
       <c r="F8" t="n">
-        <v>-46.69266602613643</v>
+        <v>-32.91462292440414</v>
       </c>
       <c r="G8" t="n">
-        <v>-106.1066317042646</v>
+        <v>-106.3777234101915</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.25042319317021</v>
+        <v>-38.03198318059387</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.98181519757405</v>
+        <v>-20.34741971239529</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.670030238898169</v>
+        <v>-14.15839124674943</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.00133655388981</v>
+        <v>-29.13378113445096</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.332550483197</v>
+        <v>-26.96994871529039</v>
       </c>
       <c r="F9" t="n">
-        <v>-45.23794607677243</v>
+        <v>-30.97499632525214</v>
       </c>
       <c r="G9" t="n">
-        <v>-104.41178363188</v>
+        <v>-104.1179259803453</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.93924369703524</v>
+        <v>-37.61707718574726</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8966820765628947</v>
+        <v>0.1961740124848336</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3905710149790562</v>
+        <v>0.3911116274586962</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4598623069291252</v>
+        <v>-0.7945291411889326</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.55863602111429</v>
+        <v>-0.7568584962353389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1826851544125745</v>
+        <v>0.1323612288552677</v>
       </c>
       <c r="G2" t="n">
         <v>-1.811626779927902</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3933644770027986</v>
+        <v>-0.4405612580922293</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04322049029882903</v>
+        <v>0.117943225451191</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2068656549115688</v>
+        <v>0.205493416438418</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02983824588808327</v>
+        <v>0.02928612394158384</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03131004303763074</v>
+        <v>0.02745309217140703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01798993639681126</v>
+        <v>0.01865688793925888</v>
       </c>
       <c r="G3" t="n">
         <v>0.0181070948716821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0578885775674342</v>
+        <v>0.06948997346892348</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004417381661567159</v>
+        <v>0.03436776561331256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08565933629588891</v>
+        <v>0.08558334958154246</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001113979052521978</v>
+        <v>0.001369353714344362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001507322503672445</v>
+        <v>0.001034985955521092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005545425678985619</v>
+        <v>0.0005886870093655803</v>
       </c>
       <c r="G4" t="n">
         <v>0.0005088461505788288</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01562690137202132</v>
+        <v>0.02057549800411082</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06646338587197585</v>
+        <v>0.1853854514607674</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2926761628419522</v>
+        <v>0.292546320403355</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03337632473059277</v>
+        <v>0.03700477961486005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0388242514888883</v>
+        <v>0.03217119760781516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0235487275218548</v>
+        <v>0.0242628730649439</v>
       </c>
       <c r="G5" t="n">
         <v>0.02255761845982037</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07957441181918072</v>
+        <v>0.09898804010192701</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.06844248402464</v>
+        <v>43.3725232144383</v>
       </c>
       <c r="C6" t="n">
-        <v>39.70102087116187</v>
+        <v>38.51131949420451</v>
       </c>
       <c r="D6" t="n">
-        <v>56.34111556682216</v>
+        <v>42.40825128313342</v>
       </c>
       <c r="E6" t="n">
-        <v>63.93011317276217</v>
+        <v>63.96190080560122</v>
       </c>
       <c r="F6" t="n">
-        <v>674.9493314339276</v>
+        <v>642.0251420389293</v>
       </c>
       <c r="G6" t="n">
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>160.4983372547831</v>
+        <v>155.0465228060511</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03408754419422862</v>
+        <v>0.2652052321838688</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2427902309134054</v>
+        <v>0.2425748564694709</v>
       </c>
       <c r="D7" t="n">
-        <v>0.877476954831006</v>
+        <v>1.078634579913442</v>
       </c>
       <c r="E7" t="n">
-        <v>1.537291864173716</v>
+        <v>1.055564078078933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2455826334737567</v>
+        <v>0.2607037122499756</v>
       </c>
       <c r="G7" t="n">
         <v>1.687688452567552</v>
       </c>
       <c r="H7" t="n">
-        <v>0.770819613358944</v>
+        <v>0.7650618185772071</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-32.79987328414011</v>
+        <v>-12.33572580026632</v>
       </c>
       <c r="C8" t="n">
-        <v>1.255737670319789</v>
+        <v>3.250412826065368</v>
       </c>
       <c r="D8" t="n">
-        <v>-24.79890164896445</v>
+        <v>-21.56049835080925</v>
       </c>
       <c r="E8" t="n">
-        <v>-22.98452227081552</v>
+        <v>-23.24020453141026</v>
       </c>
       <c r="F8" t="n">
-        <v>-73.96840383252336</v>
+        <v>-71.25139090583272</v>
       </c>
       <c r="G8" t="n">
-        <v>-82.58374298887142</v>
+        <v>-80.58374298887142</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.31328439249918</v>
+        <v>-34.2868582918541</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-31.22207666545036</v>
+        <v>-10.56070460424035</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4101865758557715</v>
+        <v>1.376248049117862</v>
       </c>
       <c r="D9" t="n">
-        <v>-26.46482589514001</v>
+        <v>-23.43466312775676</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.65044651699108</v>
+        <v>-25.11436930835777</v>
       </c>
       <c r="F9" t="n">
-        <v>-70.08915063421937</v>
+        <v>-66.88723105774072</v>
       </c>
       <c r="G9" t="n">
-        <v>-78.06414812917913</v>
+        <v>-75.49919877171759</v>
       </c>
       <c r="H9" t="n">
-        <v>-38.48347240280595</v>
+        <v>-33.35331980344922</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6292149430707189</v>
+        <v>0.6242182470685678</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5479386378944238</v>
+        <v>0.5469542423130003</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3033393609461879</v>
+        <v>-1.005002618088895</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.214614020358071</v>
+        <v>-2.593949844397561</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.35050610638805</v>
+        <v>-10.48234794440723</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.8273477202021</v>
+        <v>-18.82288994316132</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.919775604488211</v>
+        <v>-5.28883631011224</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1051888682658564</v>
+        <v>0.1123789958892294</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1873868548258576</v>
+        <v>0.1878857626409395</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02058620137162243</v>
+        <v>0.02392586901099193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05023202871657283</v>
+        <v>0.03976093771724729</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07847095296695611</v>
+        <v>0.08254573503953094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05061155085371816</v>
+        <v>0.05503785648071136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08207940950009726</v>
+        <v>0.08358919279644177</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01585300068346428</v>
+        <v>0.01606663557423679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06354026013654142</v>
+        <v>0.06367862300535786</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009945408820613677</v>
+        <v>0.001529959987460098</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003661102043128619</v>
+        <v>0.002117237357679036</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007022748046575409</v>
+        <v>0.007790694629006605</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003045401037222954</v>
+        <v>0.003587532069666825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01568617547149901</v>
+        <v>0.01579511377056787</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1259086997926048</v>
+        <v>0.1267542329637823</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2520719344483662</v>
+        <v>0.2523462363605962</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03153634224290077</v>
+        <v>0.03911470295758487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06050704126900124</v>
+        <v>0.04601344757436717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08380183796657092</v>
+        <v>0.08826491165240356</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05518515232581092</v>
+        <v>0.05989601046536259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1015018346742091</v>
+        <v>0.1020649236623494</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.09110737688584</v>
+        <v>80.91347697453639</v>
       </c>
       <c r="C6" t="n">
-        <v>42.75138263388546</v>
+        <v>190078782.7235824</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52995936110691</v>
+        <v>35.41622198088917</v>
       </c>
       <c r="E6" t="n">
-        <v>76.71554829690069</v>
+        <v>123222416.9116887</v>
       </c>
       <c r="F6" t="n">
-        <v>5043.711121600737</v>
+        <v>94288665.11841877</v>
       </c>
       <c r="G6" t="n">
-        <v>735.0020552005021</v>
+        <v>794.2028643661706</v>
       </c>
       <c r="H6" t="n">
-        <v>997.6335290783363</v>
+        <v>67931795.8810422</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1223326175572093</v>
+        <v>0.1244811707813954</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1800965907272519</v>
+        <v>0.1809887634098504</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7833959738025987</v>
+        <v>1.206143514835782</v>
       </c>
       <c r="E7" t="n">
-        <v>3.733893955075223</v>
+        <v>2.160334038939288</v>
       </c>
       <c r="F7" t="n">
-        <v>6.220135511098037</v>
+        <v>6.901315739124948</v>
       </c>
       <c r="G7" t="n">
-        <v>10.10067219357337</v>
+        <v>11.89975651079433</v>
       </c>
       <c r="H7" t="n">
-        <v>3.523421140305615</v>
+        <v>3.745503289647599</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-33.29956831107589</v>
+        <v>-35.17909433628138</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.53648933653781</v>
+        <v>-14.52343816803631</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.47937611415362</v>
+        <v>-36.89508217543976</v>
       </c>
       <c r="E8" t="n">
-        <v>-29.65994643327097</v>
+        <v>-34.94585903970925</v>
       </c>
       <c r="F8" t="n">
-        <v>-55.50320813502344</v>
+        <v>-56.25790304505207</v>
       </c>
       <c r="G8" t="n">
-        <v>-71.32359487862207</v>
+        <v>-71.19377986253322</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.96703053478064</v>
+        <v>-41.49919277117533</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-32.90511915640346</v>
+        <v>-34.98186975894516</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.9529703980817</v>
+        <v>-14.73167869880826</v>
       </c>
       <c r="D9" t="n">
-        <v>-37.89585717569751</v>
+        <v>-37.10332270621171</v>
       </c>
       <c r="E9" t="n">
-        <v>-30.07642749481487</v>
+        <v>-35.15409957048119</v>
       </c>
       <c r="F9" t="n">
-        <v>-54.53339483544744</v>
+        <v>-55.77299639526407</v>
       </c>
       <c r="G9" t="n">
-        <v>-70.193696163699</v>
+        <v>-70.62883050507168</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.75957753735733</v>
+        <v>-41.39546627246367</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9358523174973806</v>
+        <v>0.9358523101537487</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9354231829001819</v>
+        <v>0.9354231812847352</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3299573055021524</v>
+        <v>0.3299574420323351</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2172626324536414</v>
+        <v>0.2172626748534547</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08439981635766203</v>
+        <v>-0.1009049463140475</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.498627549600519</v>
+        <v>-0.4986279029635967</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3059113453991959</v>
+        <v>0.3031604598411049</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03967898180705334</v>
+        <v>0.03967898509581338</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08657079773389731</v>
+        <v>0.08657079735014256</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02122398565161878</v>
+        <v>0.02122398346709019</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01792055902367315</v>
+        <v>0.01792055428438077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01730089273568576</v>
+        <v>0.01871634943053579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01205316252282256</v>
+        <v>0.0120531643684481</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03245806324579182</v>
+        <v>0.03269397233273513</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002742648970210877</v>
+        <v>0.002742649284189556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009076705291070667</v>
+        <v>0.009076705441077526</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005112903610314418</v>
+        <v>0.0005112902568491755</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004611197680450597</v>
+        <v>0.0004611195976019037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007357579053387975</v>
+        <v>0.0007469564843201963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002712205137643345</v>
+        <v>0.0002712205777157248</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002299790468243529</v>
+        <v>0.002301656940292347</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05237030618786639</v>
+        <v>0.05237030918554478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09527174445275297</v>
+        <v>0.09527174524001084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02261173060673247</v>
+        <v>0.02261172830301071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02147369944944419</v>
+        <v>0.02147369548079472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0271248577017244</v>
+        <v>0.02733050464810696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0164687738998486</v>
+        <v>0.01646877584144386</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0392201853830615</v>
+        <v>0.03925445978315197</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.20199947056931</v>
+        <v>50.20200751176096</v>
       </c>
       <c r="C6" t="n">
-        <v>46.1778195629239</v>
+        <v>112878232.2950384</v>
       </c>
       <c r="D6" t="n">
-        <v>45.27169371571927</v>
+        <v>45.27168948329209</v>
       </c>
       <c r="E6" t="n">
-        <v>42.47819414532132</v>
+        <v>53412468.91123276</v>
       </c>
       <c r="F6" t="n">
-        <v>317.0574159459401</v>
+        <v>6717338.345380874</v>
       </c>
       <c r="G6" t="n">
-        <v>118.1757419165995</v>
+        <v>118.1757844835821</v>
       </c>
       <c r="H6" t="n">
-        <v>103.2271441261789</v>
+        <v>28834708.86685559</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02116415902993343</v>
+        <v>0.02266416145280808</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0257267388336949</v>
+        <v>0.0272267394233337</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2013707116020763</v>
+        <v>0.2028706705700939</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2351439941015392</v>
+        <v>0.2366439812622849</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6516699508820716</v>
+        <v>0.6645887068664769</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8995562384795817</v>
+        <v>0.9025564505869602</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3391052988214828</v>
+        <v>0.3427584516936596</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.08947943345141</v>
+        <v>-47.08947840313073</v>
       </c>
       <c r="C8" t="n">
-        <v>-22.21226403373485</v>
+        <v>-22.2122639345754</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.47143744764327</v>
+        <v>-39.47143867022385</v>
       </c>
       <c r="E8" t="n">
-        <v>-40.09111648907014</v>
+        <v>-40.09111870684347</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.57531311571162</v>
+        <v>-80.39404354140451</v>
       </c>
       <c r="G8" t="n">
-        <v>-100.7635187324511</v>
+        <v>-100.7635156671668</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.03385487534374</v>
+        <v>-55.0036431538908</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-46.49780570144275</v>
+        <v>-46.49780467112207</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.83698562605069</v>
+        <v>-22.83698552689123</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.0961590399591</v>
+        <v>-40.09616026253968</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.71583808138598</v>
+        <v>-40.71584029915931</v>
       </c>
       <c r="F9" t="n">
-        <v>-79.12059316634762</v>
+        <v>-78.93932359204051</v>
       </c>
       <c r="G9" t="n">
-        <v>-99.0686706600665</v>
+        <v>-99.06866759478223</v>
       </c>
       <c r="H9" t="n">
-        <v>-54.72267537920877</v>
+        <v>-54.69246365775584</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9383617591999311</v>
+        <v>0.9382724796865366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9178740605441984</v>
+        <v>0.9178734981976175</v>
       </c>
       <c r="D2" t="n">
-        <v>0.406646069696403</v>
+        <v>0.406635551294229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3174327722175003</v>
+        <v>0.3174039975807891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0433896418601597</v>
+        <v>-0.3918255522281504</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.293725879474102</v>
+        <v>-6.294054888251819</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6116702626593182</v>
+        <v>-0.6842824856201327</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04069983782270459</v>
+        <v>0.04071552727063856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09990764559628819</v>
+        <v>0.09990827822354524</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02001601917880387</v>
+        <v>0.02001610834363572</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01837415119216067</v>
+        <v>0.01837453948440277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01661719010282851</v>
+        <v>0.02592835593026466</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03153848624671562</v>
+        <v>0.03153906644589401</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03785888835658358</v>
+        <v>0.03941364594973015</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00263535721105772</v>
+        <v>0.002639174377257953</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01154335228446438</v>
+        <v>0.01154343122805678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004527713647735705</v>
+        <v>0.0004527793910645654</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004021083632903019</v>
+        <v>0.0004021251879119028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006490536264515779</v>
+        <v>0.0009443441277652195</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001320013155246284</v>
+        <v>0.001320072699013346</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002833776000880639</v>
+        <v>0.002883654501844961</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05133573035477064</v>
+        <v>0.05137289535599442</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1074399938778125</v>
+        <v>0.1074403612617567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02127842486589575</v>
+        <v>0.02127861346668446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02005263980852152</v>
+        <v>0.02005305931552347</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02547653089515089</v>
+        <v>0.03073018268356404</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03633198529183733</v>
+        <v>0.03633280472263799</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04365255084899811</v>
+        <v>0.04453465280102684</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.16156846903237</v>
+        <v>60.21929386495438</v>
       </c>
       <c r="C6" t="n">
-        <v>47.10833712252131</v>
+        <v>115757584.2721639</v>
       </c>
       <c r="D6" t="n">
-        <v>38.87050439134849</v>
+        <v>38.87059742930015</v>
       </c>
       <c r="E6" t="n">
-        <v>55.43477398026939</v>
+        <v>83127336.44329353</v>
       </c>
       <c r="F6" t="n">
-        <v>277.0681937888127</v>
+        <v>1062038.841341086</v>
       </c>
       <c r="G6" t="n">
-        <v>432.0495729160068</v>
+        <v>432.0692500968321</v>
       </c>
       <c r="H6" t="n">
-        <v>151.7821584446652</v>
+        <v>33324581.78598997</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02033622228776106</v>
+        <v>0.02436567815811959</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03271812843586555</v>
+        <v>0.03671835240035448</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1783231190464206</v>
+        <v>0.1823262801854765</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2050516441890531</v>
+        <v>0.2090602883573016</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2874374449804682</v>
+        <v>0.8444174131157617</v>
       </c>
       <c r="G7" t="n">
-        <v>4.378083546101807</v>
+        <v>4.38628103472971</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8503250175068958</v>
+        <v>0.9471948411577874</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-37.44862887987202</v>
+        <v>-37.43560231960805</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.76987340499451</v>
+        <v>-10.76983237185933</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.20073964049666</v>
+        <v>-30.20063327926697</v>
       </c>
       <c r="E8" t="n">
-        <v>-30.912733671479</v>
+        <v>-30.91248263064772</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.07994258382223</v>
+        <v>-67.58023899348724</v>
       </c>
       <c r="G8" t="n">
-        <v>-70.19147649239204</v>
+        <v>-70.19089009557416</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.93389911217607</v>
+        <v>-41.18161328174057</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-35.87083226118226</v>
+        <v>-35.85780570091829</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.43579765117007</v>
+        <v>-12.43575661803489</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.86666388667222</v>
+        <v>-31.86655752544253</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.57865791765455</v>
+        <v>-32.57840687682328</v>
       </c>
       <c r="F9" t="n">
-        <v>-68.20068938551823</v>
+        <v>-63.70098579518324</v>
       </c>
       <c r="G9" t="n">
-        <v>-65.67188163269975</v>
+        <v>-65.67129523588187</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.10408712248285</v>
+        <v>-40.35180129204735</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9388592283199081</v>
+        <v>0.9302684776860627</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9488556934252594</v>
+        <v>0.9340865924474501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004620976238046026</v>
+        <v>0.5704896259644087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07189126256263167</v>
+        <v>0.62202900302613</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8562143141788643</v>
+        <v>-0.1244989458922239</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.389844788162663</v>
+        <v>-0.900221815007374</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2136386569659471</v>
+        <v>0.3386921563707423</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03873992244549219</v>
+        <v>0.04223391767075546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07452930670756128</v>
+        <v>0.08518594299760834</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02486726366939902</v>
+        <v>0.01759045954721329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01951842127944229</v>
+        <v>0.0108460013425871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02567445805382493</v>
+        <v>0.01949478678703804</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02031296190742456</v>
+        <v>0.01405217588575912</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03394038901052405</v>
+        <v>0.03156721403849356</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002614087804020905</v>
+        <v>0.002981387330052771</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007188675734474938</v>
+        <v>0.009264571976054453</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007595451821227316</v>
+        <v>0.000327747046584824</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005467597478695375</v>
+        <v>0.0002226670792748391</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001259428796518427</v>
+        <v>0.0007629648518318265</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006134916212316444</v>
+        <v>0.0003439007491019886</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002163664814373031</v>
+        <v>0.00231720650548345</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05112815079797924</v>
+        <v>0.05460208173735476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08478605860915424</v>
+        <v>0.09625264659246754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02755984728046822</v>
+        <v>0.01810378542142013</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02338289434329158</v>
+        <v>0.01492203334920677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03548843186896861</v>
+        <v>0.02762181840197757</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02476876301375675</v>
+        <v>0.01854456117307683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0411856909856031</v>
+        <v>0.03834115444591726</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.59203404618206</v>
+        <v>50.2813172501141</v>
       </c>
       <c r="C6" t="n">
-        <v>47.29067983037687</v>
+        <v>113506010.5627965</v>
       </c>
       <c r="D6" t="n">
-        <v>51.50594868143621</v>
+        <v>34.66348029955759</v>
       </c>
       <c r="E6" t="n">
-        <v>47.36760104331478</v>
+        <v>19586420.60607208</v>
       </c>
       <c r="F6" t="n">
-        <v>512.1039749509657</v>
+        <v>7390733.618811353</v>
       </c>
       <c r="G6" t="n">
-        <v>239.2757401623423</v>
+        <v>143.9008769030378</v>
       </c>
       <c r="H6" t="n">
-        <v>157.6893297857697</v>
+        <v>23413898.93889239</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02017209296684221</v>
+        <v>0.02400642782521813</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02037536498655463</v>
+        <v>0.0272592226490031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2991453887560722</v>
+        <v>0.1300825351432868</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2788153530547192</v>
+        <v>0.1145471660476534</v>
       </c>
       <c r="F7" t="n">
-        <v>1.115491788822444</v>
+        <v>0.6777675183278989</v>
       </c>
       <c r="G7" t="n">
-        <v>2.034765761167323</v>
+        <v>1.142614550053167</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6281276249589925</v>
+        <v>0.3527129033410379</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-43.52156066992131</v>
+        <v>-48.33829885820569</v>
       </c>
       <c r="C8" t="n">
-        <v>-19.61148983472682</v>
+        <v>-24.0893457095322</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.09674449039207</v>
+        <v>-44.13961067926343</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.06900641889275</v>
+        <v>-46.45899692040044</v>
       </c>
       <c r="F8" t="n">
-        <v>-70.12516396283733</v>
+        <v>-82.13958312190503</v>
       </c>
       <c r="G8" t="n">
-        <v>-86.15247136599913</v>
+        <v>-99.67704700955099</v>
       </c>
       <c r="H8" t="n">
-        <v>-47.92940612379491</v>
+        <v>-57.47381371647631</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-42.53543778324021</v>
+        <v>-47.94384970353325</v>
       </c>
       <c r="C9" t="n">
-        <v>-20.65269248858655</v>
+        <v>-24.50582677107609</v>
       </c>
       <c r="D9" t="n">
-        <v>-34.1379471442518</v>
+        <v>-44.55609174080733</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.11020907275248</v>
+        <v>-46.87547798194433</v>
       </c>
       <c r="F9" t="n">
-        <v>-67.70063071389734</v>
+        <v>-81.16976982232903</v>
       </c>
       <c r="G9" t="n">
-        <v>-83.32772457869144</v>
+        <v>-98.54714829462792</v>
       </c>
       <c r="H9" t="n">
-        <v>-47.41077363023663</v>
+        <v>-57.26636071905298</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4109252069551631</v>
+        <v>0.2704896958769257</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4323244136118698</v>
+        <v>0.451459625674964</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.266818124996156</v>
+        <v>-3.147039821451279</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.712897249395463</v>
+        <v>-1.552010420787948</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.319358320730304</v>
+        <v>-1.39458925594807</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.500244409617933</v>
+        <v>-3.866687999613852</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.49267808069547</v>
+        <v>-1.539729696041543</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1167226778913886</v>
+        <v>0.1281459102939406</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2050234523845794</v>
+        <v>0.2024270917062616</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04893076911857847</v>
+        <v>0.04819937001953484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03162959152156563</v>
+        <v>0.03045993540975718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0368313176303809</v>
+        <v>0.03703434346474178</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02635239647228899</v>
+        <v>0.02748419039359162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07758170083646367</v>
+        <v>0.07895847354797127</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02518602873074388</v>
+        <v>0.03119038141837276</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07979061573468756</v>
+        <v>0.07710103252747924</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003255886524096401</v>
+        <v>0.003164487136316955</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001598199603390248</v>
+        <v>0.001503418810504897</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001573668857232449</v>
+        <v>0.001624712449519369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008144509295635246</v>
+        <v>0.0008807696214698848</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01870314172995234</v>
+        <v>0.01924413366061051</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1587010672010238</v>
+        <v>0.1766079879800819</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2824723273786081</v>
+        <v>0.2776707268105142</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05706037612999411</v>
+        <v>0.05625377441840641</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0399774887078997</v>
+        <v>0.03877394499538184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03966949529843364</v>
+        <v>0.04030772195894192</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02853858667775131</v>
+        <v>0.02967776308062797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1010698902322851</v>
+        <v>0.1032153198739924</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.88611485235626</v>
+        <v>64.05577420118438</v>
       </c>
       <c r="C6" t="n">
-        <v>55.66704208994436</v>
+        <v>99980333.89751077</v>
       </c>
       <c r="D6" t="n">
-        <v>103.8481960415131</v>
+        <v>100.7165734672028</v>
       </c>
       <c r="E6" t="n">
-        <v>129.4778702528748</v>
+        <v>136430117.0489591</v>
       </c>
       <c r="F6" t="n">
-        <v>2347.573531265377</v>
+        <v>47837810.56880286</v>
       </c>
       <c r="G6" t="n">
-        <v>389.3828037372977</v>
+        <v>413.421091038737</v>
       </c>
       <c r="H6" t="n">
-        <v>514.1392597065607</v>
+        <v>47374806.61811856</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1943526580249718</v>
+        <v>0.2411863582297832</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2261561069307204</v>
+        <v>0.2190328350667463</v>
       </c>
       <c r="D7" t="n">
-        <v>2.564649116131429</v>
+        <v>2.493654174861611</v>
       </c>
       <c r="E7" t="n">
-        <v>1.629975829082025</v>
+        <v>1.534311038807476</v>
       </c>
       <c r="F7" t="n">
-        <v>1.393818128838308</v>
+        <v>1.440028150998169</v>
       </c>
       <c r="G7" t="n">
-        <v>2.701286877072149</v>
+        <v>2.922245877238369</v>
       </c>
       <c r="H7" t="n">
-        <v>1.451706452679934</v>
+        <v>1.475076405867026</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-31.13319268290853</v>
+        <v>-29.20880967612859</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.17009627250696</v>
+        <v>-13.37583163868214</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.36374409662545</v>
+        <v>-32.53458567252513</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.63326518710531</v>
+        <v>-37.00008134393836</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.45214640887869</v>
+        <v>-75.06909319600715</v>
       </c>
       <c r="G8" t="n">
-        <v>-90.46895291169044</v>
+        <v>-89.45128801709239</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.5368995932859</v>
+        <v>-46.10661492406229</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.93596810557231</v>
+        <v>-29.01158509879237</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.3783368032789</v>
+        <v>-13.58407216945409</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.5719846273974</v>
+        <v>-32.74282620329708</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.84150571787725</v>
+        <v>-37.20832187471031</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.96723975909069</v>
+        <v>-74.58418654621914</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.90400355422889</v>
+        <v>-88.88633865963085</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.43317309457424</v>
+        <v>-46.00288842535064</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9272164543459296</v>
+        <v>0.9243348021748079</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9444132601205452</v>
+        <v>0.9305799700048665</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6535852862926024</v>
+        <v>0.7234100527885048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7641929467615701</v>
+        <v>0.7590560409062479</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3149781133768428</v>
+        <v>-0.34941601714139</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.720745585104758</v>
+        <v>-1.630877265211264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.208947374839841</v>
+        <v>0.2261812639202955</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04832502846962943</v>
+        <v>0.05018118992266771</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07148421067539686</v>
+        <v>0.08440627404736427</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01548673037864825</v>
+        <v>0.01243725468090755</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008324325044225443</v>
+        <v>0.00953221166722662</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02105402056711525</v>
+        <v>0.02161255053898004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01769415654676505</v>
+        <v>0.01733222706181758</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03039474528029671</v>
+        <v>0.03258361798649397</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003111877292344605</v>
+        <v>0.003235082995984957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007813089567380332</v>
+        <v>0.00975745130392508</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002643391316590615</v>
+        <v>0.0002110578551616267</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001389167020779213</v>
+        <v>0.0001419428688176068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008922037127544129</v>
+        <v>0.0009155695479650993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004923985386568272</v>
+        <v>0.0004761342360960286</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00211880415747886</v>
+        <v>0.002456206467991733</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05578420289243725</v>
+        <v>0.05687779000616108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08839168268214115</v>
+        <v>0.09877981222863851</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01625850951529879</v>
+        <v>0.01452783036663172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01178629297438008</v>
+        <v>0.01191397787548755</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02986977925520061</v>
+        <v>0.03025837979742305</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02219005494938728</v>
+        <v>0.02182050036309957</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03738008704480753</v>
+        <v>0.03902971510624024</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.88845376054349</v>
+        <v>49.36451901166404</v>
       </c>
       <c r="C6" t="n">
-        <v>50.12061579622965</v>
+        <v>107171588.9281006</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31277067585181</v>
+        <v>25.62042383589248</v>
       </c>
       <c r="E6" t="n">
-        <v>24.09631401923784</v>
+        <v>34676875.21719491</v>
       </c>
       <c r="F6" t="n">
-        <v>361.6823645150346</v>
+        <v>9233798.14196662</v>
       </c>
       <c r="G6" t="n">
-        <v>201.3909893112998</v>
+        <v>197.7436607383216</v>
       </c>
       <c r="H6" t="n">
-        <v>119.0819180130329</v>
+        <v>25180422.50264429</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02401337780086235</v>
+        <v>0.0259641174447471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02214518466100269</v>
+        <v>0.02865622491128762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1041094515043807</v>
+        <v>0.08412472466206172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07083935766298352</v>
+        <v>0.07338254773629797</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7902359532239619</v>
+        <v>0.8129314076519853</v>
       </c>
       <c r="G7" t="n">
-        <v>1.633136709016975</v>
+        <v>1.581192947057293</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4407466723116943</v>
+        <v>0.4343753282439455</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-45.95276193531527</v>
+        <v>-47.60330626149442</v>
       </c>
       <c r="C8" t="n">
-        <v>-23.11172881285348</v>
+        <v>-23.7783442973134</v>
       </c>
       <c r="D8" t="n">
-        <v>-43.42966613747777</v>
+        <v>-46.78026960196405</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.28981642054877</v>
+        <v>-49.16051548154439</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.26179288717289</v>
+        <v>-79.95157075450605</v>
       </c>
       <c r="G8" t="n">
-        <v>-93.01088770891809</v>
+        <v>-95.44753955350116</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.17610898371438</v>
+        <v>-57.12025765838724</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-45.36108820330661</v>
+        <v>-47.20885710682198</v>
       </c>
       <c r="C9" t="n">
-        <v>-23.73645040516931</v>
+        <v>-24.19482535885729</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.0543877297936</v>
+        <v>-47.19675066350794</v>
       </c>
       <c r="E9" t="n">
-        <v>-47.91453801286461</v>
+        <v>-49.57699654308828</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.80707293780888</v>
+        <v>-78.98175745493005</v>
       </c>
       <c r="G9" t="n">
-        <v>-91.31603963653347</v>
+        <v>-94.31764083857809</v>
       </c>
       <c r="H9" t="n">
-        <v>-54.86492948757941</v>
+        <v>-56.91280466096394</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8522492639478814</v>
+        <v>0.8524121283350803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.809611520842735</v>
+        <v>0.8098869054569401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1309503972227823</v>
+        <v>0.1333592707801856</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7006189026780063</v>
+        <v>0.6995391102805146</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2758830816062997</v>
+        <v>0.2750858264220268</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2719645224067939</v>
+        <v>-0.2904901141512752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4162247739818185</v>
+        <v>0.4132988545205786</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05063601419052546</v>
+        <v>0.05065165168574028</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1339249953933344</v>
+        <v>0.1338567879114956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02285560528750792</v>
+        <v>0.02282476881830642</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01103209755484904</v>
+        <v>0.01106726480170613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01549202128291841</v>
+        <v>0.01551161346182172</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01216321960075562</v>
+        <v>0.01216173248223943</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04101732555164848</v>
+        <v>0.04101230319355159</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006317116819687066</v>
+        <v>0.006310153515224478</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02676037924654097</v>
+        <v>0.02672167186289681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006631468245336149</v>
+        <v>0.0006613086822167781</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001763689174402639</v>
+        <v>0.0001770049799741182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004913084077118762</v>
+        <v>0.000491849313914536</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002301992054991496</v>
+        <v>0.0002335519534931832</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00577308657023549</v>
+        <v>0.005765923384619983</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07948029202064538</v>
+        <v>0.07943647471548872</v>
       </c>
       <c r="C5" t="n">
-        <v>0.163585999543179</v>
+        <v>0.1634676477560524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02575163731753022</v>
+        <v>0.0257159227370277</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01328039598205806</v>
+        <v>0.01330432185322191</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02216547783630834</v>
+        <v>0.02217767602600723</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01517231707746545</v>
+        <v>0.01528240666561335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05323935329619775</v>
+        <v>0.05323074162556855</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.62458853041023</v>
+        <v>30.66539603591791</v>
       </c>
       <c r="C6" t="n">
-        <v>45.02962239763533</v>
+        <v>84007935.22937576</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68273320433253</v>
+        <v>38.63381243525056</v>
       </c>
       <c r="E6" t="n">
-        <v>27.90260842166132</v>
+        <v>33186462.71268325</v>
       </c>
       <c r="F6" t="n">
-        <v>399.1303423871526</v>
+        <v>10916432.62119691</v>
       </c>
       <c r="G6" t="n">
-        <v>156.1911446122074</v>
+        <v>157.6343054030266</v>
       </c>
       <c r="H6" t="n">
-        <v>116.2601732588999</v>
+        <v>21351842.9161283</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04874720258941655</v>
+        <v>0.04969346896013305</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07584880921975819</v>
+        <v>0.07673909866694575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2611790836103389</v>
+        <v>0.2614551348434961</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08993778743880632</v>
+        <v>0.09126217040182752</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2175789914035084</v>
+        <v>0.2188185465931322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7635009923317753</v>
+        <v>0.7766210412256557</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2427988110989339</v>
+        <v>0.2457649101151984</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-41.58043136897528</v>
+        <v>-41.59035746461649</v>
       </c>
       <c r="C8" t="n">
-        <v>-17.72499723007848</v>
+        <v>-17.73368217531142</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.91108482496445</v>
+        <v>-39.92773900613668</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.85759580942803</v>
+        <v>-47.83599614203546</v>
       </c>
       <c r="F8" t="n">
-        <v>-87.42126206891342</v>
+        <v>-87.40805793097289</v>
       </c>
       <c r="G8" t="n">
-        <v>-104.8953516694263</v>
+        <v>-104.7073780871571</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.56512049529766</v>
+        <v>-56.533868467705</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-41.18598221430284</v>
+        <v>-41.19590830994405</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.14147829162237</v>
+        <v>-18.15016323685531</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.32756588650834</v>
+        <v>-40.34422006768057</v>
       </c>
       <c r="E9" t="n">
-        <v>-48.27407687097192</v>
+        <v>-48.25247720357935</v>
       </c>
       <c r="F9" t="n">
-        <v>-86.45144876933742</v>
+        <v>-86.43824463139688</v>
       </c>
       <c r="G9" t="n">
-        <v>-103.7654529545033</v>
+        <v>-103.577479372234</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.35766749787436</v>
+        <v>-56.32641547028169</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.081584095289294</v>
+        <v>0.5980621465028176</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7965009581940004</v>
+        <v>0.04439210722990161</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.089541075273007</v>
+        <v>-2.604377170530574</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.739642495344448</v>
+        <v>-4.269905104079136</v>
       </c>
       <c r="F2" t="n">
-        <v>-47.7197350532606</v>
+        <v>-17.27163850304695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1656967468262993</v>
+        <v>0.008026008216286629</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.917522803928078</v>
+        <v>-3.915906752617942</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.124533456087522</v>
+        <v>0.1050841019083412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1326177249530655</v>
+        <v>0.268838557964647</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03441086586423938</v>
+        <v>0.0396430315272567</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05597767389585093</v>
+        <v>0.05184663080142737</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1767961211653906</v>
+        <v>0.1091504298687464</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01031235950820824</v>
+        <v>0.01112031546668534</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08910803357904612</v>
+        <v>0.09761384458951733</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03926708396951449</v>
+        <v>0.01718494569056029</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02860315686716513</v>
+        <v>0.1343171053081416</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00235754017582663</v>
+        <v>0.002750396832839409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003381290744316034</v>
+        <v>0.003104561955747071</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03305600911280985</v>
+        <v>0.0123971818863208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001509915902862889</v>
+        <v>0.0001795267248117479</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01780267874331974</v>
+        <v>0.02832228639973681</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1981592389204059</v>
+        <v>0.1310913639053324</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1691246784687709</v>
+        <v>0.3664929812535863</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04855450726582065</v>
+        <v>0.05244422592468506</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05814886709400308</v>
+        <v>0.05571859613941355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1818131158987433</v>
+        <v>0.1113426328336132</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01228786353628201</v>
+        <v>0.01339875833097037</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1113480451973376</v>
+        <v>0.1217480930646001</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.91891311526455</v>
+        <v>64.10009746069494</v>
       </c>
       <c r="C6" t="n">
-        <v>34.84076199714097</v>
+        <v>35429930.8060507</v>
       </c>
       <c r="D6" t="n">
-        <v>44.98413026584216</v>
+        <v>53.45346290153913</v>
       </c>
       <c r="E6" t="n">
-        <v>137.3881143251949</v>
+        <v>261001023.9133789</v>
       </c>
       <c r="F6" t="n">
-        <v>11426.06654685645</v>
+        <v>88629284.35182235</v>
       </c>
       <c r="G6" t="n">
-        <v>72.3547320552197</v>
+        <v>61.36058512593247</v>
       </c>
       <c r="H6" t="n">
-        <v>1961.258866435853</v>
+        <v>64176736.33089957</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.303011730191872</v>
+        <v>0.1341108180325469</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08107192234881549</v>
+        <v>0.3822043415467287</v>
       </c>
       <c r="D7" t="n">
-        <v>1.857025201409962</v>
+        <v>2.16947685788432</v>
       </c>
       <c r="E7" t="n">
-        <v>3.448519304248712</v>
+        <v>3.169289449185528</v>
       </c>
       <c r="F7" t="n">
-        <v>29.2781194447143</v>
+        <v>10.98333915646902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2503966700653106</v>
+        <v>0.2992178662424823</v>
       </c>
       <c r="H7" t="n">
-        <v>5.869690712163163</v>
+        <v>2.856273081560105</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.13631802174016</v>
+        <v>-30.57349376070262</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.32542912366165</v>
+        <v>-6.045310902952373</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.30081901136317</v>
+        <v>-29.37606044918171</v>
       </c>
       <c r="E8" t="n">
-        <v>-26.13698659220261</v>
+        <v>-28.64929590361849</v>
       </c>
       <c r="F8" t="n">
-        <v>-32.91462292440414</v>
+        <v>-46.6834331931894</v>
       </c>
       <c r="G8" t="n">
-        <v>-106.3777234101915</v>
+        <v>-106.1274241928498</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.03198318059387</v>
+        <v>-41.2425030670824</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.34741971239529</v>
+        <v>-29.98182002869396</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.15839124674943</v>
+        <v>-6.670032495268208</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.13378113445096</v>
+        <v>-30.00078204149754</v>
       </c>
       <c r="E9" t="n">
-        <v>-26.96994871529039</v>
+        <v>-29.27401749593433</v>
       </c>
       <c r="F9" t="n">
-        <v>-30.97499632525214</v>
+        <v>-45.2287132438254</v>
       </c>
       <c r="G9" t="n">
-        <v>-104.1179259803453</v>
+        <v>-104.4325761204652</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.61707718574726</v>
+        <v>-40.93132357094743</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1961740124848336</v>
+        <v>0.374511628918107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3911116274586962</v>
+        <v>-0.05307034858632154</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7945291411889326</v>
+        <v>-3.593142729548505</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7568584962353389</v>
+        <v>-1.209195268943054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1323612288552677</v>
+        <v>-2.674096410389299</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.811626779927902</v>
+        <v>-8.995100357154721</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4405612580922293</v>
+        <v>-2.691682247617299</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.117943225451191</v>
+        <v>0.1236036012589695</v>
       </c>
       <c r="C3" t="n">
-        <v>0.205493416438418</v>
+        <v>0.2751620537663014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02928612394158384</v>
+        <v>0.05196273027124796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02745309217140703</v>
+        <v>0.03058171803047694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01865688793925888</v>
+        <v>0.0435732650577683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0181070948716821</v>
+        <v>0.0366265246201526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06948997346892348</v>
+        <v>0.09358498216748611</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03436776561331256</v>
+        <v>0.02674289966370312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08558334958154246</v>
+        <v>0.1480161078388868</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001369353714344362</v>
+        <v>0.003504895469712999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001034985955521092</v>
+        <v>0.001301462445589045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005886870093655803</v>
+        <v>0.002492849311783336</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0005088461505788288</v>
+        <v>0.001808905925102077</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02057549800411082</v>
+        <v>0.03064452010912956</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1853854514607674</v>
+        <v>0.1635325645359453</v>
       </c>
       <c r="C5" t="n">
-        <v>0.292546320403355</v>
+        <v>0.3847286158305447</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03700477961486005</v>
+        <v>0.05920215764406733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03217119760781516</v>
+        <v>0.03607578752555577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0242628730649439</v>
+        <v>0.04992844191223412</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02255761845982037</v>
+        <v>0.0425312346999482</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09898804010192701</v>
+        <v>0.1226664670247159</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.3725232144383</v>
+        <v>61.25783840216857</v>
       </c>
       <c r="C6" t="n">
-        <v>38.51131949420451</v>
+        <v>55407472.24138872</v>
       </c>
       <c r="D6" t="n">
-        <v>42.40825128313342</v>
+        <v>101.8921315208958</v>
       </c>
       <c r="E6" t="n">
-        <v>63.96190080560122</v>
+        <v>144663186.3034872</v>
       </c>
       <c r="F6" t="n">
-        <v>642.0251420389293</v>
+        <v>53590819.8353707</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>661.1111365929138</v>
       </c>
       <c r="H6" t="n">
-        <v>155.0465228060511</v>
+        <v>42277050.44022552</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2652052321838688</v>
+        <v>0.2068665410891601</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2425748564694709</v>
+        <v>0.8400647601262345</v>
       </c>
       <c r="D7" t="n">
-        <v>1.078634579913442</v>
+        <v>2.761792491386702</v>
       </c>
       <c r="E7" t="n">
-        <v>1.055564078078933</v>
+        <v>1.328339208789657</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2607037122499756</v>
+        <v>2.208947835270077</v>
       </c>
       <c r="G7" t="n">
-        <v>1.687688452567552</v>
+        <v>6.000592682587977</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7650618185772071</v>
+        <v>2.224433919874968</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-12.33572580026632</v>
+        <v>-30.59337646605692</v>
       </c>
       <c r="C8" t="n">
-        <v>3.250412826065368</v>
+        <v>-9.462605046346455</v>
       </c>
       <c r="D8" t="n">
-        <v>-21.56049835080925</v>
+        <v>-31.92156749279219</v>
       </c>
       <c r="E8" t="n">
-        <v>-23.24020453141026</v>
+        <v>-37.86560013196291</v>
       </c>
       <c r="F8" t="n">
-        <v>-71.25139090583272</v>
+        <v>-69.93194704958697</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.58374298887142</v>
+        <v>-80.09543001054639</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.2868582918541</v>
+        <v>-43.3117543662153</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-10.56070460424035</v>
+        <v>-30.3961518887207</v>
       </c>
       <c r="C9" t="n">
-        <v>1.376248049117862</v>
+        <v>-9.670845577118401</v>
       </c>
       <c r="D9" t="n">
-        <v>-23.43466312775676</v>
+        <v>-32.12980802356413</v>
       </c>
       <c r="E9" t="n">
-        <v>-25.11436930835777</v>
+        <v>-38.07384066273485</v>
       </c>
       <c r="F9" t="n">
-        <v>-66.88723105774072</v>
+        <v>-69.44704039979896</v>
       </c>
       <c r="G9" t="n">
-        <v>-75.49919877171759</v>
+        <v>-79.53048065308485</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.35331980344922</v>
+        <v>-43.20802786750365</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6242182470685678</v>
+        <v>-0.7219507968120125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5469542423130003</v>
+        <v>-0.6655058291566938</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.005002618088895</v>
+        <v>-0.07982323803594005</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.593949844397561</v>
+        <v>-3.1193869980427</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.48234794440723</v>
+        <v>-7.752022263113181</v>
       </c>
       <c r="G2" t="n">
-        <v>-18.82288994316132</v>
+        <v>-61.83446555728851</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.28883631011224</v>
+        <v>-12.36219244707484</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1123789958892294</v>
+        <v>0.1813296168634512</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1878857626409395</v>
+        <v>0.3232198609904123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02392586901099193</v>
+        <v>0.02705970065515089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03976093771724729</v>
+        <v>0.04271180619760223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08254573503953094</v>
+        <v>0.07065375491273128</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05503785648071136</v>
+        <v>0.1035519216371019</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08358919279644177</v>
+        <v>0.1247544435427416</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01606663557423679</v>
+        <v>0.07362240373122481</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06367862300535786</v>
+        <v>0.2340980285300898</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001529959987460098</v>
+        <v>0.000823982139883341</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002117237357679036</v>
+        <v>0.002426779218398287</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007790694629006605</v>
+        <v>0.005938187622915284</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003587532069666825</v>
+        <v>0.01137173544894324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01579511377056787</v>
+        <v>0.05471351944857578</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1267542329637823</v>
+        <v>0.2713344868077495</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2523462363605962</v>
+        <v>0.4838367788108814</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03911470295758487</v>
+        <v>0.02870508909380601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04601344757436717</v>
+        <v>0.04926235092236552</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08826491165240356</v>
+        <v>0.07705963679459749</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05989601046536259</v>
+        <v>0.1066383394888688</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020649236623494</v>
+        <v>0.1694727803197115</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.91347697453639</v>
+        <v>59.3941069464933</v>
       </c>
       <c r="C6" t="n">
-        <v>190078782.7235824</v>
+        <v>73.46858511734891</v>
       </c>
       <c r="D6" t="n">
-        <v>35.41622198088917</v>
+        <v>58.2547337648142</v>
       </c>
       <c r="E6" t="n">
-        <v>123222416.9116887</v>
+        <v>116.8945010000821</v>
       </c>
       <c r="F6" t="n">
-        <v>94288665.11841877</v>
+        <v>5093.672569921243</v>
       </c>
       <c r="G6" t="n">
-        <v>794.2028643661706</v>
+        <v>1479.906152564523</v>
       </c>
       <c r="H6" t="n">
-        <v>67931795.8810422</v>
+        <v>1146.931774885751</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1244811707813954</v>
+        <v>1.137241843310922</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1809887634098504</v>
+        <v>1.328040737436142</v>
       </c>
       <c r="D7" t="n">
-        <v>1.206143514835782</v>
+        <v>0.6500475178174008</v>
       </c>
       <c r="E7" t="n">
-        <v>2.160334038939288</v>
+        <v>2.476029689731378</v>
       </c>
       <c r="F7" t="n">
-        <v>6.901315739124948</v>
+        <v>5.260526820539991</v>
       </c>
       <c r="G7" t="n">
-        <v>11.89975651079433</v>
+        <v>37.71759976400163</v>
       </c>
       <c r="H7" t="n">
-        <v>3.745503289647599</v>
+        <v>8.094914395472911</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-35.17909433628138</v>
+        <v>-21.47925310940555</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.52343816803631</v>
+        <v>-6.712091956041363</v>
       </c>
       <c r="D8" t="n">
-        <v>-36.89508217543976</v>
+        <v>-40.60817021913138</v>
       </c>
       <c r="E8" t="n">
-        <v>-34.94585903970925</v>
+        <v>-34.12714195185485</v>
       </c>
       <c r="F8" t="n">
-        <v>-56.25790304505207</v>
+        <v>-59.51621567381983</v>
       </c>
       <c r="G8" t="n">
-        <v>-71.19377986253322</v>
+        <v>-56.19611653485673</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.49919277117533</v>
+        <v>-36.43983157418495</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-34.98186975894516</v>
+        <v>-21.28202853206933</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.73167869880826</v>
+        <v>-6.920332486813308</v>
       </c>
       <c r="D9" t="n">
-        <v>-37.10332270621171</v>
+        <v>-40.81641074990333</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.15409957048119</v>
+        <v>-34.3353824826268</v>
       </c>
       <c r="F9" t="n">
-        <v>-55.77299639526407</v>
+        <v>-59.03130902403183</v>
       </c>
       <c r="G9" t="n">
-        <v>-70.62883050507168</v>
+        <v>-55.6311671773952</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.39546627246367</v>
+        <v>-36.33610507547329</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9358523101537487</v>
+        <v>-0.7402680851083621</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9354231812847352</v>
+        <v>-0.6655058291566938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3299574420323351</v>
+        <v>-0.5865605900288331</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2172626748534547</v>
+        <v>-5.56491591993468</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1009049463140475</v>
+        <v>-7.506525587155577</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4986279029635967</v>
+        <v>-32.74745253799041</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3031604598411049</v>
+        <v>-7.968538091562427</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03967898509581338</v>
+        <v>0.1830487782189051</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08657079735014256</v>
+        <v>0.3232198609904123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02122398346709019</v>
+        <v>0.02807320078339531</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01792055428438077</v>
+        <v>0.05725694078851579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01871634943053579</v>
+        <v>0.07136614458707505</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0120531643684481</v>
+        <v>0.07698447843550096</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03269397233273513</v>
+        <v>0.1233249006339674</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002742649284189556</v>
+        <v>0.07440556361983008</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009076705441077526</v>
+        <v>0.2340980285300898</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0005112902568491755</v>
+        <v>0.00121065887821079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004611195976019037</v>
+        <v>0.00386746900269369</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007469564843201963</v>
+        <v>0.005771619796781838</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002712205777157248</v>
+        <v>0.006107589185872846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002301656940292347</v>
+        <v>0.05424348816891317</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05237030918554478</v>
+        <v>0.2727738323590261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09527174524001084</v>
+        <v>0.4838367788108814</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02261172830301071</v>
+        <v>0.03479452368133224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02147369548079472</v>
+        <v>0.06218897814479419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02733050464810696</v>
+        <v>0.07597117740815815</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01646877584144386</v>
+        <v>0.07815106644104639</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03925445978315197</v>
+        <v>0.1679527261408731</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.20200751176096</v>
+        <v>61.68877725682576</v>
       </c>
       <c r="C6" t="n">
-        <v>112878232.2950384</v>
+        <v>73.46858511734891</v>
       </c>
       <c r="D6" t="n">
-        <v>45.27168948329209</v>
+        <v>79.16202456032879</v>
       </c>
       <c r="E6" t="n">
-        <v>53412468.91123276</v>
+        <v>161.8130118844954</v>
       </c>
       <c r="F6" t="n">
-        <v>6717338.345380874</v>
+        <v>4919.362998106447</v>
       </c>
       <c r="G6" t="n">
-        <v>118.1757844835821</v>
+        <v>1107.456990311949</v>
       </c>
       <c r="H6" t="n">
-        <v>28834708.86685559</v>
+        <v>1067.158731206232</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02266416145280808</v>
+        <v>1.149328640132779</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0272267394233337</v>
+        <v>1.328040737436142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2028706705700939</v>
+        <v>0.9546312764467951</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2366439812622849</v>
+        <v>3.945364008564579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6645887068664769</v>
+        <v>5.112995620008842</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9025564505869602</v>
+        <v>20.25802214765448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3427584516936596</v>
+        <v>5.458063738373936</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.08947840313073</v>
+        <v>-21.38402104092284</v>
       </c>
       <c r="C8" t="n">
-        <v>-22.2122639345754</v>
+        <v>-6.712091956041363</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.47143867022385</v>
+        <v>-38.29954324076696</v>
       </c>
       <c r="E8" t="n">
-        <v>-40.09111870684347</v>
+        <v>-31.33092994219946</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.39404354140451</v>
+        <v>-59.85763012616166</v>
       </c>
       <c r="G8" t="n">
-        <v>-100.7635156671668</v>
+        <v>-64.27690097935685</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.0036431538908</v>
+        <v>-36.97685288090819</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-46.49780467112207</v>
+        <v>-21.18679646358662</v>
       </c>
       <c r="C9" t="n">
-        <v>-22.83698552689123</v>
+        <v>-6.920332486813308</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.09616026253968</v>
+        <v>-38.5077837715389</v>
       </c>
       <c r="E9" t="n">
-        <v>-40.71584029915931</v>
+        <v>-31.53917047297141</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.93932359204051</v>
+        <v>-59.37272347637366</v>
       </c>
       <c r="G9" t="n">
-        <v>-99.06866759478223</v>
+        <v>-63.71195162189532</v>
       </c>
       <c r="H9" t="n">
-        <v>-54.69246365775584</v>
+        <v>-36.87312638219654</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9382724796865366</v>
+        <v>-0.5070546556655879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9178734981976175</v>
+        <v>-0.1284382375728996</v>
       </c>
       <c r="D2" t="n">
-        <v>0.406635551294229</v>
+        <v>-0.3057099625406368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3174039975807891</v>
+        <v>-1.214831213757406</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3918255522281504</v>
+        <v>-1.490934465860295</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.294054888251819</v>
+        <v>-2.838851442279048</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6842824856201327</v>
+        <v>-1.080969996279312</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04071552727063856</v>
+        <v>0.2354766336770275</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09990827822354524</v>
+        <v>0.2798916546039374</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02001610834363572</v>
+        <v>0.02644763407746487</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01837453948440277</v>
+        <v>0.02875720703968259</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02592835593026466</v>
+        <v>0.03033532668080355</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03153906644589401</v>
+        <v>0.02431460367533984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03941364594973015</v>
+        <v>0.104203843292376</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002639174377257953</v>
+        <v>0.06443446962006706</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01154343122805678</v>
+        <v>0.1586095720046452</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004527793910645654</v>
+        <v>0.0009963498201410461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004021251879119028</v>
+        <v>0.001304783057372414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009443441277652195</v>
+        <v>0.001690082105595921</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001320072699013346</v>
+        <v>0.0006947525158718857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002883654501844961</v>
+        <v>0.03795500152061559</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05137289535599442</v>
+        <v>0.2538394563894019</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1074403612617567</v>
+        <v>0.3982581725522342</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02127861346668446</v>
+        <v>0.03156500942722885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02005305931552347</v>
+        <v>0.03612178092747386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03073018268356404</v>
+        <v>0.04111060818810543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03633280472263799</v>
+        <v>0.02635815843096565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04453465280102684</v>
+        <v>0.131208864319235</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60.21929386495438</v>
+        <v>286.4326612967199</v>
       </c>
       <c r="C6" t="n">
-        <v>115757584.2721639</v>
+        <v>61.58766666426906</v>
       </c>
       <c r="D6" t="n">
-        <v>38.87059742930015</v>
+        <v>72.28030788740932</v>
       </c>
       <c r="E6" t="n">
-        <v>83127336.44329353</v>
+        <v>90.19888600314097</v>
       </c>
       <c r="F6" t="n">
-        <v>1062038.841341086</v>
+        <v>994.4852283828437</v>
       </c>
       <c r="G6" t="n">
-        <v>432.0692500968321</v>
+        <v>374.9261498172942</v>
       </c>
       <c r="H6" t="n">
-        <v>33324581.78598997</v>
+        <v>313.3184833419462</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02436567815811959</v>
+        <v>0.9964410508674468</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03671835240035448</v>
+        <v>0.9011163433502432</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1823262801854765</v>
+        <v>0.7868208672725796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2090602883573016</v>
+        <v>1.332725424534765</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8444174131157617</v>
+        <v>1.498926794464012</v>
       </c>
       <c r="G7" t="n">
-        <v>4.38628103472971</v>
+        <v>2.30628351888965</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9471948411577874</v>
+        <v>1.303718999896449</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-37.43560231960805</v>
+        <v>-20.67895891863864</v>
       </c>
       <c r="C8" t="n">
-        <v>-10.76983237185933</v>
+        <v>-7.047857710902463</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.20063327926697</v>
+        <v>-37.46847282202125</v>
       </c>
       <c r="E8" t="n">
-        <v>-30.91248263064772</v>
+        <v>-35.85031094952906</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.58023899348724</v>
+        <v>-72.59573801641314</v>
       </c>
       <c r="G8" t="n">
-        <v>-70.19089009557416</v>
+        <v>-90.53541328511875</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.18161328174057</v>
+        <v>-44.02945861710388</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-35.85780570091829</v>
+        <v>-20.2845097639662</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.43575661803489</v>
+        <v>-7.464338772446353</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.86655752544253</v>
+        <v>-37.88495388356514</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.57840687682328</v>
+        <v>-36.26679201107295</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.70098579518324</v>
+        <v>-71.62592471683713</v>
       </c>
       <c r="G9" t="n">
-        <v>-65.67129523588187</v>
+        <v>-89.40551457019568</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.35180129204735</v>
+        <v>-43.82200561968057</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9302684776860627</v>
+        <v>-0.7402680851083621</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9340865924474501</v>
+        <v>-0.6655058291566938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5704896259644087</v>
+        <v>-1.956220041564231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.62202900302613</v>
+        <v>-1.992195356569522</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1244989458922239</v>
+        <v>-9.380905213985098</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.900221815007374</v>
+        <v>-32.74745253799041</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3386921563707423</v>
+        <v>-7.913757844062386</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04223391767075546</v>
+        <v>0.1830487782189051</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08518594299760834</v>
+        <v>0.3232198609904123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01759045954721329</v>
+        <v>0.04155605587102768</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0108460013425871</v>
+        <v>0.03484424656649474</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01949478678703804</v>
+        <v>0.07466553900356016</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01405217588575912</v>
+        <v>0.07698447843550096</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03156721403849356</v>
+        <v>0.1223864931809835</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002981387330052771</v>
+        <v>0.07440556361983008</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009264571976054453</v>
+        <v>0.2340980285300898</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000327747046584824</v>
+        <v>0.002255806719111411</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002226670792748391</v>
+        <v>0.001762737395675855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007629648518318265</v>
+        <v>0.007043373634474252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003439007491019886</v>
+        <v>0.006107589185872846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00231720650548345</v>
+        <v>0.05427884984750903</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05460208173735476</v>
+        <v>0.2727738323590261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09625264659246754</v>
+        <v>0.4838367788108814</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01810378542142013</v>
+        <v>0.04749533365617523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01492203334920677</v>
+        <v>0.04198496630552245</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02762181840197757</v>
+        <v>0.08392480940981786</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01854456117307683</v>
+        <v>0.07815106644104639</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03834115444591726</v>
+        <v>0.1680277978304116</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.2813172501141</v>
+        <v>61.68877725682576</v>
       </c>
       <c r="C6" t="n">
-        <v>113506010.5627965</v>
+        <v>73.46858511734891</v>
       </c>
       <c r="D6" t="n">
-        <v>34.66348029955759</v>
+        <v>98.23292755706476</v>
       </c>
       <c r="E6" t="n">
-        <v>19586420.60607208</v>
+        <v>91.31372284499403</v>
       </c>
       <c r="F6" t="n">
-        <v>7390733.618811353</v>
+        <v>2474.197860006264</v>
       </c>
       <c r="G6" t="n">
-        <v>143.9008769030378</v>
+        <v>1107.456990311949</v>
       </c>
       <c r="H6" t="n">
-        <v>23413898.93889239</v>
+        <v>651.0598105157411</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02400642782521813</v>
+        <v>1.153328640132779</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0272592226490031</v>
+        <v>1.332040737436142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1300825351432868</v>
+        <v>1.781890154345295</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1145471660476534</v>
+        <v>1.80278504629566</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6777675183278989</v>
+        <v>6.243403851479323</v>
       </c>
       <c r="G7" t="n">
-        <v>1.142614550053167</v>
+        <v>20.26202214765447</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3527129033410379</v>
+        <v>5.429245096223945</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-48.33829885820569</v>
+        <v>-13.38402104092284</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.0893457095322</v>
+        <v>1.287908043958637</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.13961067926343</v>
+        <v>-26.56548573901584</v>
       </c>
       <c r="E8" t="n">
-        <v>-46.45899692040044</v>
+        <v>-28.04532403859622</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.13958312190503</v>
+        <v>-49.46801616984796</v>
       </c>
       <c r="G8" t="n">
-        <v>-99.67704700955099</v>
+        <v>-56.27690097935685</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.47381371647631</v>
+        <v>-28.74197332063018</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.94384970353325</v>
+        <v>-12.39789815424174</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.50582677107609</v>
+        <v>0.2467053900989118</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.55609174080733</v>
+        <v>-27.60668839287557</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.87547798194433</v>
+        <v>-29.08652669245595</v>
       </c>
       <c r="F9" t="n">
-        <v>-81.16976982232903</v>
+        <v>-47.04348292090796</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.54714829462792</v>
+        <v>-53.45215419204917</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.26636071905298</v>
+        <v>-28.22334082707191</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2704896958769257</v>
+        <v>-1.874866957665706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.451459625674964</v>
+        <v>-0.900340692963403</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.147039821451279</v>
+        <v>-0.2019060144192213</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.552010420787948</v>
+        <v>-0.8582739186190835</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.39458925594807</v>
+        <v>-3.777266643701708</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.866687999613852</v>
+        <v>-8.758022468110733</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.539729696041543</v>
+        <v>-2.728446115913309</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1281459102939406</v>
+        <v>0.2691529923582171</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2024270917062616</v>
+        <v>0.3564811414571474</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04819937001953484</v>
+        <v>0.02578361176443215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03045993540975718</v>
+        <v>0.02572026638763776</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03703434346474178</v>
+        <v>0.0502358179775369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02748419039359162</v>
+        <v>0.02675098713060099</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07895847354797127</v>
+        <v>0.1256874695125954</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03119038141837276</v>
+        <v>0.12291560027306</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07710103252747924</v>
+        <v>0.2671056456064697</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003164487136316955</v>
+        <v>0.0009171400047855292</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001503418810504897</v>
+        <v>0.001094730970879662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001624712449519369</v>
+        <v>0.003241342949338504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008807696214698848</v>
+        <v>0.00176599974278492</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01924413366061051</v>
+        <v>0.06617340992455305</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1766079879800819</v>
+        <v>0.3505932119608993</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2776707268105142</v>
+        <v>0.5168226442470083</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05625377441840641</v>
+        <v>0.03028431945389444</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03877394499538184</v>
+        <v>0.03308671895005097</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04030772195894192</v>
+        <v>0.05693279326836603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02967776308062797</v>
+        <v>0.04202379971855139</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1032153198739924</v>
+        <v>0.1716239145997951</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.05577420118438</v>
+        <v>269.7629545185741</v>
       </c>
       <c r="C6" t="n">
-        <v>99980333.89751077</v>
+        <v>98.86393151802991</v>
       </c>
       <c r="D6" t="n">
-        <v>100.7165734672028</v>
+        <v>44.07988762145504</v>
       </c>
       <c r="E6" t="n">
-        <v>136430117.0489591</v>
+        <v>62.91183594476782</v>
       </c>
       <c r="F6" t="n">
-        <v>47837810.56880286</v>
+        <v>3977.713431712262</v>
       </c>
       <c r="G6" t="n">
-        <v>413.421091038737</v>
+        <v>119.0240102487721</v>
       </c>
       <c r="H6" t="n">
-        <v>47374806.61811856</v>
+        <v>762.0593419273101</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2411863582297832</v>
+        <v>1.899002014981708</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2190328350667463</v>
+        <v>1.5161523196271</v>
       </c>
       <c r="D7" t="n">
-        <v>2.493654174861611</v>
+        <v>0.7244276046582326</v>
       </c>
       <c r="E7" t="n">
-        <v>1.534311038807476</v>
+        <v>1.118496974530682</v>
       </c>
       <c r="F7" t="n">
-        <v>1.440028150998169</v>
+        <v>2.872897866350099</v>
       </c>
       <c r="G7" t="n">
-        <v>2.922245877238369</v>
+        <v>5.85928588050634</v>
       </c>
       <c r="H7" t="n">
-        <v>1.475076405867026</v>
+        <v>2.33171044344236</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-29.20880967612859</v>
+        <v>-14.86631602200603</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.37583163868214</v>
+        <v>-3.920666134474625</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.53458567252513</v>
+        <v>-37.96550252232409</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.00008134393836</v>
+        <v>-36.90347980756674</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.06909319600715</v>
+        <v>-64.78121053422556</v>
       </c>
       <c r="G8" t="n">
-        <v>-89.45128801709239</v>
+        <v>-78.40749819183418</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.10661492406229</v>
+        <v>-39.47411220207187</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.01158509879237</v>
+        <v>-14.47186686733359</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.58407216945409</v>
+        <v>-4.337147196018515</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.74282620329708</v>
+        <v>-38.38198358386798</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.20832187471031</v>
+        <v>-37.31996086911063</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.58418654621914</v>
+        <v>-63.81139723464956</v>
       </c>
       <c r="G9" t="n">
-        <v>-88.88633865963085</v>
+        <v>-77.27759947691111</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.00288842535064</v>
+        <v>-39.26665920464856</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9243348021748079</v>
+        <v>-0.06308946836671714</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9305799700048665</v>
+        <v>-0.4508784747369825</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7234100527885048</v>
+        <v>-0.9009220680151979</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7590560409062479</v>
+        <v>-14.23765217726621</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.34941601714139</v>
+        <v>-2.404269757726109</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.630877265211264</v>
+        <v>-15.74041271505018</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2261812639202955</v>
+        <v>-5.632870776860234</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05018118992266771</v>
+        <v>0.1621328364049049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08440627404736427</v>
+        <v>0.2918070888237356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01243725468090755</v>
+        <v>0.03002523077767879</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00953221166722662</v>
+        <v>0.0906079750915232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02161255053898004</v>
+        <v>0.04426815157316305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01733222706181758</v>
+        <v>0.04737736773120705</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03258361798649397</v>
+        <v>0.1110364417337021</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003235082995984957</v>
+        <v>0.04545263557321732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00975745130392508</v>
+        <v>0.2039307125959729</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002110578551616267</v>
+        <v>0.001450539105088695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001419428688176068</v>
+        <v>0.00897667969980512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0009155695479650993</v>
+        <v>0.002309773893697027</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004761342360960286</v>
+        <v>0.003029667603810702</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002456206467991733</v>
+        <v>0.04419166807859862</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05687779000616108</v>
+        <v>0.2131962372398193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09877981222863851</v>
+        <v>0.4515868826659748</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01452783036663172</v>
+        <v>0.03808594366808698</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01191397787548755</v>
+        <v>0.09474534130924391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03025837979742305</v>
+        <v>0.0480601070920262</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02182050036309957</v>
+        <v>0.05504241640599276</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03902971510624024</v>
+        <v>0.150119488063524</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.36451901166404</v>
+        <v>113.5271005792236</v>
       </c>
       <c r="C6" t="n">
-        <v>107171588.9281006</v>
+        <v>51.94756938911495</v>
       </c>
       <c r="D6" t="n">
-        <v>25.62042383589248</v>
+        <v>42.02936064892007</v>
       </c>
       <c r="E6" t="n">
-        <v>34676875.21719491</v>
+        <v>295.6425401851361</v>
       </c>
       <c r="F6" t="n">
-        <v>9233798.14196662</v>
+        <v>2394.299746962058</v>
       </c>
       <c r="G6" t="n">
-        <v>197.7436607383216</v>
+        <v>758.8808221630198</v>
       </c>
       <c r="H6" t="n">
-        <v>25180422.50264429</v>
+        <v>609.3878566545787</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0259641174447471</v>
+        <v>0.7034873708225347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02865622491128762</v>
+        <v>1.158030082476552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08412472466206172</v>
+        <v>1.144583995556243</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07338254773629797</v>
+        <v>9.157158657939457</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8129314076519853</v>
+        <v>2.047795538086842</v>
       </c>
       <c r="G7" t="n">
-        <v>1.581192947057293</v>
+        <v>10.05048916367545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4343753282439455</v>
+        <v>4.04359080142618</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.60330626149442</v>
+        <v>-23.81976024467261</v>
       </c>
       <c r="C8" t="n">
-        <v>-23.7783442973134</v>
+        <v>-5.539849921804652</v>
       </c>
       <c r="D8" t="n">
-        <v>-46.78026960196405</v>
+        <v>-35.21491997021597</v>
       </c>
       <c r="E8" t="n">
-        <v>-49.16051548154439</v>
+        <v>-24.27875125362283</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.95157075450605</v>
+        <v>-68.84726768906698</v>
       </c>
       <c r="G8" t="n">
-        <v>-95.44753955350116</v>
+        <v>-71.39093077348524</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.12025765838724</v>
+        <v>-38.18191330881138</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.20885710682198</v>
+        <v>-23.42531109000017</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.19482535885729</v>
+        <v>-5.956330983348542</v>
       </c>
       <c r="D9" t="n">
-        <v>-47.19675066350794</v>
+        <v>-35.63140103175986</v>
       </c>
       <c r="E9" t="n">
-        <v>-49.57699654308828</v>
+        <v>-24.69523231516672</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.98175745493005</v>
+        <v>-67.87745438949098</v>
       </c>
       <c r="G9" t="n">
-        <v>-94.31764083857809</v>
+        <v>-70.26103205856217</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.91280466096394</v>
+        <v>-37.97446031138808</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8524121283350803</v>
+        <v>-0.2340831280227187</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8098869054569401</v>
+        <v>0.4818716621159402</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1333592707801856</v>
+        <v>-4.425211298057813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6995391102805146</v>
+        <v>-35.81193958788672</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2750858264220268</v>
+        <v>-2.941208610114028</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2904901141512752</v>
+        <v>-0.9272773354596631</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4132988545205786</v>
+        <v>-7.309641382904167</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05065165168574028</v>
+        <v>0.1494174662269666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1338567879114956</v>
+        <v>0.2158937282425435</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02282476881830642</v>
+        <v>0.0562880219130549</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01106726480170613</v>
+        <v>0.1471469872497781</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01551161346182172</v>
+        <v>0.03913996641673991</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01216173248223943</v>
+        <v>0.01586715146111039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04101230319355159</v>
+        <v>0.1039588869183656</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006310153515224478</v>
+        <v>0.05276350895588352</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02672167186289681</v>
+        <v>0.0728264172366455</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006613086822167781</v>
+        <v>0.004139823127740625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001770049799741182</v>
+        <v>0.02168634557114041</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000491849313914536</v>
+        <v>0.002674083255768749</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002335519534931832</v>
+        <v>0.0003487972373316274</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005765923384619983</v>
+        <v>0.02573982923075174</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07943647471548872</v>
+        <v>0.2297030886946963</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1634676477560524</v>
+        <v>0.2698637012209043</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0257159227370277</v>
+        <v>0.0643414573019653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01330432185322191</v>
+        <v>0.147262845182145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02217767602600723</v>
+        <v>0.05171153890350536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01528240666561335</v>
+        <v>0.01867611408542011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05323074162556855</v>
+        <v>0.1302597908981061</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.66539603591791</v>
+        <v>48.52808742332401</v>
       </c>
       <c r="C6" t="n">
-        <v>84007935.22937576</v>
+        <v>104.0584986077463</v>
       </c>
       <c r="D6" t="n">
-        <v>38.63381243525056</v>
+        <v>128.2616489274648</v>
       </c>
       <c r="E6" t="n">
-        <v>33186462.71268325</v>
+        <v>456.1532573812528</v>
       </c>
       <c r="F6" t="n">
-        <v>10916432.62119691</v>
+        <v>464.4809483038601</v>
       </c>
       <c r="G6" t="n">
-        <v>157.6343054030266</v>
+        <v>124.0549978408352</v>
       </c>
       <c r="H6" t="n">
-        <v>21351842.9161283</v>
+        <v>220.9229064140805</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04969346896013305</v>
+        <v>0.8163187893518682</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07673909866694575</v>
+        <v>0.2074169934308698</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2614551348434961</v>
+        <v>3.262922531213525</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09126217040182752</v>
+        <v>22.11952463653163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2188185465931322</v>
+        <v>2.370468882626493</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7766210412256557</v>
+        <v>1.158854717408062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2457649101151984</v>
+        <v>4.989251091760408</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-41.59035746461649</v>
+        <v>-22.47741900915819</v>
       </c>
       <c r="C8" t="n">
-        <v>-17.73368217531142</v>
+        <v>-11.71805909283587</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.92773900613668</v>
+        <v>-28.92261328895313</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.83599614203546</v>
+        <v>-18.98643471704587</v>
       </c>
       <c r="F8" t="n">
-        <v>-87.40805793097289</v>
+        <v>-67.08978398595018</v>
       </c>
       <c r="G8" t="n">
-        <v>-104.7073780871571</v>
+        <v>-99.49325722391507</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.533868467705</v>
+        <v>-41.44792788630971</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-41.19590830994405</v>
+        <v>-22.08296985448575</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.15016323685531</v>
+        <v>-12.13454015437976</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.34422006768057</v>
+        <v>-29.33909435049702</v>
       </c>
       <c r="E9" t="n">
-        <v>-48.25247720357935</v>
+        <v>-19.40291577858977</v>
       </c>
       <c r="F9" t="n">
-        <v>-86.43824463139688</v>
+        <v>-66.11997068637417</v>
       </c>
       <c r="G9" t="n">
-        <v>-103.577479372234</v>
+        <v>-98.36335850899199</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.32641547028169</v>
+        <v>-41.24047488888641</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5980621465028176</v>
+        <v>-0.003626906463657154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04439210722990161</v>
+        <v>-0.7914208671002909</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.604377170530574</v>
+        <v>-1.69461672614056</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.269905104079136</v>
+        <v>-8.393942754269787</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.27163850304695</v>
+        <v>-32.99488820205919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008026008216286629</v>
+        <v>-18.06140082579642</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.915906752617942</v>
+        <v>-10.32331604697165</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1050841019083412</v>
+        <v>0.1568701392734949</v>
       </c>
       <c r="C3" t="n">
-        <v>0.268838557964647</v>
+        <v>0.3379931959291588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0396430315272567</v>
+        <v>0.03793204723144439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05184663080142737</v>
+        <v>0.07206250422268616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1091504298687464</v>
+        <v>0.1493702628169159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01112031546668534</v>
+        <v>0.03905112917496451</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09761384458951733</v>
+        <v>0.1322132131081108</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01718494569056029</v>
+        <v>0.04291030001553184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1343171053081416</v>
+        <v>0.2517962326605506</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002750396832839409</v>
+        <v>0.002056184732798686</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003104561955747071</v>
+        <v>0.005534081907263616</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0123971818863208</v>
+        <v>0.0230653006008294</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001795267248117479</v>
+        <v>0.003449718328225389</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02832228639973681</v>
+        <v>0.05480196970753324</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1310913639053324</v>
+        <v>0.2071480147516066</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3664929812535863</v>
+        <v>0.5017930177479063</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05244422592468506</v>
+        <v>0.04534517320287448</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05571859613941355</v>
+        <v>0.07439141017122619</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1113426328336132</v>
+        <v>0.1518726459927179</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01339875833097037</v>
+        <v>0.05873430282403452</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1217480930646001</v>
+        <v>0.173214094115061</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.10009746069494</v>
+        <v>88.80140501324871</v>
       </c>
       <c r="C6" t="n">
-        <v>35429930.8060507</v>
+        <v>82.19777226964447</v>
       </c>
       <c r="D6" t="n">
-        <v>53.45346290153913</v>
+        <v>105.5262318951832</v>
       </c>
       <c r="E6" t="n">
-        <v>261001023.9133789</v>
+        <v>214.3418479462026</v>
       </c>
       <c r="F6" t="n">
-        <v>88629284.35182235</v>
+        <v>9175.407071240226</v>
       </c>
       <c r="G6" t="n">
-        <v>61.36058512593247</v>
+        <v>297.8647622894277</v>
       </c>
       <c r="H6" t="n">
-        <v>64176736.33089957</v>
+        <v>1660.689848442322</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1341108180325469</v>
+        <v>0.664250563899939</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3822043415467287</v>
+        <v>1.429367245984945</v>
       </c>
       <c r="D7" t="n">
-        <v>2.16947685788432</v>
+        <v>1.621648694310254</v>
       </c>
       <c r="E7" t="n">
-        <v>3.169289449185528</v>
+        <v>5.646113367232043</v>
       </c>
       <c r="F7" t="n">
-        <v>10.98333915646902</v>
+        <v>20.43122434207668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2992178662424823</v>
+        <v>11.44367010113737</v>
       </c>
       <c r="H7" t="n">
-        <v>2.856273081560105</v>
+        <v>6.872712385773538</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.57349376070262</v>
+        <v>-24.33779049437493</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.045310902952373</v>
+        <v>-4.274810714707096</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.37606044918171</v>
+        <v>-33.12141850905513</v>
       </c>
       <c r="E8" t="n">
-        <v>-28.64929590361849</v>
+        <v>-27.18097758195579</v>
       </c>
       <c r="F8" t="n">
-        <v>-46.6834331931894</v>
+        <v>-41.23311115145289</v>
       </c>
       <c r="G8" t="n">
-        <v>-106.1274241928498</v>
+        <v>-69.7030150384393</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.2425030670824</v>
+        <v>-33.30852058166419</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.98182002869396</v>
+        <v>-23.94334133970249</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.670032495268208</v>
+        <v>-4.691291776250986</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.00078204149754</v>
+        <v>-33.53789957059902</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.27401749593433</v>
+        <v>-27.59745864349969</v>
       </c>
       <c r="F9" t="n">
-        <v>-45.2287132438254</v>
+        <v>-40.26329785187689</v>
       </c>
       <c r="G9" t="n">
-        <v>-104.4325761204652</v>
+        <v>-68.57311632351623</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.93132357094743</v>
+        <v>-33.10106758424089</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.374511628918107</v>
+        <v>0.1104653564842443</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05307034858632154</v>
+        <v>0.1816805202346378</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.593142729548505</v>
+        <v>-0.07217772775675413</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.209195268943054</v>
+        <v>-1.013705180390188</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.674096410389299</v>
+        <v>0.007088250439611143</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.995100357154721</v>
+        <v>-1.058814391921116</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.691682247617299</v>
+        <v>-0.3075771954849276</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1236036012589695</v>
+        <v>0.1479644544894505</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2751620537663014</v>
+        <v>0.2798189668981919</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05196273027124796</v>
+        <v>0.02055598211787085</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03058171803047694</v>
+        <v>0.02806698321238466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0435732650577683</v>
+        <v>0.02155872515181445</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0366265246201526</v>
+        <v>0.01483623459947906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09358498216748611</v>
+        <v>0.08546689107819856</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02674289966370312</v>
+        <v>0.0380322589815426</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1480161078388868</v>
+        <v>0.1150202980783546</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003504895469712999</v>
+        <v>0.0008181480702889489</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001301462445589045</v>
+        <v>0.00118629735105583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002492849311783336</v>
+        <v>0.0006736838738101383</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001808905925102077</v>
+        <v>0.0003726027172469229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03064452010912956</v>
+        <v>0.02601721484538317</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1635325645359453</v>
+        <v>0.1950186118849752</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3847286158305447</v>
+        <v>0.3391464257195623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05920215764406733</v>
+        <v>0.02860328775314035</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03607578752555577</v>
+        <v>0.03444266759494436</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04992844191223412</v>
+        <v>0.0259554208944902</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0425312346999482</v>
+        <v>0.0193029199150523</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1226664670247159</v>
+        <v>0.1070782222936941</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.25783840216857</v>
+        <v>89.71410518011186</v>
       </c>
       <c r="C6" t="n">
-        <v>55407472.24138872</v>
+        <v>73.94685263136252</v>
       </c>
       <c r="D6" t="n">
-        <v>101.8921315208958</v>
+        <v>34.00712399551962</v>
       </c>
       <c r="E6" t="n">
-        <v>144663186.3034872</v>
+        <v>69.49607531259664</v>
       </c>
       <c r="F6" t="n">
-        <v>53590819.8353707</v>
+        <v>702.8126695995885</v>
       </c>
       <c r="G6" t="n">
-        <v>661.1111365929138</v>
+        <v>75.28916621049503</v>
       </c>
       <c r="H6" t="n">
-        <v>42277050.44022552</v>
+        <v>174.2109988216124</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2068665410891601</v>
+        <v>0.2944829743418066</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8400647601262345</v>
+        <v>0.3270100525844569</v>
       </c>
       <c r="D7" t="n">
-        <v>2.761792491386702</v>
+        <v>0.646452043952457</v>
       </c>
       <c r="E7" t="n">
-        <v>1.328339208789657</v>
+        <v>1.211883924525591</v>
       </c>
       <c r="F7" t="n">
-        <v>2.208947835270077</v>
+        <v>0.2993451035797838</v>
       </c>
       <c r="G7" t="n">
-        <v>6.000592682587977</v>
+        <v>1.237810278956816</v>
       </c>
       <c r="H7" t="n">
-        <v>2.224433919874968</v>
+        <v>0.6694973963234853</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-30.59337646605692</v>
+        <v>-25.42388502936295</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.462605046346455</v>
+        <v>-8.975879966989382</v>
       </c>
       <c r="D8" t="n">
-        <v>-31.92156749279219</v>
+        <v>-38.65080333631763</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.86560013196291</v>
+        <v>-36.42150975347592</v>
       </c>
       <c r="F8" t="n">
-        <v>-69.93194704958697</v>
+        <v>-83.63299504443448</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.09543001054639</v>
+        <v>-98.63497149306086</v>
       </c>
       <c r="H8" t="n">
-        <v>-43.3117543662153</v>
+        <v>-48.62334077060687</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-30.3961518887207</v>
+        <v>-25.02943587469051</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.670845577118401</v>
+        <v>-9.392361028533273</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.12980802356413</v>
+        <v>-39.06728439786152</v>
       </c>
       <c r="E9" t="n">
-        <v>-38.07384066273485</v>
+        <v>-36.83799081501981</v>
       </c>
       <c r="F9" t="n">
-        <v>-69.44704039979896</v>
+        <v>-82.66318174485848</v>
       </c>
       <c r="G9" t="n">
-        <v>-79.53048065308485</v>
+        <v>-97.50507277813779</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.20802786750365</v>
+        <v>-48.41588777318356</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7219507968120125</v>
+        <v>-0.720379391938752</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6655058291566938</v>
+        <v>-0.6627625320878658</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07982323803594005</v>
+        <v>-0.07035571199980684</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.1193869980427</v>
+        <v>-3.512555770607032</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.752022263113181</v>
+        <v>-5.428053898870361</v>
       </c>
       <c r="G2" t="n">
-        <v>-61.83446555728851</v>
+        <v>-31.83241896088811</v>
       </c>
       <c r="H2" t="n">
-        <v>-12.36219244707484</v>
+        <v>-7.037754377731987</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1813296168634512</v>
+        <v>0.1811820832640759</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3232198609904123</v>
+        <v>0.3227991830880492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02705970065515089</v>
+        <v>0.02695176920692947</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04271180619760223</v>
+        <v>0.04537545013213454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07065375491273128</v>
+        <v>0.06668325167449908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1035519216371019</v>
+        <v>0.1003046010042614</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1247544435427416</v>
+        <v>0.1238827230616583</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07362240373122481</v>
+        <v>0.07355521795319991</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2340980285300898</v>
+        <v>0.2337124397052159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000823982139883341</v>
+        <v>0.0008167577423265304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002426779218398287</v>
+        <v>0.002658399555850348</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005938187622915284</v>
+        <v>0.005412308864217153</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01137173544894324</v>
+        <v>0.01066376802025722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05471351944857578</v>
+        <v>0.05446981530684452</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2713344868077495</v>
+        <v>0.271210652359379</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4838367788108814</v>
+        <v>0.48343814465267</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02870508909380601</v>
+        <v>0.02857897378015051</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04926235092236552</v>
+        <v>0.05155966985784867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07705963679459749</v>
+        <v>0.07356839582468244</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1066383394888688</v>
+        <v>0.1032655219337859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1694727803197115</v>
+        <v>0.1686035597347527</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.3941069464933</v>
+        <v>59.31869257082558</v>
       </c>
       <c r="C6" t="n">
-        <v>73.46858511734891</v>
+        <v>73.1473930013597</v>
       </c>
       <c r="D6" t="n">
-        <v>58.2547337648142</v>
+        <v>59.00191854202349</v>
       </c>
       <c r="E6" t="n">
-        <v>116.8945010000821</v>
+        <v>125.1281255778794</v>
       </c>
       <c r="F6" t="n">
-        <v>5093.672569921243</v>
+        <v>4613.603445500888</v>
       </c>
       <c r="G6" t="n">
-        <v>1479.906152564523</v>
+        <v>1359.509528940825</v>
       </c>
       <c r="H6" t="n">
-        <v>1146.931774885751</v>
+        <v>1048.284850688967</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.137241843310922</v>
+        <v>1.136204940297731</v>
       </c>
       <c r="C7" t="n">
-        <v>1.328040737436142</v>
+        <v>1.325854934840022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6500475178174008</v>
+        <v>0.6443568880391413</v>
       </c>
       <c r="E7" t="n">
-        <v>2.476029689731378</v>
+        <v>2.712255221742411</v>
       </c>
       <c r="F7" t="n">
-        <v>5.260526820539991</v>
+        <v>3.865409571732121</v>
       </c>
       <c r="G7" t="n">
-        <v>37.71759976400163</v>
+        <v>19.71538065176123</v>
       </c>
       <c r="H7" t="n">
-        <v>8.094914395472911</v>
+        <v>4.899910368068777</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.47925310940555</v>
+        <v>-21.48747001136803</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.712091956041363</v>
+        <v>-6.721982856866598</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.60817021913138</v>
+        <v>-40.66100816857288</v>
       </c>
       <c r="E8" t="n">
-        <v>-34.12714195185485</v>
+        <v>-33.58018604798771</v>
       </c>
       <c r="F8" t="n">
-        <v>-59.51621567381983</v>
+        <v>-65.8480335006185</v>
       </c>
       <c r="G8" t="n">
-        <v>-56.19611653485673</v>
+        <v>-61.57264829834256</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.43983157418495</v>
+        <v>-38.31188814729271</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.28202853206933</v>
+        <v>-21.29024543403181</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.920332486813308</v>
+        <v>-6.930223387638543</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.81641074990333</v>
+        <v>-40.86924869934482</v>
       </c>
       <c r="E9" t="n">
-        <v>-34.3353824826268</v>
+        <v>-33.78842657875965</v>
       </c>
       <c r="F9" t="n">
-        <v>-59.03130902403183</v>
+        <v>-65.28308414315696</v>
       </c>
       <c r="G9" t="n">
-        <v>-55.6311671773952</v>
+        <v>-60.9335909687273</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.33610507547329</v>
+        <v>-38.18246986860984</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7402680851083621</v>
+        <v>-0.7357564678921553</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6655058291566938</v>
+        <v>-0.6627625320878658</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5865605900288331</v>
+        <v>-0.5685176010955908</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.56491591993468</v>
+        <v>-1.363242407804699</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.506525587155577</v>
+        <v>-5.669245738870557</v>
       </c>
       <c r="G2" t="n">
-        <v>-32.74745253799041</v>
+        <v>-16.48413452831864</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.968538091562427</v>
+        <v>-4.247276546011586</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1830487782189051</v>
+        <v>0.1826264781796371</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3232198609904123</v>
+        <v>0.3227991830880492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02807320078339531</v>
+        <v>0.02789056637944888</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05725694078851579</v>
+        <v>0.03152371652821151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07136614458707505</v>
+        <v>0.05811909759847253</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07698447843550096</v>
+        <v>0.0731706611182343</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1233249006339674</v>
+        <v>0.1160216171486756</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07440556361983008</v>
+        <v>0.07421266838450323</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2340980285300898</v>
+        <v>0.2337124397052159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00121065887821079</v>
+        <v>0.001196890790891104</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00386746900269369</v>
+        <v>0.001392213833277367</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005771619796781838</v>
+        <v>0.005615388171601199</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006107589185872846</v>
+        <v>0.005678739506433128</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05424348816891317</v>
+        <v>0.05363472339865365</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2727738323590261</v>
+        <v>0.2724200219963709</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4838367788108814</v>
+        <v>0.48343814465267</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03479452368133224</v>
+        <v>0.0345961094762273</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06218897814479419</v>
+        <v>0.03731238176902363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07597117740815815</v>
+        <v>0.0749358937465965</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07815106644104639</v>
+        <v>0.07535741175513612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1679527261408731</v>
+        <v>0.1630099938993374</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.68877725682576</v>
+        <v>61.53185376015702</v>
       </c>
       <c r="C6" t="n">
-        <v>73.46858511734891</v>
+        <v>73.1473930013597</v>
       </c>
       <c r="D6" t="n">
-        <v>79.16202456032879</v>
+        <v>78.62185581850757</v>
       </c>
       <c r="E6" t="n">
-        <v>161.8130118844954</v>
+        <v>85.41983395130042</v>
       </c>
       <c r="F6" t="n">
-        <v>4919.362998106447</v>
+        <v>1240.984159576235</v>
       </c>
       <c r="G6" t="n">
-        <v>1107.456990311949</v>
+        <v>1027.327328981727</v>
       </c>
       <c r="H6" t="n">
-        <v>1067.158731206232</v>
+        <v>427.8387375148811</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.149328640132779</v>
+        <v>1.149351616473598</v>
       </c>
       <c r="C7" t="n">
-        <v>1.328040737436142</v>
+        <v>1.328854934840022</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9546312764467951</v>
+        <v>0.9467862077646022</v>
       </c>
       <c r="E7" t="n">
-        <v>3.945364008564579</v>
+        <v>1.423894544049408</v>
       </c>
       <c r="F7" t="n">
-        <v>5.112995620008842</v>
+        <v>4.013408986762576</v>
       </c>
       <c r="G7" t="n">
-        <v>20.25802214765448</v>
+        <v>10.50243095230019</v>
       </c>
       <c r="H7" t="n">
-        <v>5.458063738373936</v>
+        <v>3.227454540365067</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.38402104092284</v>
+        <v>-15.40738369393503</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.712091956041363</v>
+        <v>-0.7219828568665978</v>
       </c>
       <c r="D8" t="n">
-        <v>-38.29954324076696</v>
+        <v>-32.36816855349085</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.33092994219946</v>
+        <v>-31.46116067804464</v>
       </c>
       <c r="F8" t="n">
-        <v>-59.85763012616166</v>
+        <v>-59.36917930595631</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.27690097935685</v>
+        <v>-64.3943638426118</v>
       </c>
       <c r="H8" t="n">
-        <v>-36.97685288090819</v>
+        <v>-33.9537064884842</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.18679646358662</v>
+        <v>-14.61848538459015</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.920332486813308</v>
+        <v>-1.554944979954378</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.5077837715389</v>
+        <v>-33.20113067657863</v>
       </c>
       <c r="E9" t="n">
-        <v>-31.53917047297141</v>
+        <v>-32.29412280113242</v>
       </c>
       <c r="F9" t="n">
-        <v>-59.37272347637366</v>
+        <v>-57.10938187611016</v>
       </c>
       <c r="G9" t="n">
-        <v>-63.71195162189532</v>
+        <v>-61.83813452415076</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.87312638219654</v>
+        <v>-33.43603337375274</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5070546556655879</v>
+        <v>-0.5082193055443167</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1284382375728996</v>
+        <v>-0.1216574554095637</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3057099625406368</v>
+        <v>-0.2759300076736511</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.214831213757406</v>
+        <v>-1.209859359086119</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.490934465860295</v>
+        <v>-0.8928967140939887</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.838851442279048</v>
+        <v>-1.129162018098078</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.080969996279312</v>
+        <v>-0.6896208099842863</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2354766336770275</v>
+        <v>0.2355695798598767</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2798916546039374</v>
+        <v>0.2799689147592905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02644763407746487</v>
+        <v>0.02621623002364936</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02875720703968259</v>
+        <v>0.02873398744113524</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03033532668080355</v>
+        <v>0.03033442831312958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02431460367533984</v>
+        <v>0.02350654213047237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.104203843292376</v>
+        <v>0.1040549470879256</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06443446962006706</v>
+        <v>0.0644842644944247</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1586095720046452</v>
+        <v>0.1576564875371278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009963498201410461</v>
+        <v>0.000973625590774062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001304783057372414</v>
+        <v>0.001301854079444653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001690082105595921</v>
+        <v>0.001593785899421102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006947525158718857</v>
+        <v>0.0006915387460664413</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03795500152061559</v>
+        <v>0.03778359272454313</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2538394563894019</v>
+        <v>0.2539375208479926</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3982581725522342</v>
+        <v>0.3970598034769168</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03156500942722885</v>
+        <v>0.03120297406937457</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03612178092747386</v>
+        <v>0.03608121504944994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04111060818810543</v>
+        <v>0.03992224817593696</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02635815843096565</v>
+        <v>0.02629712429271386</v>
       </c>
       <c r="H5" t="n">
-        <v>0.131208864319235</v>
+        <v>0.1307501476520641</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>286.4326612967199</v>
+        <v>286.5927001638634</v>
       </c>
       <c r="C6" t="n">
-        <v>61.58766666426906</v>
+        <v>62.07373868682902</v>
       </c>
       <c r="D6" t="n">
-        <v>72.28030788740932</v>
+        <v>71.32315005261397</v>
       </c>
       <c r="E6" t="n">
-        <v>90.19888600314097</v>
+        <v>90.02922149454801</v>
       </c>
       <c r="F6" t="n">
-        <v>994.4852283828437</v>
+        <v>960.4154476808139</v>
       </c>
       <c r="G6" t="n">
-        <v>374.9261498172942</v>
+        <v>362.5191023524281</v>
       </c>
       <c r="H6" t="n">
-        <v>313.3184833419462</v>
+        <v>305.4922267385161</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9964410508674468</v>
+        <v>0.9972095536187847</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9011163433502432</v>
+        <v>0.8957135557977172</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7868208672725796</v>
+        <v>0.7689210804312745</v>
       </c>
       <c r="E7" t="n">
-        <v>1.332725424534765</v>
+        <v>1.329738211162894</v>
       </c>
       <c r="F7" t="n">
-        <v>1.498926794464012</v>
+        <v>1.139969328715583</v>
       </c>
       <c r="G7" t="n">
-        <v>2.30628351888965</v>
+        <v>1.28046536510334</v>
       </c>
       <c r="H7" t="n">
-        <v>1.303718999896449</v>
+        <v>1.068669515804932</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-20.67895891863864</v>
+        <v>-20.67200641643508</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.047857710902463</v>
+        <v>-7.084020453906616</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.46847282202125</v>
+        <v>-37.60690239167911</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.85031094952906</v>
+        <v>-35.86379489381474</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.59573801641314</v>
+        <v>-79.74135931439537</v>
       </c>
       <c r="G8" t="n">
-        <v>-90.53541328511875</v>
+        <v>-97.87227927125497</v>
       </c>
       <c r="H8" t="n">
-        <v>-44.02945861710388</v>
+        <v>-46.47339379024765</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.2845097639662</v>
+        <v>-20.27755726176264</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.464338772446353</v>
+        <v>-7.500501515450506</v>
       </c>
       <c r="D9" t="n">
-        <v>-37.88495388356514</v>
+        <v>-38.023383453223</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.26679201107295</v>
+        <v>-36.28027595535863</v>
       </c>
       <c r="F9" t="n">
-        <v>-71.62592471683713</v>
+        <v>-78.6114605994723</v>
       </c>
       <c r="G9" t="n">
-        <v>-89.40551457019568</v>
+        <v>-96.59416461202446</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.82200561968057</v>
+        <v>-46.21455723288193</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7402680851083621</v>
+        <v>-0.7357564678921553</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6655058291566938</v>
+        <v>-0.6627625320878658</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.956220041564231</v>
+        <v>-1.929666722701176</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.992195356569522</v>
+        <v>-0.4012306937912842</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.380905213985098</v>
+        <v>-8.610918417216643</v>
       </c>
       <c r="G2" t="n">
-        <v>-32.74745253799041</v>
+        <v>-16.48413452831864</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.913757844062386</v>
+        <v>-4.804078227001295</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1830487782189051</v>
+        <v>0.1826264781796371</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3232198609904123</v>
+        <v>0.3227991830880492</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04155605587102768</v>
+        <v>0.0411100294193596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03484424656649474</v>
+        <v>0.02478182007251997</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07466553900356016</v>
+        <v>0.08012806233132651</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07698447843550096</v>
+        <v>0.0731706611182343</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1223864931809835</v>
+        <v>0.1207693723681878</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07440556361983008</v>
+        <v>0.07421266838450323</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2340980285300898</v>
+        <v>0.2337124397052159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002255806719111411</v>
+        <v>0.002235544643127957</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001762737395675855</v>
+        <v>0.0008254814440814172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007043373634474252</v>
+        <v>0.008092225074825652</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006107589185872846</v>
+        <v>0.005678739506433128</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05427884984750903</v>
+        <v>0.05412618312636455</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2727738323590261</v>
+        <v>0.2724200219963709</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4838367788108814</v>
+        <v>0.48343814465267</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04749533365617523</v>
+        <v>0.04728154653908813</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04198496630552245</v>
+        <v>0.02873119287606098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08392480940981786</v>
+        <v>0.08995679560114206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07815106644104639</v>
+        <v>0.07535741175513612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1680277978304116</v>
+        <v>0.1661975189034114</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.68877725682576</v>
+        <v>61.53185376015702</v>
       </c>
       <c r="C6" t="n">
-        <v>73.46858511734891</v>
+        <v>73.1473930013597</v>
       </c>
       <c r="D6" t="n">
-        <v>98.23292755706476</v>
+        <v>96.1661937470933</v>
       </c>
       <c r="E6" t="n">
-        <v>91.31372284499403</v>
+        <v>56.01108813212541</v>
       </c>
       <c r="F6" t="n">
-        <v>2474.197860006264</v>
+        <v>2298.882399550662</v>
       </c>
       <c r="G6" t="n">
-        <v>1107.456990311949</v>
+        <v>1027.327328981727</v>
       </c>
       <c r="H6" t="n">
-        <v>651.0598105157411</v>
+        <v>602.1777095288541</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.153328640132779</v>
+        <v>1.150351616473598</v>
       </c>
       <c r="C7" t="n">
-        <v>1.332040737436142</v>
+        <v>1.329854934840022</v>
       </c>
       <c r="D7" t="n">
-        <v>1.781890154345295</v>
+        <v>1.765929796121085</v>
       </c>
       <c r="E7" t="n">
-        <v>1.80278504629566</v>
+        <v>0.8468940902964847</v>
       </c>
       <c r="F7" t="n">
-        <v>6.243403851479323</v>
+        <v>5.782880165434743</v>
       </c>
       <c r="G7" t="n">
-        <v>20.26202214765447</v>
+        <v>10.5034309523002</v>
       </c>
       <c r="H7" t="n">
-        <v>5.429245096223945</v>
+        <v>3.563223592577688</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-13.38402104092284</v>
+        <v>-13.40738369393503</v>
       </c>
       <c r="C8" t="n">
-        <v>1.287908043958637</v>
+        <v>1.278017143133402</v>
       </c>
       <c r="D8" t="n">
-        <v>-26.56548573901584</v>
+        <v>-26.61962235441994</v>
       </c>
       <c r="E8" t="n">
-        <v>-28.04532403859622</v>
+        <v>-32.59726263953592</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.46801616984796</v>
+        <v>-52.61907009249896</v>
       </c>
       <c r="G8" t="n">
-        <v>-56.27690097935685</v>
+        <v>-62.3943638426118</v>
       </c>
       <c r="H8" t="n">
-        <v>-28.74197332063018</v>
+        <v>-31.05994757997804</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-12.39789815424174</v>
+        <v>-12.42126080725393</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2467053900989118</v>
+        <v>0.2368144892736765</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.60668839287557</v>
+        <v>-27.66082500827967</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.08652669245595</v>
+        <v>-33.63846529339565</v>
       </c>
       <c r="F9" t="n">
-        <v>-47.04348292090796</v>
+        <v>-49.79432330519128</v>
       </c>
       <c r="G9" t="n">
-        <v>-53.45215419204917</v>
+        <v>-59.1990771945355</v>
       </c>
       <c r="H9" t="n">
-        <v>-28.22334082707191</v>
+        <v>-30.41285618656373</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.874866957665706</v>
+        <v>-1.585942499818243</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.900340692963403</v>
+        <v>-0.6421595913397733</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2019060144192213</v>
+        <v>-1.914636249697871</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8582739186190835</v>
+        <v>-9.855874078244574</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.777266643701708</v>
+        <v>-0.03461459980641401</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.758022468110733</v>
+        <v>-6.008922653784118</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.728446115913309</v>
+        <v>-3.340358278781832</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2691529923582171</v>
+        <v>0.2395520432269244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3564811414571474</v>
+        <v>0.3217474673273396</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02578361176443215</v>
+        <v>0.03726782804328437</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02572026638763776</v>
+        <v>0.07624774803697025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0502358179775369</v>
+        <v>0.02671906521579672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02675098713060099</v>
+        <v>0.03877022768963296</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1256874695125954</v>
+        <v>0.123384063256658</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.12291560027306</v>
+        <v>0.1105625683961606</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2671056456064697</v>
+        <v>0.2308165580297415</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009171400047855292</v>
+        <v>0.00222407532030504</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001094730970879662</v>
+        <v>0.006395322804861538</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003241342949338504</v>
+        <v>0.0008711273828249631</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00176599974278492</v>
+        <v>0.002276455028821236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06617340992455305</v>
+        <v>0.05885768449378581</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3505932119608993</v>
+        <v>0.332509501211861</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5168226442470083</v>
+        <v>0.4804337186644392</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03028431945389444</v>
+        <v>0.04716010305655661</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03308671895005097</v>
+        <v>0.07997076218757414</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05693279326836603</v>
+        <v>0.02951486714903123</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04202379971855139</v>
+        <v>0.04771221047930222</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1716239145997951</v>
+        <v>0.1695501937914607</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>269.7629545185741</v>
+        <v>246.6602240467429</v>
       </c>
       <c r="C6" t="n">
-        <v>98.86393151802991</v>
+        <v>72.44967579328173</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07988762145504</v>
+        <v>107.6813136949151</v>
       </c>
       <c r="E6" t="n">
-        <v>62.91183594476782</v>
+        <v>220.5157318104225</v>
       </c>
       <c r="F6" t="n">
-        <v>3977.713431712262</v>
+        <v>1758.61924820668</v>
       </c>
       <c r="G6" t="n">
-        <v>119.0240102487721</v>
+        <v>434.9881056529599</v>
       </c>
       <c r="H6" t="n">
-        <v>762.0593419273101</v>
+        <v>473.4857165341671</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.899002014981708</v>
+        <v>1.71135309564557</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5161523196271</v>
+        <v>1.313438936045502</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7244276046582326</v>
+        <v>1.75689545526715</v>
       </c>
       <c r="E7" t="n">
-        <v>1.118496974530682</v>
+        <v>6.527477898873551</v>
       </c>
       <c r="F7" t="n">
-        <v>2.872897866350099</v>
+        <v>0.6269883382198035</v>
       </c>
       <c r="G7" t="n">
-        <v>5.85928588050634</v>
+        <v>4.213540629310821</v>
       </c>
       <c r="H7" t="n">
-        <v>2.33171044344236</v>
+        <v>2.6916157255604</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-14.86631602200603</v>
+        <v>-9.819563195981992</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.920666134474625</v>
+        <v>1.203207969850647</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.96550252232409</v>
+        <v>-26.65048421674186</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.90347980756674</v>
+        <v>-20.31313020517983</v>
       </c>
       <c r="F8" t="n">
-        <v>-64.78121053422556</v>
+        <v>-81.59439045727288</v>
       </c>
       <c r="G8" t="n">
-        <v>-78.40749819183418</v>
+        <v>-75.19190201074986</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.47411220207187</v>
+        <v>-35.39437701934596</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-14.47186686733359</v>
+        <v>-8.833440309300894</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.337147196018515</v>
+        <v>0.1620053159909212</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.38198358386798</v>
+        <v>-27.69168687060159</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.31996086911063</v>
+        <v>-21.35433285903956</v>
       </c>
       <c r="F9" t="n">
-        <v>-63.81139723464956</v>
+        <v>-78.76964366996519</v>
       </c>
       <c r="G9" t="n">
-        <v>-77.27759947691111</v>
+        <v>-71.99661536267357</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.26665920464856</v>
+        <v>-34.74728562593165</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.06308946836671714</v>
+        <v>0.1197259009980576</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4508784747369825</v>
+        <v>-0.1204340204955177</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9009220680151979</v>
+        <v>-3.306133932570119</v>
       </c>
       <c r="E2" t="n">
-        <v>-14.23765217726621</v>
+        <v>-2.7422684583095</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.404269757726109</v>
+        <v>-0.8705903152851102</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.74041271505018</v>
+        <v>-7.857033402197152</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.632870776860234</v>
+        <v>-2.462789037976556</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1621328364049049</v>
+        <v>0.1571928659932406</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2918070888237356</v>
+        <v>0.2682220506315554</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03002523077767879</v>
+        <v>0.03993345347207895</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0906079750915232</v>
+        <v>0.03807227550923062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04426815157316305</v>
+        <v>0.03715560521097146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04737736773120705</v>
+        <v>0.04781208982836077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1110364417337021</v>
+        <v>0.09806472344090629</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04545263557321732</v>
+        <v>0.03763632226358923</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2039307125959729</v>
+        <v>0.157484525544321</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001450539105088695</v>
+        <v>0.003285887289142872</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00897667969980512</v>
+        <v>0.002204614261444235</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002309773893697027</v>
+        <v>0.001575004302082089</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003029667603810702</v>
+        <v>0.002876710048723902</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04419166807859862</v>
+        <v>0.03417717728488389</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2131962372398193</v>
+        <v>0.1940008305744829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4515868826659748</v>
+        <v>0.3968432001991731</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03808594366808698</v>
+        <v>0.05732265947374451</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09474534130924391</v>
+        <v>0.04695332002578981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0480601070920262</v>
+        <v>0.0396863238670715</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05504241640599276</v>
+        <v>0.05363497038988557</v>
       </c>
       <c r="H5" t="n">
-        <v>0.150119488063524</v>
+        <v>0.1314068840883579</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>113.5271005792236</v>
+        <v>123.7344933817658</v>
       </c>
       <c r="C6" t="n">
-        <v>51.94756938911495</v>
+        <v>52.88546784932988</v>
       </c>
       <c r="D6" t="n">
-        <v>42.02936064892007</v>
+        <v>54.59153901381237</v>
       </c>
       <c r="E6" t="n">
-        <v>295.6425401851361</v>
+        <v>133.3094830403781</v>
       </c>
       <c r="F6" t="n">
-        <v>2394.299746962058</v>
+        <v>1918.521247980415</v>
       </c>
       <c r="G6" t="n">
-        <v>758.8808221630198</v>
+        <v>686.4903701973701</v>
       </c>
       <c r="H6" t="n">
-        <v>609.3878566545787</v>
+        <v>494.9221002438451</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7034873708225347</v>
+        <v>0.2914276552850952</v>
       </c>
       <c r="C7" t="n">
-        <v>1.158030082476552</v>
+        <v>0.89473874805936</v>
       </c>
       <c r="D7" t="n">
-        <v>1.144583995556243</v>
+        <v>2.590280601746872</v>
       </c>
       <c r="E7" t="n">
-        <v>9.157158657939457</v>
+        <v>2.250447534951722</v>
       </c>
       <c r="F7" t="n">
-        <v>2.047795538086842</v>
+        <v>1.126559195193981</v>
       </c>
       <c r="G7" t="n">
-        <v>10.05048916367545</v>
+        <v>5.320247435386505</v>
       </c>
       <c r="H7" t="n">
-        <v>4.04359080142618</v>
+        <v>2.078950195103923</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.81976024467261</v>
+        <v>-25.51807109509171</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.539849921804652</v>
+        <v>-7.090568456333568</v>
       </c>
       <c r="D8" t="n">
-        <v>-35.21491997021597</v>
+        <v>-30.30871136166222</v>
       </c>
       <c r="E8" t="n">
-        <v>-24.27875125362283</v>
+        <v>-32.70321634104388</v>
       </c>
       <c r="F8" t="n">
-        <v>-68.84726768906698</v>
+        <v>-79.89546457795853</v>
       </c>
       <c r="G8" t="n">
-        <v>-71.39093077348524</v>
+        <v>-77.91551174799758</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.18191330881138</v>
+        <v>-42.23859059668125</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-23.42531109000017</v>
+        <v>-25.12362194041927</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.956330983348542</v>
+        <v>-7.507049517877458</v>
       </c>
       <c r="D9" t="n">
-        <v>-35.63140103175986</v>
+        <v>-30.72519242320611</v>
       </c>
       <c r="E9" t="n">
-        <v>-24.69523231516672</v>
+        <v>-33.11969740258778</v>
       </c>
       <c r="F9" t="n">
-        <v>-67.87745438949098</v>
+        <v>-78.76556586303546</v>
       </c>
       <c r="G9" t="n">
-        <v>-70.26103205856217</v>
+        <v>-76.63739708876707</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.97446031138808</v>
+        <v>-41.97975403931552</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.2340831280227187</v>
+        <v>-0.241075260050521</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4818716621159402</v>
+        <v>0.4774781494814297</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.425211298057813</v>
+        <v>-3.659736686411827</v>
       </c>
       <c r="E2" t="n">
-        <v>-35.81193958788672</v>
+        <v>-39.049479540219</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.941208610114028</v>
+        <v>-2.332997404382326</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9272773354596631</v>
+        <v>-2.401768248918339</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.309641382904167</v>
+        <v>-7.867929831750097</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1494174662269666</v>
+        <v>0.1499943537392076</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2158937282425435</v>
+        <v>0.216853368971591</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0562880219130549</v>
+        <v>0.04864512500391807</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1471469872497781</v>
+        <v>0.1534831188964386</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03913996641673991</v>
+        <v>0.04088271297968599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01586715146111039</v>
+        <v>0.01673577234592554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1039588869183656</v>
+        <v>0.1044324086561278</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05276350895588352</v>
+        <v>0.05306245917446464</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0728264172366455</v>
+        <v>0.07344395494084059</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004139823127740625</v>
+        <v>0.003555711408050596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02168634557114041</v>
+        <v>0.02359361834711103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002674083255768749</v>
+        <v>0.002806325472678654</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003487972373316274</v>
+        <v>0.001104873433430399</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02573982923075174</v>
+        <v>0.02626115712942931</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2297030886946963</v>
+        <v>0.2303529013806092</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2698637012209043</v>
+        <v>0.2710054518655309</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0643414573019653</v>
+        <v>0.05962978624857376</v>
       </c>
       <c r="E5" t="n">
-        <v>0.147262845182145</v>
+        <v>0.1536021430420521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05171153890350536</v>
+        <v>0.05297476260143743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01867611408542011</v>
+        <v>0.03323963648162234</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1302597908981061</v>
+        <v>0.1334674469366376</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.52808742332401</v>
+        <v>48.99242248337388</v>
       </c>
       <c r="C6" t="n">
-        <v>104.0584986077463</v>
+        <v>105.0324114952438</v>
       </c>
       <c r="D6" t="n">
-        <v>128.2616489274648</v>
+        <v>110.8226286659933</v>
       </c>
       <c r="E6" t="n">
-        <v>456.1532573812528</v>
+        <v>475.845602167809</v>
       </c>
       <c r="F6" t="n">
-        <v>464.4809483038601</v>
+        <v>410.4414765038554</v>
       </c>
       <c r="G6" t="n">
-        <v>124.0549978408352</v>
+        <v>76.46480831722235</v>
       </c>
       <c r="H6" t="n">
-        <v>220.9229064140805</v>
+        <v>204.599891605583</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8163187893518682</v>
+        <v>0.8209325988745633</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2074169934308698</v>
+        <v>0.2091673236141595</v>
       </c>
       <c r="D7" t="n">
-        <v>3.262922531213525</v>
+        <v>2.802820007818367</v>
       </c>
       <c r="E7" t="n">
-        <v>22.11952463653163</v>
+        <v>24.06471878981736</v>
       </c>
       <c r="F7" t="n">
-        <v>2.370468882626493</v>
+        <v>2.005727298291146</v>
       </c>
       <c r="G7" t="n">
-        <v>1.158854717408062</v>
+        <v>2.044607772157806</v>
       </c>
       <c r="H7" t="n">
-        <v>4.989251091760408</v>
+        <v>5.3246622984289</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-22.47741900915819</v>
+        <v>-22.42657025867023</v>
       </c>
       <c r="C8" t="n">
-        <v>-11.71805909283587</v>
+        <v>-11.66739608863769</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.92261328895313</v>
+        <v>-29.83520072579036</v>
       </c>
       <c r="E8" t="n">
-        <v>-18.98643471704587</v>
+        <v>-18.48067407523042</v>
       </c>
       <c r="F8" t="n">
-        <v>-67.08978398595018</v>
+        <v>-72.38643106041515</v>
       </c>
       <c r="G8" t="n">
-        <v>-99.49325722391507</v>
+        <v>-91.31234286636447</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.44792788630971</v>
+        <v>-41.01810251251806</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.08296985448575</v>
+        <v>-22.03212110399779</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.13454015437976</v>
+        <v>-12.08387715018157</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.33909435049702</v>
+        <v>-30.25168178733425</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.40291577858977</v>
+        <v>-18.89715513677431</v>
       </c>
       <c r="F9" t="n">
-        <v>-66.11997068637417</v>
+        <v>-71.25653234549208</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.36335850899199</v>
+        <v>-90.03422820713396</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.24047488888641</v>
+        <v>-40.75926595515232</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.003626906463657154</v>
+        <v>0.1713139368472347</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7914208671002909</v>
+        <v>-0.4184761049847014</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.69461672614056</v>
+        <v>-7.404745568787067</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.393942754269787</v>
+        <v>-34.23888648697653</v>
       </c>
       <c r="F2" t="n">
-        <v>-32.99488820205919</v>
+        <v>-0.7583459306042888</v>
       </c>
       <c r="G2" t="n">
-        <v>-18.06140082579642</v>
+        <v>-7.300806958841838</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.32331604697165</v>
+        <v>-8.324991185557865</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1568701392734949</v>
+        <v>0.1610752851602301</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3379931959291588</v>
+        <v>0.2943996746126746</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03793204723144439</v>
+        <v>0.07387260299337246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07206250422268616</v>
+        <v>0.1435825820567276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1493702628169159</v>
+        <v>0.03237178108220377</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03905112917496451</v>
+        <v>0.02921248230169585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1322132131081108</v>
+        <v>0.122419068034484</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04291030001553184</v>
+        <v>0.03543066388471997</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2517962326605506</v>
+        <v>0.1993763419381693</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002056184732798686</v>
+        <v>0.00641342026639521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005534081907263616</v>
+        <v>0.0207596415308209</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0230653006008294</v>
+        <v>0.001480496494941055</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003449718328225389</v>
+        <v>0.002696051116290696</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05480196970753324</v>
+        <v>0.04435943587188951</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2071480147516066</v>
+        <v>0.1882303479376266</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5017930177479063</v>
+        <v>0.4465157801670276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04534517320287448</v>
+        <v>0.08008383274041778</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07439141017122619</v>
+        <v>0.1440820652642823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1518726459927179</v>
+        <v>0.03847722046797371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05873430282403452</v>
+        <v>0.05192351217214313</v>
       </c>
       <c r="H5" t="n">
-        <v>0.173214094115061</v>
+        <v>0.1582187931249119</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>88.80140501324871</v>
+        <v>134.1136909383512</v>
       </c>
       <c r="C6" t="n">
-        <v>82.19777226964447</v>
+        <v>58.71925358545463</v>
       </c>
       <c r="D6" t="n">
-        <v>105.5262318951832</v>
+        <v>135.2382552682407</v>
       </c>
       <c r="E6" t="n">
-        <v>214.3418479462026</v>
+        <v>434.9273033496682</v>
       </c>
       <c r="F6" t="n">
-        <v>9175.407071240226</v>
+        <v>1265.704914801616</v>
       </c>
       <c r="G6" t="n">
-        <v>297.8647622894277</v>
+        <v>149.7882286838346</v>
       </c>
       <c r="H6" t="n">
-        <v>1660.689848442322</v>
+        <v>363.0819411045275</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.664250563899939</v>
+        <v>0.2744072836651336</v>
       </c>
       <c r="C7" t="n">
-        <v>1.429367245984945</v>
+        <v>1.132212541704258</v>
       </c>
       <c r="D7" t="n">
-        <v>1.621648694310254</v>
+        <v>5.053826129645194</v>
       </c>
       <c r="E7" t="n">
-        <v>5.646113367232043</v>
+        <v>21.17439539032907</v>
       </c>
       <c r="F7" t="n">
-        <v>20.43122434207668</v>
+        <v>1.059080253455491</v>
       </c>
       <c r="G7" t="n">
-        <v>11.44367010113737</v>
+        <v>4.986258646867911</v>
       </c>
       <c r="H7" t="n">
-        <v>6.872712385773538</v>
+        <v>5.613363374277843</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-24.33779049437493</v>
+        <v>-26.06159860118833</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.274810714707096</v>
+        <v>-5.675366448447914</v>
       </c>
       <c r="D8" t="n">
-        <v>-33.12141850905513</v>
+        <v>-26.29617540471996</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.18097758195579</v>
+        <v>-19.24846692881017</v>
       </c>
       <c r="F8" t="n">
-        <v>-41.23311115145289</v>
+        <v>-80.69991111281279</v>
       </c>
       <c r="G8" t="n">
-        <v>-69.7030150384393</v>
+        <v>-78.82353976488673</v>
       </c>
       <c r="H8" t="n">
-        <v>-33.30852058166419</v>
+        <v>-39.46750971014432</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-23.94334133970249</v>
+        <v>-25.66714944651589</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.691291776250986</v>
+        <v>-6.091847509991804</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.53789957059902</v>
+        <v>-26.71265646626386</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.59745864349969</v>
+        <v>-19.66494799035406</v>
       </c>
       <c r="F9" t="n">
-        <v>-40.26329785187689</v>
+        <v>-79.57001239788971</v>
       </c>
       <c r="G9" t="n">
-        <v>-68.57311632351623</v>
+        <v>-77.54542510565622</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.10106758424089</v>
+        <v>-39.20867315277859</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1104653564842443</v>
+        <v>0.1106868443557812</v>
       </c>
       <c r="C2" t="n">
         <v>0.1816805202346378</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07217772775675413</v>
+        <v>-0.1939863666731814</v>
       </c>
       <c r="E2" t="n">
         <v>-1.013705180390188</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007088250439611143</v>
+        <v>-0.2230199780537203</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.058814391921116</v>
+        <v>-0.4007250821427966</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3075771954849276</v>
+        <v>-0.2565115404449113</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1479644544894505</v>
+        <v>0.1479450845877643</v>
       </c>
       <c r="C3" t="n">
         <v>0.2798189668981919</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02055598211787085</v>
+        <v>0.02425931294058893</v>
       </c>
       <c r="E3" t="n">
         <v>0.02806698321238466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02155872515181445</v>
+        <v>0.02550186817953367</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01483623459947906</v>
+        <v>0.01502357160269399</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08546689107819856</v>
+        <v>0.08676929790352622</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0380322589815426</v>
+        <v>0.03802278921647727</v>
       </c>
       <c r="C4" t="n">
         <v>0.1150202980783546</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008181480702889489</v>
+        <v>0.0009110967487533906</v>
       </c>
       <c r="E4" t="n">
         <v>0.00118629735105583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006736838738101383</v>
+        <v>0.001029761413403531</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003726027172469229</v>
+        <v>0.0004549469033615938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02601721484538317</v>
+        <v>0.02610419828523436</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1950186118849752</v>
+        <v>0.1949943312419037</v>
       </c>
       <c r="C5" t="n">
         <v>0.3391464257195623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02860328775314035</v>
+        <v>0.03018437921762498</v>
       </c>
       <c r="E5" t="n">
         <v>0.03444266759494436</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0259554208944902</v>
+        <v>0.03208989581478149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0193029199150523</v>
+        <v>0.0213294843669882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1070782222936941</v>
+        <v>0.1086978639926342</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.71410518011186</v>
+        <v>89.70501787635182</v>
       </c>
       <c r="C6" t="n">
         <v>73.94685263136252</v>
       </c>
       <c r="D6" t="n">
-        <v>34.00712399551962</v>
+        <v>43.08641162352664</v>
       </c>
       <c r="E6" t="n">
         <v>69.49607531259664</v>
       </c>
       <c r="F6" t="n">
-        <v>702.8126695995885</v>
+        <v>652.1617290519558</v>
       </c>
       <c r="G6" t="n">
-        <v>75.28916621049503</v>
+        <v>66.71228891265535</v>
       </c>
       <c r="H6" t="n">
-        <v>174.2109988216124</v>
+        <v>165.8513959014082</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2944829743418066</v>
+        <v>0.2944098991447998</v>
       </c>
       <c r="C7" t="n">
         <v>0.3270100525844569</v>
       </c>
       <c r="D7" t="n">
-        <v>0.646452043952457</v>
+        <v>0.7196673554521636</v>
       </c>
       <c r="E7" t="n">
         <v>1.211883924525591</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2993451035797838</v>
+        <v>0.7372536528109972</v>
       </c>
       <c r="G7" t="n">
-        <v>1.237810278956816</v>
+        <v>0.8430719749503842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6694973963234853</v>
+        <v>0.6888828099113988</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-25.42388502936295</v>
+        <v>-25.42612624511516</v>
       </c>
       <c r="C8" t="n">
         <v>-8.975879966989382</v>
       </c>
       <c r="D8" t="n">
-        <v>-38.65080333631763</v>
+        <v>-38.00516879441449</v>
       </c>
       <c r="E8" t="n">
         <v>-36.42150975347592</v>
       </c>
       <c r="F8" t="n">
-        <v>-83.63299504443448</v>
+        <v>-85.41956583358494</v>
       </c>
       <c r="G8" t="n">
-        <v>-98.63497149306086</v>
+        <v>-103.7346177842397</v>
       </c>
       <c r="H8" t="n">
-        <v>-48.62334077060687</v>
+        <v>-49.66381139630326</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-25.02943587469051</v>
+        <v>-25.03167709044272</v>
       </c>
       <c r="C9" t="n">
         <v>-9.392361028533273</v>
       </c>
       <c r="D9" t="n">
-        <v>-39.06728439786152</v>
+        <v>-38.42164985595838</v>
       </c>
       <c r="E9" t="n">
         <v>-36.83799081501981</v>
       </c>
       <c r="F9" t="n">
-        <v>-82.66318174485848</v>
+        <v>-84.28966711866187</v>
       </c>
       <c r="G9" t="n">
-        <v>-97.50507277813779</v>
+        <v>-102.4565031250092</v>
       </c>
       <c r="H9" t="n">
-        <v>-48.41588777318356</v>
+        <v>-49.40497483893754</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.720379391938752</v>
+        <v>0.624218231661847</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6627625320878658</v>
+        <v>0.5469542506087026</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07035571199980684</v>
+        <v>-1.005002847660437</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.512555770607032</v>
+        <v>-2.593949280898641</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.428053898870361</v>
+        <v>-10.48234707606543</v>
       </c>
       <c r="G2" t="n">
-        <v>-31.83241896088811</v>
+        <v>-18.82288847642363</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.037754377731987</v>
+        <v>-5.288835866462932</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1811820832640759</v>
+        <v>0.1123789981191349</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3227991830880492</v>
+        <v>0.1878857632202878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02695176920692947</v>
+        <v>0.02392587127281239</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04537545013213454</v>
+        <v>0.03976094122229139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06668325167449908</v>
+        <v>0.08254573396227728</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1003046010042614</v>
+        <v>0.05503785470208666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1238827230616583</v>
+        <v>0.08358919374981506</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07355521795319991</v>
+        <v>0.0160666362329547</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2337124397052159</v>
+        <v>0.06367862237992912</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008167577423265304</v>
+        <v>0.001529960162639556</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002658399555850348</v>
+        <v>0.00211723769361955</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005412308864217153</v>
+        <v>0.007790694452010615</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01066376802025722</v>
+        <v>0.003587531804217714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05446981530684452</v>
+        <v>0.01579511378756187</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.271210652359379</v>
+        <v>0.1267542355621882</v>
       </c>
       <c r="C5" t="n">
-        <v>0.48343814465267</v>
+        <v>0.2523462351213688</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02857897378015051</v>
+        <v>0.03911470519688927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05155966985784867</v>
+        <v>0.04601345122482718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07356839582468244</v>
+        <v>0.08826491064976283</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1032655219337859</v>
+        <v>0.05989600824944609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1686035597347527</v>
+        <v>0.1020649243340804</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.31869257082558</v>
+        <v>80.9134790190225</v>
       </c>
       <c r="C6" t="n">
-        <v>73.1473930013597</v>
+        <v>42.44813567373596</v>
       </c>
       <c r="D6" t="n">
-        <v>59.00191854202349</v>
+        <v>35.41622444215896</v>
       </c>
       <c r="E6" t="n">
-        <v>125.1281255778794</v>
+        <v>89.8255146214133</v>
       </c>
       <c r="F6" t="n">
-        <v>4613.603445500888</v>
+        <v>5329.458208604381</v>
       </c>
       <c r="G6" t="n">
-        <v>1359.509528940825</v>
+        <v>794.2028229569027</v>
       </c>
       <c r="H6" t="n">
-        <v>1048.284850688967</v>
+        <v>1062.044064219602</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.136204940297731</v>
+        <v>0.1244811758645142</v>
       </c>
       <c r="C7" t="n">
-        <v>1.325854934840022</v>
+        <v>0.1809887604833396</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6443568880391413</v>
+        <v>1.206143652823957</v>
       </c>
       <c r="E7" t="n">
-        <v>2.712255221742411</v>
+        <v>2.160333701310252</v>
       </c>
       <c r="F7" t="n">
-        <v>3.865409571732121</v>
+        <v>6.901315217872075</v>
       </c>
       <c r="G7" t="n">
-        <v>19.71538065176123</v>
+        <v>11.89975563038009</v>
       </c>
       <c r="H7" t="n">
-        <v>4.899910368068777</v>
+        <v>3.745503023122371</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.48747001136803</v>
+        <v>-35.17909396728932</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.721982856866598</v>
+        <v>-14.52343822696617</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.66100816857288</v>
+        <v>-36.89508148844356</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.58018604798771</v>
+        <v>-34.94585808769368</v>
       </c>
       <c r="F8" t="n">
-        <v>-65.8480335006185</v>
+        <v>-56.25790331767885</v>
       </c>
       <c r="G8" t="n">
-        <v>-61.57264829834256</v>
+        <v>-71.19378082443085</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.31188814729271</v>
+        <v>-41.49919265208374</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.29024543403181</v>
+        <v>-34.9818693899531</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.930223387638543</v>
+        <v>-14.73167875773812</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.86924869934482</v>
+        <v>-37.1033220192155</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.78842657875965</v>
+        <v>-35.15409861846562</v>
       </c>
       <c r="F9" t="n">
-        <v>-65.28308414315696</v>
+        <v>-55.77299666789084</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.9335909687273</v>
+        <v>-70.6288314669693</v>
       </c>
       <c r="H9" t="n">
-        <v>-38.18246986860984</v>
+        <v>-41.39546615337208</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7357564678921553</v>
+        <v>0.9305116344993817</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6627625320878658</v>
+        <v>0.9318071330970025</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5685176010955908</v>
+        <v>0.5707812894133408</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.363242407804699</v>
+        <v>0.6136212684351214</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.669245738870557</v>
+        <v>-0.1367113067394219</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.48413452831864</v>
+        <v>-0.9410460564586678</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.247276546011586</v>
+        <v>0.3281606603744595</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1826264781796371</v>
+        <v>0.04201426292594349</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3227991830880492</v>
+        <v>0.0874070210084671</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02789056637944888</v>
+        <v>0.01757079972689395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03152371652821151</v>
+        <v>0.01094357227099465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05811909759847253</v>
+        <v>0.01955279776278124</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0731706611182343</v>
+        <v>0.01432123495757893</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1160216171486756</v>
+        <v>0.0319682814421099</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07421266838450323</v>
+        <v>0.002970991104380518</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2337124397052159</v>
+        <v>0.009584965373486317</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001196890790891104</v>
+        <v>0.0003275244865728595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001392213833277367</v>
+        <v>0.0002276202446233526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005615388171601199</v>
+        <v>0.0007712508960308392</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005678739506433128</v>
+        <v>0.0003512890903502264</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05363472339865365</v>
+        <v>0.002372273532574019</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2724200219963709</v>
+        <v>0.05450679869869921</v>
       </c>
       <c r="C5" t="n">
-        <v>0.48343814465267</v>
+        <v>0.09790283639142595</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0345961094762273</v>
+        <v>0.01809763759646157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03731238176902363</v>
+        <v>0.01508708867288029</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0749358937465965</v>
+        <v>0.0277714042862589</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07535741175513612</v>
+        <v>0.01874270765791929</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1630099938993374</v>
+        <v>0.03868474555060754</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.53185376015702</v>
+        <v>50.28205410043235</v>
       </c>
       <c r="C6" t="n">
-        <v>73.1473930013597</v>
+        <v>47.35283875752297</v>
       </c>
       <c r="D6" t="n">
-        <v>78.62185581850757</v>
+        <v>34.51451942400236</v>
       </c>
       <c r="E6" t="n">
-        <v>85.41983395130042</v>
+        <v>29.22344386457556</v>
       </c>
       <c r="F6" t="n">
-        <v>1240.984159576235</v>
+        <v>463.2568116597662</v>
       </c>
       <c r="G6" t="n">
-        <v>1027.327328981727</v>
+        <v>148.2654199512374</v>
       </c>
       <c r="H6" t="n">
-        <v>427.8387375148811</v>
+        <v>128.8158479595895</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.149351616473598</v>
+        <v>0.02392620342325186</v>
       </c>
       <c r="C7" t="n">
-        <v>1.328854934840022</v>
+        <v>0.02816733583233968</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9467862077646022</v>
+        <v>0.1299948803165988</v>
       </c>
       <c r="E7" t="n">
-        <v>1.423894544049408</v>
+        <v>0.1170729536406999</v>
       </c>
       <c r="F7" t="n">
-        <v>4.013408986762576</v>
+        <v>0.6851065352980964</v>
       </c>
       <c r="G7" t="n">
-        <v>10.50243095230019</v>
+        <v>1.167119438601691</v>
       </c>
       <c r="H7" t="n">
-        <v>3.227454540365067</v>
+        <v>0.358564557852113</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-15.40738369393503</v>
+        <v>-48.36973708990483</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.7219828568665978</v>
+        <v>-23.88535709038525</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.36816855349085</v>
+        <v>-44.14368642513539</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.46116067804464</v>
+        <v>-46.32699146846299</v>
       </c>
       <c r="F8" t="n">
-        <v>-59.36917930595631</v>
+        <v>-82.00996185145952</v>
       </c>
       <c r="G8" t="n">
-        <v>-64.3943638426118</v>
+        <v>-99.40071370531753</v>
       </c>
       <c r="H8" t="n">
-        <v>-33.9537064884842</v>
+        <v>-57.35607460511091</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-14.61848538459015</v>
+        <v>-47.97528793523239</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.554944979954378</v>
+        <v>-24.30183815192914</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.20113067657863</v>
+        <v>-44.56016748667928</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.29412280113242</v>
+        <v>-46.74347253000688</v>
       </c>
       <c r="F9" t="n">
-        <v>-57.10938187611016</v>
+        <v>-81.04014855188352</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.83813452415076</v>
+        <v>-98.27081499039446</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.43603337375274</v>
+        <v>-57.14862160768761</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5082193055443167</v>
+        <v>0.9349544316290622</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1216574554095637</v>
+        <v>0.9382522518947246</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2759300076736511</v>
+        <v>0.4535346164079856</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.209859359086119</v>
+        <v>0.5562906311188368</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8928967140939887</v>
+        <v>-0.1095231798463383</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.129162018098078</v>
+        <v>-0.7975777403992073</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6896208099842863</v>
+        <v>0.3293218351341773</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2355695798598767</v>
+        <v>0.04298524271274561</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2799689147592905</v>
+        <v>0.08146437604460501</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02621623002364936</v>
+        <v>0.01964921401848696</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02873398744113524</v>
+        <v>0.01174356471282706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03033442831312958</v>
+        <v>0.01922773886716817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02350654213047237</v>
+        <v>0.01359960227481059</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1040549470879256</v>
+        <v>0.03144495643844056</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0644842644944247</v>
+        <v>0.002781038287736261</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1576564875371278</v>
+        <v>0.0086790606460601</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000973625590774062</v>
+        <v>0.0004169920597035087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001301854079444653</v>
+        <v>0.0002613943957974945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001593785899421102</v>
+        <v>0.0007528039367163949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006915387460664413</v>
+        <v>0.0003253242998317796</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03778359272454313</v>
+        <v>0.002202768937640924</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2539375208479926</v>
+        <v>0.05273555051136056</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3970598034769168</v>
+        <v>0.0931614761908596</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03120297406937457</v>
+        <v>0.02042038343674057</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03608121504944994</v>
+        <v>0.01616769605718435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03992224817593696</v>
+        <v>0.02743727276382248</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02629712429271386</v>
+        <v>0.0180367485936845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1307501476520641</v>
+        <v>0.03799318792560868</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>286.5927001638634</v>
+        <v>48.96820168951784</v>
       </c>
       <c r="C6" t="n">
-        <v>62.07373868682902</v>
+        <v>47.20251209574641</v>
       </c>
       <c r="D6" t="n">
-        <v>71.32315005261397</v>
+        <v>38.61215150936788</v>
       </c>
       <c r="E6" t="n">
-        <v>90.02922149454801</v>
+        <v>29.51327909798106</v>
       </c>
       <c r="F6" t="n">
-        <v>960.4154476808139</v>
+        <v>480.5440569645891</v>
       </c>
       <c r="G6" t="n">
-        <v>362.5191023524281</v>
+        <v>127.1332683605082</v>
       </c>
       <c r="H6" t="n">
-        <v>305.4922267385161</v>
+        <v>128.6622449529517</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9972095536187847</v>
+        <v>0.02296039731269672</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8957135557977172</v>
+        <v>0.02609966688382469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7689210804312745</v>
+        <v>0.1657315095193968</v>
       </c>
       <c r="E7" t="n">
-        <v>1.329738211162894</v>
+        <v>0.1347957867414072</v>
       </c>
       <c r="F7" t="n">
-        <v>1.139969328715583</v>
+        <v>0.669767833419206</v>
       </c>
       <c r="G7" t="n">
-        <v>1.28046536510334</v>
+        <v>1.082002098259289</v>
       </c>
       <c r="H7" t="n">
-        <v>1.068669515804932</v>
+        <v>0.3502262153559701</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-20.67200641643508</v>
+        <v>-46.96437842589415</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.084020453906616</v>
+        <v>-22.48105185999676</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.60690239167911</v>
+        <v>-40.69466026695096</v>
       </c>
       <c r="E8" t="n">
-        <v>-35.86379489381474</v>
+        <v>-43.49688117712344</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.74135931439537</v>
+        <v>-80.30046888329755</v>
       </c>
       <c r="G8" t="n">
-        <v>-97.87227927125497</v>
+        <v>-98.39894435769907</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.47339379024765</v>
+        <v>-55.38939749516032</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-20.27755726176264</v>
+        <v>-46.37270469388549</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.500501515450506</v>
+        <v>-23.1057734523126</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.023383453223</v>
+        <v>-41.3193818592668</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.28027595535863</v>
+        <v>-44.12160276943928</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.6114605994723</v>
+        <v>-78.84574893393355</v>
       </c>
       <c r="G9" t="n">
-        <v>-96.59416461202446</v>
+        <v>-96.70409628531445</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.21455723288193</v>
+        <v>-55.07821799902536</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7357564678921553</v>
+        <v>0.9302684795781531</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6627625320878658</v>
+        <v>0.9340865940854675</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.929666722701176</v>
+        <v>0.5704895144801678</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4012306937912842</v>
+        <v>0.6220289895208266</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.610918417216643</v>
+        <v>-0.1244988094582515</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.48413452831864</v>
+        <v>-0.9002214140813318</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.804078227001295</v>
+        <v>0.3386922256875053</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1826264781796371</v>
+        <v>0.04223391607866176</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3227991830880492</v>
+        <v>0.08518594336635876</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0411100294193596</v>
+        <v>0.01759046177895965</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02478182007251997</v>
+        <v>0.01084600262090946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08012806233132651</v>
+        <v>0.01949478661460031</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0731706611182343</v>
+        <v>0.01405217400445131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1207693723681878</v>
+        <v>0.03156721407732354</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07421266838450323</v>
+        <v>0.002981387249156007</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2337124397052159</v>
+        <v>0.009264571824469983</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002235544643127957</v>
+        <v>0.0003277471316552504</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008254814440814172</v>
+        <v>0.0002226671574735964</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008092225074825652</v>
+        <v>0.000762964799627088</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005678739506433128</v>
+        <v>0.0003439006765426878</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05412618312636455</v>
+        <v>0.002317206473154102</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2724200219963709</v>
+        <v>0.05460208099657015</v>
       </c>
       <c r="C5" t="n">
-        <v>0.48343814465267</v>
+        <v>0.0962526458050374</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04728154653908813</v>
+        <v>0.01810378777094038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02873119287606098</v>
+        <v>0.01492203596945123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08995679560114206</v>
+        <v>0.02762181745698657</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07535741175513612</v>
+        <v>0.01854455921672683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1661975189034114</v>
+        <v>0.0383411545359521</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.53185376015702</v>
+        <v>50.28131805146266</v>
       </c>
       <c r="C6" t="n">
-        <v>73.1473930013597</v>
+        <v>47.44876650029125</v>
       </c>
       <c r="D6" t="n">
-        <v>96.1661937470933</v>
+        <v>34.66348467098185</v>
       </c>
       <c r="E6" t="n">
-        <v>56.01108813212541</v>
+        <v>28.83418742866849</v>
       </c>
       <c r="F6" t="n">
-        <v>2298.882399550662</v>
+        <v>491.5924238218593</v>
       </c>
       <c r="G6" t="n">
-        <v>1027.327328981727</v>
+        <v>143.9008338647275</v>
       </c>
       <c r="H6" t="n">
-        <v>602.1777095288541</v>
+        <v>132.7868357229985</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.150351616473598</v>
+        <v>0.02400642720096329</v>
       </c>
       <c r="C7" t="n">
-        <v>1.329854934840022</v>
+        <v>0.02725922205148875</v>
       </c>
       <c r="D7" t="n">
-        <v>1.765929796121085</v>
+        <v>0.1300825686481083</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8468940902964847</v>
+        <v>0.1145471701539835</v>
       </c>
       <c r="F7" t="n">
-        <v>5.782880165434743</v>
+        <v>0.6777674363944289</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5034309523002</v>
+        <v>1.142614309395959</v>
       </c>
       <c r="H7" t="n">
-        <v>3.563223592577688</v>
+        <v>0.3527128556408219</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-13.40738369393503</v>
+        <v>-48.33829910241109</v>
       </c>
       <c r="C8" t="n">
-        <v>1.278017143133402</v>
+        <v>-24.08934580770261</v>
       </c>
       <c r="D8" t="n">
-        <v>-26.61962235441994</v>
+        <v>-44.13960912189626</v>
       </c>
       <c r="E8" t="n">
-        <v>-32.59726263953592</v>
+        <v>-46.45899481325257</v>
       </c>
       <c r="F8" t="n">
-        <v>-52.61907009249896</v>
+        <v>-82.13958394298727</v>
       </c>
       <c r="G8" t="n">
-        <v>-62.3943638426118</v>
+        <v>-99.67704975240923</v>
       </c>
       <c r="H8" t="n">
-        <v>-31.05994757997804</v>
+        <v>-57.4738137567765</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-12.42126080725393</v>
+        <v>-47.94384994773865</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2368144892736765</v>
+        <v>-24.5058268692465</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.66082500827967</v>
+        <v>-44.55609018344015</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.63846529339565</v>
+        <v>-46.87547587479646</v>
       </c>
       <c r="F9" t="n">
-        <v>-49.79432330519128</v>
+        <v>-81.16977064341127</v>
       </c>
       <c r="G9" t="n">
-        <v>-59.1990771945355</v>
+        <v>-98.54715103748616</v>
       </c>
       <c r="H9" t="n">
-        <v>-30.41285618656373</v>
+        <v>-57.2663607593532</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.585942499818243</v>
+        <v>0.2704896952585615</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6421595913397733</v>
+        <v>0.4514596285092943</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.914636249697871</v>
+        <v>-3.147039912825206</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.855874078244574</v>
+        <v>-1.552010063934912</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.03461459980641401</v>
+        <v>-1.394589203688072</v>
       </c>
       <c r="G2" t="n">
-        <v>-6.008922653784118</v>
+        <v>-3.866687657169492</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.340358278781832</v>
+        <v>-1.539729585641638</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2395520432269244</v>
+        <v>0.1281459117648756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3217474673273396</v>
+        <v>0.2024270936061401</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03726782804328437</v>
+        <v>0.04819937066364175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07624774803697025</v>
+        <v>0.030459938670961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02671906521579672</v>
+        <v>0.03703434378339702</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03877022768963296</v>
+        <v>0.0274841891893207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.123384063256658</v>
+        <v>0.07895847461305604</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1105625683961606</v>
+        <v>0.03119038144481107</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2308165580297415</v>
+        <v>0.07710103278363008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00222407532030504</v>
+        <v>0.003164487206041778</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006395322804861538</v>
+        <v>0.001503419074547541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008711273828249631</v>
+        <v>0.001624712500017001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002276455028821236</v>
+        <v>0.0008807695594945558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05885768449378581</v>
+        <v>0.01924413376142367</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.332509501211861</v>
+        <v>0.1766079880549322</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4804337186644392</v>
+        <v>0.2776707272717635</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04716010305655661</v>
+        <v>0.05625377503814102</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07997076218757414</v>
+        <v>0.03877394840027954</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02951486714903123</v>
+        <v>0.04030772258534339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04771221047930222</v>
+        <v>0.02967776203649048</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1695501937914607</v>
+        <v>0.1032153205644917</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246.6602240467429</v>
+        <v>64.05577820337528</v>
       </c>
       <c r="C6" t="n">
-        <v>72.44967579328173</v>
+        <v>56.80321053976497</v>
       </c>
       <c r="D6" t="n">
-        <v>107.6813136949151</v>
+        <v>100.7165743493346</v>
       </c>
       <c r="E6" t="n">
-        <v>220.5157318104225</v>
+        <v>125.675885471314</v>
       </c>
       <c r="F6" t="n">
-        <v>1758.61924820668</v>
+        <v>2264.683196871958</v>
       </c>
       <c r="G6" t="n">
-        <v>434.9881056529599</v>
+        <v>413.4210732300234</v>
       </c>
       <c r="H6" t="n">
-        <v>473.4857165341671</v>
+        <v>504.2259531109617</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.71135309564557</v>
+        <v>0.2411863584337993</v>
       </c>
       <c r="C7" t="n">
-        <v>1.313438936045502</v>
+        <v>0.2190328343957528</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75689545526715</v>
+        <v>2.493654229783582</v>
       </c>
       <c r="E7" t="n">
-        <v>6.527477898873551</v>
+        <v>1.534310825065314</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6269883382198035</v>
+        <v>1.440028119712867</v>
       </c>
       <c r="G7" t="n">
-        <v>4.213540629310821</v>
+        <v>2.922245671684988</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6916157255604</v>
+        <v>1.47507633984605</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-9.819563195981992</v>
+        <v>-29.2088096684998</v>
       </c>
       <c r="C8" t="n">
-        <v>1.203207969850647</v>
+        <v>-13.37583161874849</v>
       </c>
       <c r="D8" t="n">
-        <v>-26.65048421674186</v>
+        <v>-32.53458554032395</v>
       </c>
       <c r="E8" t="n">
-        <v>-20.31313020517983</v>
+        <v>-37.00008029016963</v>
       </c>
       <c r="F8" t="n">
-        <v>-81.59439045727288</v>
+        <v>-75.06909282303555</v>
       </c>
       <c r="G8" t="n">
-        <v>-75.19190201074986</v>
+        <v>-89.45128893183706</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.39437701934596</v>
+        <v>-46.10661481210241</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-8.833440309300894</v>
+        <v>-29.01158509116359</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1620053159909212</v>
+        <v>-13.58407214952044</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.69168687060159</v>
+        <v>-32.74282607109589</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.35433285903956</v>
+        <v>-37.20832082094158</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.76964366996519</v>
+        <v>-74.58418617324755</v>
       </c>
       <c r="G9" t="n">
-        <v>-71.99661536267357</v>
+        <v>-88.88633957437551</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.74728562593165</v>
+        <v>-46.00288831339075</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1197259009980576</v>
+        <v>0.9284528651496975</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1204340204955177</v>
+        <v>0.9448334609450085</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.306133932570119</v>
+        <v>0.7053282012794257</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.7422684583095</v>
+        <v>0.7574862104738728</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8705903152851102</v>
+        <v>-0.3263464959744331</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.857033402197152</v>
+        <v>-1.399003327951846</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.462789037976556</v>
+        <v>0.2684584856536209</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1571928659932406</v>
+        <v>0.04842492317623772</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2682220506315554</v>
+        <v>0.07164682187830403</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03993345347207895</v>
+        <v>0.01375332140142398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03807227550923062</v>
+        <v>0.009034231243831308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03715560521097146</v>
+        <v>0.02141981679178479</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04781208982836077</v>
+        <v>0.01612294630532499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09806472344090629</v>
+        <v>0.0300670101328178</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03763632226358923</v>
+        <v>0.003059014263075027</v>
       </c>
       <c r="C4" t="n">
-        <v>0.157484525544321</v>
+        <v>0.007754027519760006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003285887289142872</v>
+        <v>0.0002248555973982203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002204614261444235</v>
+        <v>0.0001428677191234173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001575004302082089</v>
+        <v>0.000899917083082331</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002876710048723902</v>
+        <v>0.0004341698611525528</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03417717728488389</v>
+        <v>0.002085808673931926</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1940008305744829</v>
+        <v>0.05530835617766114</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3968432001991731</v>
+        <v>0.08805695611228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05732265947374451</v>
+        <v>0.01499518580739233</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04695332002578981</v>
+        <v>0.0119527285221165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0396863238670715</v>
+        <v>0.02999861801954102</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05363497038988557</v>
+        <v>0.02083674305529904</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1314068840883579</v>
+        <v>0.03685809794904834</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.7344933817658</v>
+        <v>46.67534261794331</v>
       </c>
       <c r="C6" t="n">
-        <v>52.88546784932988</v>
+        <v>50.42347147818804</v>
       </c>
       <c r="D6" t="n">
-        <v>54.59153901381237</v>
+        <v>27.9512912338138</v>
       </c>
       <c r="E6" t="n">
-        <v>133.3094830403781</v>
+        <v>26.50031550498713</v>
       </c>
       <c r="F6" t="n">
-        <v>1918.521247980415</v>
+        <v>398.2700340707031</v>
       </c>
       <c r="G6" t="n">
-        <v>686.4903701973701</v>
+        <v>181.5602017431101</v>
       </c>
       <c r="H6" t="n">
-        <v>494.9221002438451</v>
+        <v>121.8967761081243</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2914276552850952</v>
+        <v>0.02510545043924328</v>
       </c>
       <c r="C7" t="n">
-        <v>0.89473874805936</v>
+        <v>0.02347778098032945</v>
       </c>
       <c r="D7" t="n">
-        <v>2.590280601746872</v>
+        <v>0.09005893853435105</v>
       </c>
       <c r="E7" t="n">
-        <v>2.250447534951722</v>
+        <v>0.07435414426122458</v>
       </c>
       <c r="F7" t="n">
-        <v>1.126559195193981</v>
+        <v>0.8000677815009752</v>
       </c>
       <c r="G7" t="n">
-        <v>5.320247435386505</v>
+        <v>1.443009834576721</v>
       </c>
       <c r="H7" t="n">
-        <v>2.078950195103923</v>
+        <v>0.4093456550488075</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-25.51807109509171</v>
+        <v>-46.1069629604838</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.090568456333568</v>
+        <v>-23.15725734380831</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.30871136166222</v>
+        <v>-44.40031290681621</v>
       </c>
       <c r="E8" t="n">
-        <v>-32.70321634104388</v>
+        <v>-47.12154838148341</v>
       </c>
       <c r="F8" t="n">
-        <v>-79.89546457795853</v>
+        <v>-78.15849514551246</v>
       </c>
       <c r="G8" t="n">
-        <v>-77.91551174799758</v>
+        <v>-94.64697129878202</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.23859059668125</v>
+        <v>-55.59859133948103</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-25.12362194041927</v>
+        <v>-45.51528922847514</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.507049517877458</v>
+        <v>-23.78197893612415</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.72519242320611</v>
+        <v>-45.02503449913205</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.11969740258778</v>
+        <v>-47.74626997379924</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.76556586303546</v>
+        <v>-76.70377519614846</v>
       </c>
       <c r="G9" t="n">
-        <v>-76.63739708876707</v>
+        <v>-92.9521232263974</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.97975403931552</v>
+        <v>-55.28741184334607</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.241075260050521</v>
+        <v>0.8522492639478814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4774781494814297</v>
+        <v>0.809611520842735</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.659736686411827</v>
+        <v>0.1309503972227823</v>
       </c>
       <c r="E2" t="n">
-        <v>-39.049479540219</v>
+        <v>0.7006189026780063</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.332997404382326</v>
+        <v>0.2758830816062997</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.401768248918339</v>
+        <v>-0.2719645224067939</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.867929831750097</v>
+        <v>0.4162247739818185</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1499943537392076</v>
+        <v>0.05063601419052546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.216853368971591</v>
+        <v>0.1339249953933344</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04864512500391807</v>
+        <v>0.02285560528750792</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1534831188964386</v>
+        <v>0.01103209755484904</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04088271297968599</v>
+        <v>0.01549202128291841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01673577234592554</v>
+        <v>0.01216321960075562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1044324086561278</v>
+        <v>0.04101732555164848</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05306245917446464</v>
+        <v>0.006317116819687066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07344395494084059</v>
+        <v>0.02676037924654097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003555711408050596</v>
+        <v>0.0006631468245336149</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02359361834711103</v>
+        <v>0.0001763689174402639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002806325472678654</v>
+        <v>0.0004913084077118762</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001104873433430399</v>
+        <v>0.0002301992054991496</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02626115712942931</v>
+        <v>0.00577308657023549</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2303529013806092</v>
+        <v>0.07948029202064538</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2710054518655309</v>
+        <v>0.163585999543179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05962978624857376</v>
+        <v>0.02575163731753022</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1536021430420521</v>
+        <v>0.01328039598205806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05297476260143743</v>
+        <v>0.02216547783630834</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03323963648162234</v>
+        <v>0.01517231707746545</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1334674469366376</v>
+        <v>0.05323935329619775</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.99242248337388</v>
+        <v>30.62458853041023</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0324114952438</v>
+        <v>45.02962239763533</v>
       </c>
       <c r="D6" t="n">
-        <v>110.8226286659933</v>
+        <v>38.68273320433253</v>
       </c>
       <c r="E6" t="n">
-        <v>475.845602167809</v>
+        <v>27.90260842166132</v>
       </c>
       <c r="F6" t="n">
-        <v>410.4414765038554</v>
+        <v>399.1303423871526</v>
       </c>
       <c r="G6" t="n">
-        <v>76.46480831722235</v>
+        <v>156.1911446122074</v>
       </c>
       <c r="H6" t="n">
-        <v>204.599891605583</v>
+        <v>116.2601732588999</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8209325988745633</v>
+        <v>0.04974720258941655</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2091673236141595</v>
+        <v>0.07684880921975819</v>
       </c>
       <c r="D7" t="n">
-        <v>2.802820007818367</v>
+        <v>0.2621790836103389</v>
       </c>
       <c r="E7" t="n">
-        <v>24.06471878981736</v>
+        <v>0.09093778743880632</v>
       </c>
       <c r="F7" t="n">
-        <v>2.005727298291146</v>
+        <v>0.2185789914035084</v>
       </c>
       <c r="G7" t="n">
-        <v>2.044607772157806</v>
+        <v>0.7655009923317753</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3246622984289</v>
+        <v>0.2439654777656006</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-22.42657025867023</v>
+        <v>-41.58043136897528</v>
       </c>
       <c r="C8" t="n">
-        <v>-11.66739608863769</v>
+        <v>-17.72499723007848</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.83520072579036</v>
+        <v>-39.91108482496445</v>
       </c>
       <c r="E8" t="n">
-        <v>-18.48067407523042</v>
+        <v>-47.85759580942803</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.38643106041515</v>
+        <v>-87.42126206891342</v>
       </c>
       <c r="G8" t="n">
-        <v>-91.31234286636447</v>
+        <v>-104.8953516694263</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.01810251251806</v>
+        <v>-56.56512049529766</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.03212110399779</v>
+        <v>-41.18598221430284</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.08387715018157</v>
+        <v>-18.14147829162237</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.25168178733425</v>
+        <v>-40.32756588650834</v>
       </c>
       <c r="E9" t="n">
-        <v>-18.89715513677431</v>
+        <v>-48.27407687097192</v>
       </c>
       <c r="F9" t="n">
-        <v>-71.25653234549208</v>
+        <v>-86.45144876933742</v>
       </c>
       <c r="G9" t="n">
-        <v>-90.03422820713396</v>
+        <v>-103.7654529545033</v>
       </c>
       <c r="H9" t="n">
-        <v>-40.75926595515232</v>
+        <v>-56.35766749787436</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1713139368472347</v>
+        <v>0.3480532912462272</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4184761049847014</v>
+        <v>-0.2132636410766668</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.404745568787067</v>
+        <v>-2.205656322986426</v>
       </c>
       <c r="E2" t="n">
-        <v>-34.23888648697653</v>
+        <v>-7.793636259727542</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7583459306042888</v>
+        <v>0.2631707070295851</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.300806958841838</v>
+        <v>-5.718973675322125</v>
       </c>
       <c r="H2" t="n">
-        <v>-8.324991185557865</v>
+        <v>-2.553384316806158</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1610752851602301</v>
+        <v>0.1397241396086451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2943996746126746</v>
+        <v>0.2968477070975669</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07387260299337246</v>
+        <v>0.0376946800061283</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1435825820567276</v>
+        <v>0.07152480074250341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03237178108220377</v>
+        <v>0.01992660810786835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02921248230169585</v>
+        <v>0.03319766965881988</v>
       </c>
       <c r="H3" t="n">
-        <v>0.122419068034484</v>
+        <v>0.099819267536922</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03543066388471997</v>
+        <v>0.02787413199725327</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1993763419381693</v>
+        <v>0.1705323520885527</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00641342026639521</v>
+        <v>0.00244614439077019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0207596415308209</v>
+        <v>0.005180434307191849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001480496494941055</v>
+        <v>0.0004999336674632673</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002696051116290696</v>
+        <v>0.001215994923272078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04435943587188951</v>
+        <v>0.03462483189575054</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1882303479376266</v>
+        <v>0.1669554790872503</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4465157801670276</v>
+        <v>0.4129556296850216</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08008383274041778</v>
+        <v>0.04945851181313678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1440820652642823</v>
+        <v>0.07197523398497464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03847722046797371</v>
+        <v>0.02235919648518853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05192351217214313</v>
+        <v>0.03487111875567055</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1582187931249119</v>
+        <v>0.1264291949685404</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.1136909383512</v>
+        <v>73.00923238164275</v>
       </c>
       <c r="C6" t="n">
-        <v>58.71925358545463</v>
+        <v>86.06422743285805</v>
       </c>
       <c r="D6" t="n">
-        <v>135.2382552682407</v>
+        <v>50.3295594138931</v>
       </c>
       <c r="E6" t="n">
-        <v>434.9273033496682</v>
+        <v>208.8792291887194</v>
       </c>
       <c r="F6" t="n">
-        <v>1265.704914801616</v>
+        <v>1548.130758259048</v>
       </c>
       <c r="G6" t="n">
-        <v>149.7882286838346</v>
+        <v>509.1357703951458</v>
       </c>
       <c r="H6" t="n">
-        <v>363.0819411045275</v>
+        <v>412.5914628452178</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2744072836651336</v>
+        <v>0.2160959050242092</v>
       </c>
       <c r="C7" t="n">
-        <v>1.132212541704258</v>
+        <v>0.968703477569974</v>
       </c>
       <c r="D7" t="n">
-        <v>5.053826129645194</v>
+        <v>1.928818395938934</v>
       </c>
       <c r="E7" t="n">
-        <v>21.17439539032907</v>
+        <v>5.285434363866594</v>
       </c>
       <c r="F7" t="n">
-        <v>1.059080253455491</v>
+        <v>0.2223987414583488</v>
       </c>
       <c r="G7" t="n">
-        <v>4.986258646867911</v>
+        <v>4.035086598085856</v>
       </c>
       <c r="H7" t="n">
-        <v>5.613363374277843</v>
+        <v>2.109422913657319</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-26.06159860118833</v>
+        <v>-28.22050569918809</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.675366448447914</v>
+        <v>-6.612981511631265</v>
       </c>
       <c r="D8" t="n">
-        <v>-26.29617540471996</v>
+        <v>-32.07945327244056</v>
       </c>
       <c r="E8" t="n">
-        <v>-19.24846692881017</v>
+        <v>-27.57719829882891</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.69991111281279</v>
+        <v>-87.21242160099604</v>
       </c>
       <c r="G8" t="n">
-        <v>-78.82353976488673</v>
+        <v>-83.25850471503882</v>
       </c>
       <c r="H8" t="n">
-        <v>-39.46750971014432</v>
+        <v>-44.16017751635395</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-25.66714944651589</v>
+        <v>-27.82605654451565</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.091847509991804</v>
+        <v>-7.029462573175155</v>
       </c>
       <c r="D9" t="n">
-        <v>-26.71265646626386</v>
+        <v>-32.49593433398445</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.66494799035406</v>
+        <v>-27.9936793603728</v>
       </c>
       <c r="F9" t="n">
-        <v>-79.57001239788971</v>
+        <v>-86.24260830142003</v>
       </c>
       <c r="G9" t="n">
-        <v>-77.54542510565622</v>
+        <v>-82.12860600011575</v>
       </c>
       <c r="H9" t="n">
-        <v>-39.20867315277859</v>
+        <v>-43.95272451893064</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1106868443557812</v>
+        <v>0.9275111181595805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1816805202346378</v>
+        <v>0.5788632556129019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1939863666731814</v>
+        <v>-5.283736586439407</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.013705180390188</v>
+        <v>-3.286718821732013</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2230199780537203</v>
+        <v>0.3124070951458252</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4007250821427966</v>
+        <v>-1.410536700666531</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2565115404449113</v>
+        <v>-1.360368439986607</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1479450845877643</v>
+        <v>0.04820945988894363</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2798189668981919</v>
+        <v>0.1841896676640685</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02425931294058893</v>
+        <v>0.0589585404926166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02806698321238466</v>
+        <v>0.04305483727682308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02550186817953367</v>
+        <v>0.01859118280720281</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01502357160269399</v>
+        <v>0.01632468861341083</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08676929790352622</v>
+        <v>0.06155472945717758</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03802278921647727</v>
+        <v>0.00309927887298573</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1150202980783546</v>
+        <v>0.05919359745052249</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009110967487533906</v>
+        <v>0.004794939149832645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00118629735105583</v>
+        <v>0.002525356359244451</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001029761413403531</v>
+        <v>0.0004665271127586282</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004549469033615938</v>
+        <v>0.0004362571624796546</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02610419828523436</v>
+        <v>0.01175265935130393</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1949943312419037</v>
+        <v>0.05567116733988726</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3391464257195623</v>
+        <v>0.2432973436980406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03018437921762498</v>
+        <v>0.06924549913050411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03444266759494436</v>
+        <v>0.05025292388751575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03208989581478149</v>
+        <v>0.02159923870784867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0213294843669882</v>
+        <v>0.02088677003463328</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1086978639926342</v>
+        <v>0.07682549046640495</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89.70501787635182</v>
+        <v>33.04490160227337</v>
       </c>
       <c r="C6" t="n">
-        <v>73.94685263136252</v>
+        <v>45.86809328673292</v>
       </c>
       <c r="D6" t="n">
-        <v>43.08641162352664</v>
+        <v>161.286453775993</v>
       </c>
       <c r="E6" t="n">
-        <v>69.49607531259664</v>
+        <v>98.15921919181805</v>
       </c>
       <c r="F6" t="n">
-        <v>652.1617290519558</v>
+        <v>625.1855894472036</v>
       </c>
       <c r="G6" t="n">
-        <v>66.71228891265535</v>
+        <v>121.4365682159989</v>
       </c>
       <c r="H6" t="n">
-        <v>165.8513959014082</v>
+        <v>180.83013758667</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2944098991447998</v>
+        <v>0.02491615976321585</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3270100525844569</v>
+        <v>0.1687765415314952</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7196673554521636</v>
+        <v>3.778954866673411</v>
       </c>
       <c r="E7" t="n">
-        <v>1.211883924525591</v>
+        <v>2.57756679194215</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7372536528109972</v>
+        <v>0.2076044404351835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8430719749503842</v>
+        <v>1.448932780427391</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6888828099113988</v>
+        <v>1.367791930128808</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-25.42612624511516</v>
+        <v>-47.98927234552233</v>
       </c>
       <c r="C8" t="n">
-        <v>-8.975879966989382</v>
+        <v>-12.96165136468726</v>
       </c>
       <c r="D8" t="n">
-        <v>-38.00516879441449</v>
+        <v>-28.04116556638735</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.42150975347592</v>
+        <v>-31.88823856303407</v>
       </c>
       <c r="F8" t="n">
-        <v>-85.41956583358494</v>
+        <v>-88.04233303808346</v>
       </c>
       <c r="G8" t="n">
-        <v>-103.7346177842397</v>
+        <v>-96.58462266178228</v>
       </c>
       <c r="H8" t="n">
-        <v>-49.66381139630326</v>
+        <v>-50.91788058991612</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-25.03167709044272</v>
+        <v>-47.59482319084989</v>
       </c>
       <c r="C9" t="n">
-        <v>-9.392361028533273</v>
+        <v>-13.37813242623115</v>
       </c>
       <c r="D9" t="n">
-        <v>-38.42164985595838</v>
+        <v>-28.45764662793124</v>
       </c>
       <c r="E9" t="n">
-        <v>-36.83799081501981</v>
+        <v>-32.30471962457796</v>
       </c>
       <c r="F9" t="n">
-        <v>-84.28966711866187</v>
+        <v>-87.07251973850745</v>
       </c>
       <c r="G9" t="n">
-        <v>-102.4565031250092</v>
+        <v>-95.4547239468592</v>
       </c>
       <c r="H9" t="n">
-        <v>-49.40497483893754</v>
+        <v>-50.71042759249281</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -480,25 +480,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.624218231661847</v>
+        <v>-1.29894043140919</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5469542506087026</v>
+        <v>-0.6445152268202234</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.005002847660437</v>
+        <v>-2.096026420606492</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.593949280898641</v>
+        <v>-0.1266733407463556</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.48234707606543</v>
+        <v>-20.58352047423328</v>
       </c>
       <c r="G2" t="n">
-        <v>-18.82288847642363</v>
+        <v>-65.46769535702806</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.288835866462932</v>
+        <v>-15.03622854180727</v>
       </c>
     </row>
     <row r="3">
@@ -508,25 +508,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1123789981191349</v>
+        <v>0.2737414210150456</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1878857632202878</v>
+        <v>0.3438914745051496</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02392587127281239</v>
+        <v>0.04308428810378647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03976094122229139</v>
+        <v>0.02150894833556069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08254573396227728</v>
+        <v>0.1066107620959036</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05503785470208666</v>
+        <v>0.1014876145845723</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08358919374981506</v>
+        <v>0.1483874181066697</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0160666362329547</v>
+        <v>0.1250629707051897</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06367862237992912</v>
+        <v>0.2721757140113919</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001529960162639556</v>
+        <v>0.002679878055502014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00211723769361955</v>
+        <v>0.0005748393772049627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007790694452010615</v>
+        <v>0.01466951111970525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003587531804217714</v>
+        <v>0.01228206138397601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01579511378756187</v>
+        <v>0.0712408291088283</v>
       </c>
     </row>
     <row r="5">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1267542355621882</v>
+        <v>0.3536424334058197</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2523462351213688</v>
+        <v>0.5217046233371829</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03911470519688927</v>
+        <v>0.05176753862703938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04601345122482718</v>
+        <v>0.02397580816583588</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08826491064976283</v>
+        <v>0.1211177572435407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05989600824944609</v>
+        <v>0.1108244620288139</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1020649243340804</v>
+        <v>0.1971721038013721</v>
       </c>
     </row>
     <row r="6">
@@ -592,25 +592,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.9134790190225</v>
+        <v>123.8311445963705</v>
       </c>
       <c r="C6" t="n">
-        <v>42.44813567373596</v>
+        <v>229.5471349007155</v>
       </c>
       <c r="D6" t="n">
-        <v>35.41622444215896</v>
+        <v>56.78494750349724</v>
       </c>
       <c r="E6" t="n">
-        <v>89.8255146214133</v>
+        <v>2088.532091162017</v>
       </c>
       <c r="F6" t="n">
-        <v>5329.458208604381</v>
+        <v>5152.8174208276</v>
       </c>
       <c r="G6" t="n">
-        <v>794.2028229569027</v>
+        <v>1301.108980628793</v>
       </c>
       <c r="H6" t="n">
-        <v>1062.044064219602</v>
+        <v>1492.103619936499</v>
       </c>
     </row>
     <row r="7">
@@ -620,25 +620,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1244811758645142</v>
+        <v>1.555452417832779</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1809887604833396</v>
+        <v>1.368755135708083</v>
       </c>
       <c r="D7" t="n">
-        <v>1.206143652823957</v>
+        <v>1.862367681641598</v>
       </c>
       <c r="E7" t="n">
-        <v>2.160333701310252</v>
+        <v>0.6778087795759005</v>
       </c>
       <c r="F7" t="n">
-        <v>6.901315217872075</v>
+        <v>12.97164960010756</v>
       </c>
       <c r="G7" t="n">
-        <v>11.89975563038009</v>
+        <v>39.8988121001544</v>
       </c>
       <c r="H7" t="n">
-        <v>3.745503023122371</v>
+        <v>9.72247428583672</v>
       </c>
     </row>
     <row r="8">
@@ -648,25 +648,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-35.17909396728932</v>
+        <v>-16.71044112597068</v>
       </c>
       <c r="C8" t="n">
-        <v>-14.52343822696617</v>
+        <v>-5.807844483185631</v>
       </c>
       <c r="D8" t="n">
-        <v>-36.89508148844356</v>
+        <v>-33.53190392303775</v>
       </c>
       <c r="E8" t="n">
-        <v>-34.94585808769368</v>
+        <v>-42.76851940109255</v>
       </c>
       <c r="F8" t="n">
-        <v>-56.25790331767885</v>
+        <v>-48.66380815067211</v>
       </c>
       <c r="G8" t="n">
-        <v>-71.19378082443085</v>
+        <v>-55.19500156768178</v>
       </c>
       <c r="H8" t="n">
-        <v>-41.49919265208374</v>
+        <v>-33.77958644194008</v>
       </c>
     </row>
     <row r="9">
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-34.9818693899531</v>
+        <v>-16.51321654863446</v>
       </c>
       <c r="C9" t="n">
-        <v>-14.73167875773812</v>
+        <v>-6.016085013957577</v>
       </c>
       <c r="D9" t="n">
-        <v>-37.1033220192155</v>
+        <v>-33.74014445380969</v>
       </c>
       <c r="E9" t="n">
-        <v>-35.15409861846562</v>
+        <v>-42.9767599318645</v>
       </c>
       <c r="F9" t="n">
-        <v>-55.77299666789084</v>
+        <v>-48.17890150088411</v>
       </c>
       <c r="G9" t="n">
-        <v>-70.6288314669693</v>
+        <v>-54.63005221022024</v>
       </c>
       <c r="H9" t="n">
-        <v>-41.39546615337208</v>
+        <v>-33.67585994322843</v>
       </c>
     </row>
   </sheetData>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9305116344993817</v>
+        <v>0.07490263824075372</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9318071330970025</v>
+        <v>0.09109400803846279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5707812894133408</v>
+        <v>0.02264830536052298</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6136212684351214</v>
+        <v>-0.1657552683024259</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1367113067394219</v>
+        <v>-2.080476074821755</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9410460564586678</v>
+        <v>-7.50564387360294</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3281606603744595</v>
+        <v>-1.593871710847897</v>
       </c>
     </row>
     <row r="3">
@@ -783,25 +783,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04201426292594349</v>
+        <v>0.1664985002022513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0874070210084671</v>
+        <v>0.336196275844845</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01757079972689395</v>
+        <v>0.0264700739202476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01094357227099465</v>
+        <v>0.02124005415456801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01955279776278124</v>
+        <v>0.04174990251607184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01432123495757893</v>
+        <v>0.02847886204808561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0319682814421099</v>
+        <v>0.1034389447810116</v>
       </c>
     </row>
     <row r="4">
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002970991104380518</v>
+        <v>0.05032554244227486</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009584965373486317</v>
+        <v>0.1504286085630799</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003275244865728595</v>
+        <v>0.0008459822375995611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002276202446233526</v>
+        <v>0.0005947793456801365</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007712508960308392</v>
+        <v>0.002093684303611688</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003512890903502264</v>
+        <v>0.001571693430992186</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002372273532574019</v>
+        <v>0.03431004838720638</v>
       </c>
     </row>
     <row r="5">
@@ -839,25 +839,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05450679869869921</v>
+        <v>0.2243335517533542</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09790283639142595</v>
+        <v>0.3878512711892019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01809763759646157</v>
+        <v>0.02908577380094195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01508708867288029</v>
+        <v>0.02438809844330091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0277714042862589</v>
+        <v>0.04575679516325076</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01874270765791929</v>
+        <v>0.03964458892449493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03868474555060754</v>
+        <v>0.1251766798790908</v>
       </c>
     </row>
     <row r="6">
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.28205410043235</v>
+        <v>88.43831628416771</v>
       </c>
       <c r="C6" t="n">
-        <v>47.35283875752297</v>
+        <v>1237.623560742922</v>
       </c>
       <c r="D6" t="n">
-        <v>34.51451942400236</v>
+        <v>54.51960005970727</v>
       </c>
       <c r="E6" t="n">
-        <v>29.22344386457556</v>
+        <v>1427.137976993833</v>
       </c>
       <c r="F6" t="n">
-        <v>463.2568116597662</v>
+        <v>1338.895222310429</v>
       </c>
       <c r="G6" t="n">
-        <v>148.2654199512374</v>
+        <v>164.8376028871751</v>
       </c>
       <c r="H6" t="n">
-        <v>128.8158479595895</v>
+        <v>718.5753798797056</v>
       </c>
     </row>
     <row r="7">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02392620342325186</v>
+        <v>0.3142570882373663</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02816733583233968</v>
+        <v>0.3794718235826171</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1299948803165988</v>
+        <v>0.2952976959581629</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1170729536406999</v>
+        <v>0.7032858520654079</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6851065352980964</v>
+        <v>1.854216802918109</v>
       </c>
       <c r="G7" t="n">
-        <v>1.167119438601691</v>
+        <v>5.108586694965154</v>
       </c>
       <c r="H7" t="n">
-        <v>0.358564557852113</v>
+        <v>1.442519326287803</v>
       </c>
     </row>
     <row r="8">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-48.36973708990483</v>
+        <v>-20.90318275857871</v>
       </c>
       <c r="C8" t="n">
-        <v>-23.88535709038525</v>
+        <v>-5.365600014272548</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.14368642513539</v>
+        <v>-36.45007316594199</v>
       </c>
       <c r="E8" t="n">
-        <v>-46.32699146846299</v>
+        <v>-38.56392041277618</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.00996185145952</v>
+        <v>-68.02595928315205</v>
       </c>
       <c r="G8" t="n">
-        <v>-99.40071370531753</v>
+        <v>-77.92282109180451</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.35607460511091</v>
+        <v>-41.205259454421</v>
       </c>
     </row>
     <row r="9">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.97528793523239</v>
+        <v>-20.31150902657005</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.30183815192914</v>
+        <v>-5.990321606588383</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.56016748667928</v>
+        <v>-37.07479475825782</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.74347253000688</v>
+        <v>-39.18864200509201</v>
       </c>
       <c r="F9" t="n">
-        <v>-81.04014855188352</v>
+        <v>-66.57123933378804</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.27081499039446</v>
+        <v>-76.22797301941989</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.14862160768761</v>
+        <v>-40.89407995828604</v>
       </c>
     </row>
   </sheetData>
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9349544316290622</v>
+        <v>0.07724293770988677</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9382522518947246</v>
+        <v>0.09378715147091765</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4535346164079856</v>
+        <v>0.02360424000232431</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5562906311188368</v>
+        <v>-0.1778018765083298</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1095231798463383</v>
+        <v>-2.080554952995329</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7975777403992073</v>
+        <v>-7.548292850120829</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3293218351341773</v>
+        <v>-1.602002558406893</v>
       </c>
     </row>
     <row r="3">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04298524271274561</v>
+        <v>0.1665576951637656</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08146437604460501</v>
+        <v>0.3368055325575863</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01964921401848696</v>
+        <v>0.0264687647539168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01174356471282706</v>
+        <v>0.02135168204080082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01922773886716817</v>
+        <v>0.04170001631342598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01359960227481059</v>
+        <v>0.02849444163028391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03144495643844056</v>
+        <v>0.1035630220766299</v>
       </c>
     </row>
     <row r="4">
@@ -1086,25 +1086,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002781038287736261</v>
+        <v>0.05019822952892106</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0086790606460601</v>
+        <v>0.149982879496721</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004169920597035087</v>
+        <v>0.0008451547936694943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002613943957974945</v>
+        <v>0.000600925638938417</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007528039367163949</v>
+        <v>0.002093737914154311</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003253242998317796</v>
+        <v>0.001579574211945141</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002202768937640924</v>
+        <v>0.03421675026405823</v>
       </c>
     </row>
     <row r="5">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05273555051136056</v>
+        <v>0.2240496139896721</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0931614761908596</v>
+        <v>0.3872762315153371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02042038343674057</v>
+        <v>0.02907154611763011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01616769605718435</v>
+        <v>0.02451378467186201</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02743727276382248</v>
+        <v>0.04575738098005951</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0180367485936845</v>
+        <v>0.03974385753729928</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03799318792560868</v>
+        <v>0.1250687358019767</v>
       </c>
     </row>
     <row r="6">
@@ -1142,25 +1142,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.96820168951784</v>
+        <v>89.01128493570441</v>
       </c>
       <c r="C6" t="n">
-        <v>47.20251209574641</v>
+        <v>1248.033529999147</v>
       </c>
       <c r="D6" t="n">
-        <v>38.61215150936788</v>
+        <v>54.4576940081414</v>
       </c>
       <c r="E6" t="n">
-        <v>29.51327909798106</v>
+        <v>1407.423829819705</v>
       </c>
       <c r="F6" t="n">
-        <v>480.5440569645891</v>
+        <v>1332.639610777331</v>
       </c>
       <c r="G6" t="n">
-        <v>127.1332683605082</v>
+        <v>163.8897448956658</v>
       </c>
       <c r="H6" t="n">
-        <v>128.6622449529517</v>
+        <v>715.9092824059493</v>
       </c>
     </row>
     <row r="7">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02296039731269672</v>
+        <v>0.3134658793572788</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02609966688382469</v>
+        <v>0.3783518702064294</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1657315095193968</v>
+        <v>0.2950103363548714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1347957867414072</v>
+        <v>0.7105224217995117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.669767833419206</v>
+        <v>1.854264204877014</v>
       </c>
       <c r="G7" t="n">
-        <v>1.082002098259289</v>
+        <v>5.134187113969221</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3502262153559701</v>
+        <v>1.447633637760721</v>
       </c>
     </row>
     <row r="8">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-46.96437842589415</v>
+        <v>-20.92597969129124</v>
       </c>
       <c r="C8" t="n">
-        <v>-22.48105185999676</v>
+        <v>-5.383404768530974</v>
       </c>
       <c r="D8" t="n">
-        <v>-40.69466026695096</v>
+        <v>-36.4559445576563</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.49688117712344</v>
+        <v>-38.50223615983165</v>
       </c>
       <c r="F8" t="n">
-        <v>-80.30046888329755</v>
+        <v>-68.0256520170212</v>
       </c>
       <c r="G8" t="n">
-        <v>-98.39894435769907</v>
+        <v>-77.85779940683391</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.38939749516032</v>
+        <v>-41.19183610019422</v>
       </c>
     </row>
     <row r="9">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-46.37270469388549</v>
+        <v>-20.33430595928258</v>
       </c>
       <c r="C9" t="n">
-        <v>-23.1057734523126</v>
+        <v>-6.008126360846809</v>
       </c>
       <c r="D9" t="n">
-        <v>-41.3193818592668</v>
+        <v>-37.08066614997213</v>
       </c>
       <c r="E9" t="n">
-        <v>-44.12160276943928</v>
+        <v>-39.12695775214749</v>
       </c>
       <c r="F9" t="n">
-        <v>-78.84574893393355</v>
+        <v>-66.5709320676572</v>
       </c>
       <c r="G9" t="n">
-        <v>-96.70409628531445</v>
+        <v>-76.16295133444929</v>
       </c>
       <c r="H9" t="n">
-        <v>-55.07821799902536</v>
+        <v>-40.88065660405925</v>
       </c>
     </row>
   </sheetData>
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9302684795781531</v>
+        <v>0.07681394918937634</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9340865940854675</v>
+        <v>0.09327100100325325</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5704895144801678</v>
+        <v>0.02349059364862516</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6220289895208266</v>
+        <v>-0.176095761204865</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1244988094582515</v>
+        <v>-2.080770910957538</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9002214140813318</v>
+        <v>-7.538663738995973</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3386922256875053</v>
+        <v>-1.60032581121952</v>
       </c>
     </row>
     <row r="3">
@@ -1333,25 +1333,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04223391607866176</v>
+        <v>0.1665477170167832</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08518594336635876</v>
+        <v>0.3366843584493939</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01759046177895965</v>
+        <v>0.0264689824488996</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01084600262090946</v>
+        <v>0.0213361225534304</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01949478661460031</v>
+        <v>0.04171194744682111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01405217400445131</v>
+        <v>0.02849199184876859</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03156721407732354</v>
+        <v>0.1035401866273495</v>
       </c>
     </row>
     <row r="4">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002981387249156007</v>
+        <v>0.05022156661849522</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009264571824469983</v>
+        <v>0.1500683050493597</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003277471316552504</v>
+        <v>0.0008452531643963521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002226671574735964</v>
+        <v>0.0006000551628003789</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000762964799627088</v>
+        <v>0.002093884692699164</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003439006765426878</v>
+        <v>0.001577794921520321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002317206473154102</v>
+        <v>0.03423447660154519</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05460208099657015</v>
+        <v>0.2241016881205834</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0962526458050374</v>
+        <v>0.3873865060238414</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01810378777094038</v>
+        <v>0.02907323794138438</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01492203596945123</v>
+        <v>0.02449602340789988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02762181745698657</v>
+        <v>0.04575898483029496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01854455921672683</v>
+        <v>0.03972146675942772</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0383411545359521</v>
+        <v>0.1250896511805719</v>
       </c>
     </row>
     <row r="6">
@@ -1417,25 +1417,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.28131805146266</v>
+        <v>88.90827074217678</v>
       </c>
       <c r="C6" t="n">
-        <v>47.44876650029125</v>
+        <v>1245.980446819429</v>
       </c>
       <c r="D6" t="n">
-        <v>34.66348467098185</v>
+        <v>54.46484945747167</v>
       </c>
       <c r="E6" t="n">
-        <v>28.83418742866849</v>
+        <v>1410.163688635652</v>
       </c>
       <c r="F6" t="n">
-        <v>491.5924238218593</v>
+        <v>1333.961002159054</v>
       </c>
       <c r="G6" t="n">
-        <v>143.9008338647275</v>
+        <v>164.129070611362</v>
       </c>
       <c r="H6" t="n">
-        <v>132.7868357229985</v>
+        <v>716.2678880708577</v>
       </c>
     </row>
     <row r="7">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02400642720096329</v>
+        <v>0.3136109118761338</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02725922205148875</v>
+        <v>0.3785665132335759</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1300825686481083</v>
+        <v>0.29504449912049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1145471701539835</v>
+        <v>0.7094975339508397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6777674363944289</v>
+        <v>1.854393985144302</v>
       </c>
       <c r="G7" t="n">
-        <v>1.142614309395959</v>
+        <v>5.128407156287714</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3527128556408219</v>
+        <v>1.446586766602176</v>
       </c>
     </row>
     <row r="8">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-48.33829910241109</v>
+        <v>-20.92179657565057</v>
       </c>
       <c r="C8" t="n">
-        <v>-24.08934580770261</v>
+        <v>-5.379988329229418</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.13960912189626</v>
+        <v>-36.45524623585889</v>
       </c>
       <c r="E8" t="n">
-        <v>-46.45899481325257</v>
+        <v>-38.51093381384121</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.13958394298727</v>
+        <v>-68.02481080342375</v>
       </c>
       <c r="G8" t="n">
-        <v>-99.67704975240923</v>
+        <v>-77.87245133823214</v>
       </c>
       <c r="H8" t="n">
-        <v>-57.4738137567765</v>
+        <v>-41.19420451603933</v>
       </c>
     </row>
     <row r="9">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.94384994773865</v>
+        <v>-20.33012284364191</v>
       </c>
       <c r="C9" t="n">
-        <v>-24.5058268692465</v>
+        <v>-6.004709921545253</v>
       </c>
       <c r="D9" t="n">
-        <v>-44.55609018344015</v>
+        <v>-37.07996782817472</v>
       </c>
       <c r="E9" t="n">
-        <v>-46.87547587479646</v>
+        <v>-39.13565540615705</v>
       </c>
       <c r="F9" t="n">
-        <v>-81.16977064341127</v>
+        <v>-66.57009085405974</v>
       </c>
       <c r="G9" t="n">
-        <v>-98.54715103748616</v>
+        <v>-76.17760326584752</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.2663607593532</v>
+        <v>-40.88302501990437</v>
       </c>
     </row>
   </sheetData>
@@ -1580,25 +1580,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2704896952585615</v>
+        <v>-0.9803498820168386</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4514596285092943</v>
+        <v>-0.7932255591562349</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.147039912825206</v>
+        <v>-1.706628208129578</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.552010063934912</v>
+        <v>-2.777785301881678</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.394589203688072</v>
+        <v>-0.2424479106722657</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.866687657169492</v>
+        <v>-12.97245887928303</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.539729585641638</v>
+        <v>-3.245482623523271</v>
       </c>
     </row>
     <row r="3">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1281459117648756</v>
+        <v>0.2227263347894996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2024270936061401</v>
+        <v>0.3719513405378985</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04819937066364175</v>
+        <v>0.03647494561362429</v>
       </c>
       <c r="E3" t="n">
-        <v>0.030459938670961</v>
+        <v>0.03120086499267109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03703434378339702</v>
+        <v>0.02095007635376395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0274841891893207</v>
+        <v>0.01976367548578666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07895847461305604</v>
+        <v>0.1171778729622073</v>
       </c>
     </row>
     <row r="4">
@@ -1636,25 +1636,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03119038144481107</v>
+        <v>0.1077315601121876</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07710103278363008</v>
+        <v>0.2967880375851219</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003164487206041778</v>
+        <v>0.002342820297363061</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001503419074547541</v>
+        <v>0.00192746173323774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001624712500017001</v>
+        <v>0.0008444453472277584</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008807695594945558</v>
+        <v>0.002581864719675275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01924413376142367</v>
+        <v>0.06870269829913556</v>
       </c>
     </row>
     <row r="5">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1766079880549322</v>
+        <v>0.3282248621177068</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2776707272717635</v>
+        <v>0.5447825599127801</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05625377503814102</v>
+        <v>0.04840268894765105</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03877394840027954</v>
+        <v>0.04390286702753865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04030772258534339</v>
+        <v>0.02905934182371924</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02967776203649048</v>
+        <v>0.05081205289766666</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1032153205644917</v>
+        <v>0.1741973954545104</v>
       </c>
     </row>
     <row r="6">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.05577820337528</v>
+        <v>70.04683112439758</v>
       </c>
       <c r="C6" t="n">
-        <v>56.80321053976497</v>
+        <v>137.058035480489</v>
       </c>
       <c r="D6" t="n">
-        <v>100.7165743493346</v>
+        <v>45.75351822466781</v>
       </c>
       <c r="E6" t="n">
-        <v>125.675885471314</v>
+        <v>4854.03578350956</v>
       </c>
       <c r="F6" t="n">
-        <v>2264.683196871958</v>
+        <v>255.5603898929425</v>
       </c>
       <c r="G6" t="n">
-        <v>413.4210732300234</v>
+        <v>72.78024870880967</v>
       </c>
       <c r="H6" t="n">
-        <v>504.2259531109617</v>
+        <v>905.8724678234777</v>
       </c>
     </row>
     <row r="7">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2411863584337993</v>
+        <v>1.340034113367166</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2190328343957528</v>
+        <v>1.492438588112912</v>
       </c>
       <c r="D7" t="n">
-        <v>2.493654229783582</v>
+        <v>1.628256873294055</v>
       </c>
       <c r="E7" t="n">
-        <v>1.534310825065314</v>
+        <v>2.27036962755554</v>
       </c>
       <c r="F7" t="n">
-        <v>1.440028119712867</v>
+        <v>0.7476509698894783</v>
       </c>
       <c r="G7" t="n">
-        <v>2.922245671684988</v>
+        <v>8.388089938177362</v>
       </c>
       <c r="H7" t="n">
-        <v>1.47507633984605</v>
+        <v>2.644473351732752</v>
       </c>
     </row>
     <row r="8">
@@ -1748,25 +1748,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-29.2088096684998</v>
+        <v>-18.05301430444112</v>
       </c>
       <c r="C8" t="n">
-        <v>-13.37583161874849</v>
+        <v>-5.288422438801023</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.53458554032395</v>
+        <v>-34.33839892039746</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.00008029016963</v>
+        <v>-35.50930783466929</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.06909282303555</v>
+        <v>-82.92196647929367</v>
       </c>
       <c r="G8" t="n">
-        <v>-89.45128893183706</v>
+        <v>-75.470163960143</v>
       </c>
       <c r="H8" t="n">
-        <v>-46.10661481210241</v>
+        <v>-41.93021232295759</v>
       </c>
     </row>
     <row r="9">
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-29.01158509116359</v>
+        <v>-17.8557897271049</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.58407214952044</v>
+        <v>-5.496662969572968</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.74282607109589</v>
+        <v>-34.5466394511694</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.20832082094158</v>
+        <v>-35.71754836544123</v>
       </c>
       <c r="F9" t="n">
-        <v>-74.58418617324755</v>
+        <v>-82.43705982950567</v>
       </c>
       <c r="G9" t="n">
-        <v>-88.88633957437551</v>
+        <v>-74.90521460268145</v>
       </c>
       <c r="H9" t="n">
-        <v>-46.00288831339075</v>
+        <v>-41.82648582424594</v>
       </c>
     </row>
   </sheetData>
@@ -1855,25 +1855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9284528651496975</v>
+        <v>0.1013170462320683</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9448334609450085</v>
+        <v>-0.4828843540386236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7053282012794257</v>
+        <v>-3.163858924399026</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7574862104738728</v>
+        <v>-3.630905279225293</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3263464959744331</v>
+        <v>-1.357371985658509</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.399003327951846</v>
+        <v>-15.30649189334717</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2684584856536209</v>
+        <v>-3.973365898406092</v>
       </c>
     </row>
     <row r="3">
@@ -1883,25 +1883,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04842492317623772</v>
+        <v>0.1753574760138588</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07164682187830403</v>
+        <v>0.3159832924664706</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01375332140142398</v>
+        <v>0.04328348026616293</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009034231243831308</v>
+        <v>0.04115621825118628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02141981679178479</v>
+        <v>0.03706701630354436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01612294630532499</v>
+        <v>0.05019981764476426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0300670101328178</v>
+        <v>0.1105078834909979</v>
       </c>
     </row>
     <row r="4">
@@ -1911,25 +1911,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003059014263075027</v>
+        <v>0.04888859162455064</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007754027519760006</v>
+        <v>0.2454249746517584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0002248555973982203</v>
+        <v>0.003604179241957911</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001428677191234173</v>
+        <v>0.002362731601372234</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000899917083082331</v>
+        <v>0.001602217515821065</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004341698611525528</v>
+        <v>0.003013152980791902</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002085808673931926</v>
+        <v>0.0508159746027087</v>
       </c>
     </row>
     <row r="5">
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05530835617766114</v>
+        <v>0.2211076471417274</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08805695611228</v>
+        <v>0.4954038500574641</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01499518580739233</v>
+        <v>0.06003481691450313</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0119527285221165</v>
+        <v>0.04860793763751178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02999861801954102</v>
+        <v>0.04002770935016223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02083674305529904</v>
+        <v>0.05489219416995373</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03685809794904834</v>
+        <v>0.1533456925452204</v>
       </c>
     </row>
     <row r="6">
@@ -1967,25 +1967,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.67534261794331</v>
+        <v>126.4798387289465</v>
       </c>
       <c r="C6" t="n">
-        <v>50.42347147818804</v>
+        <v>344.0395876104957</v>
       </c>
       <c r="D6" t="n">
-        <v>27.9512912338138</v>
+        <v>54.28763247591601</v>
       </c>
       <c r="E6" t="n">
-        <v>26.50031550498713</v>
+        <v>349.5952156301612</v>
       </c>
       <c r="F6" t="n">
-        <v>398.2700340707031</v>
+        <v>1241.093794282395</v>
       </c>
       <c r="G6" t="n">
-        <v>181.5602017431101</v>
+        <v>625.8701880295188</v>
       </c>
       <c r="H6" t="n">
-        <v>121.8967761081243</v>
+        <v>456.894376126239</v>
       </c>
     </row>
     <row r="7">
@@ -1995,25 +1995,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02510545043924328</v>
+        <v>0.304826900267565</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02347778098032945</v>
+        <v>1.235325576935636</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09005893853435105</v>
+        <v>2.505361205578157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07435414426122458</v>
+        <v>2.783850991777097</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8000677815009752</v>
+        <v>1.418666295917255</v>
       </c>
       <c r="G7" t="n">
-        <v>1.443009834576721</v>
+        <v>9.790113550181413</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4093456550488075</v>
+        <v>3.00635742010952</v>
       </c>
     </row>
     <row r="8">
@@ -2023,25 +2023,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-46.1069629604838</v>
+        <v>-23.16390088848308</v>
       </c>
       <c r="C8" t="n">
-        <v>-23.15725734380831</v>
+        <v>-4.428583884119622</v>
       </c>
       <c r="D8" t="n">
-        <v>-44.40031290681621</v>
+        <v>-29.75396723780113</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.12154838148341</v>
+        <v>-32.28762122644616</v>
       </c>
       <c r="F8" t="n">
-        <v>-78.15849514551246</v>
+        <v>-73.23639994264207</v>
       </c>
       <c r="G8" t="n">
-        <v>-94.64697129878202</v>
+        <v>-71.4619872050778</v>
       </c>
       <c r="H8" t="n">
-        <v>-55.59859133948103</v>
+        <v>-39.05541006409498</v>
       </c>
     </row>
     <row r="9">
@@ -2051,25 +2051,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-45.51528922847514</v>
+        <v>-22.76945173381064</v>
       </c>
       <c r="C9" t="n">
-        <v>-23.78197893612415</v>
+        <v>-4.845064945663512</v>
       </c>
       <c r="D9" t="n">
-        <v>-45.02503449913205</v>
+        <v>-30.17044829934502</v>
       </c>
       <c r="E9" t="n">
-        <v>-47.74626997379924</v>
+        <v>-32.70410228799005</v>
       </c>
       <c r="F9" t="n">
-        <v>-76.70377519614846</v>
+        <v>-72.26658664306606</v>
       </c>
       <c r="G9" t="n">
-        <v>-92.9521232263974</v>
+        <v>-70.33208849015473</v>
       </c>
       <c r="H9" t="n">
-        <v>-55.28741184334607</v>
+        <v>-38.84795706667168</v>
       </c>
     </row>
   </sheetData>
@@ -2130,25 +2130,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8522492639478814</v>
+        <v>-0.6551466827940784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.809611520842735</v>
+        <v>0.07265847308176099</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1309503972227823</v>
+        <v>0.02714318502080126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7006189026780063</v>
+        <v>-6.827609841009651</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2758830816062997</v>
+        <v>-30.98790750531827</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2719645224067939</v>
+        <v>-18.99266159381989</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4162247739818185</v>
+        <v>-9.56058732747322</v>
       </c>
     </row>
     <row r="3">
@@ -2158,25 +2158,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05063601419052546</v>
+        <v>0.2014515037940175</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1339249953933344</v>
+        <v>0.3335121902494189</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02285560528750792</v>
+        <v>0.02645592377929376</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01103209755484904</v>
+        <v>0.05938300244170366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01549202128291841</v>
+        <v>0.141642024384512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01216321960075562</v>
+        <v>0.05762459664444593</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04101732555164848</v>
+        <v>0.136678206882232</v>
       </c>
     </row>
     <row r="4">
@@ -2186,25 +2186,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006317116819687066</v>
+        <v>0.09004041961025655</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02676037924654097</v>
+        <v>0.1534797842580136</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006631468245336149</v>
+        <v>0.000842091531343462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001763689174402639</v>
+        <v>0.003993720454083602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004913084077118762</v>
+        <v>0.02174098360856206</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0002301992054991496</v>
+        <v>0.003694292326601511</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00577308657023549</v>
+        <v>0.04563188196481013</v>
       </c>
     </row>
     <row r="5">
@@ -2214,25 +2214,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07948029202064538</v>
+        <v>0.3000673584551585</v>
       </c>
       <c r="C5" t="n">
-        <v>0.163585999543179</v>
+        <v>0.3917649604775976</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02575163731753022</v>
+        <v>0.02901881340343643</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01328039598205806</v>
+        <v>0.06319588953471264</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02216547783630834</v>
+        <v>0.1474482404390166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01517231707746545</v>
+        <v>0.06078069040905599</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05323935329619775</v>
+        <v>0.1653793254531629</v>
       </c>
     </row>
     <row r="6">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.62458853041023</v>
+        <v>63.85573878765364</v>
       </c>
       <c r="C6" t="n">
-        <v>45.02962239763533</v>
+        <v>1260.812771473809</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68273320433253</v>
+        <v>55.12182829004101</v>
       </c>
       <c r="E6" t="n">
-        <v>27.90260842166132</v>
+        <v>5562.225524999012</v>
       </c>
       <c r="F6" t="n">
-        <v>399.1303423871526</v>
+        <v>5595.323289493262</v>
       </c>
       <c r="G6" t="n">
-        <v>156.1911446122074</v>
+        <v>719.1921801650223</v>
       </c>
       <c r="H6" t="n">
-        <v>116.2601732588999</v>
+        <v>2209.421888868133</v>
       </c>
     </row>
     <row r="7">
@@ -2270,25 +2270,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04974720258941655</v>
+        <v>1.121144597130806</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07684880921975819</v>
+        <v>0.3866383070560812</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2621790836103389</v>
+        <v>0.2934465085657001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09093778743880632</v>
+        <v>4.704157113241508</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2185789914035084</v>
+        <v>19.22518188024295</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7655009923317753</v>
+        <v>12.00276896554918</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2439654777656006</v>
+        <v>6.288889561964371</v>
       </c>
     </row>
     <row r="8">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-41.58043136897528</v>
+        <v>-17.66746942420558</v>
       </c>
       <c r="C8" t="n">
-        <v>-17.72499723007848</v>
+        <v>-7.245118515636655</v>
       </c>
       <c r="D8" t="n">
-        <v>-39.91108482496445</v>
+        <v>-38.47773105542833</v>
       </c>
       <c r="E8" t="n">
-        <v>-47.85759580942803</v>
+        <v>-29.13819222742598</v>
       </c>
       <c r="F8" t="n">
-        <v>-87.42126206891342</v>
+        <v>-41.94267384954168</v>
       </c>
       <c r="G8" t="n">
-        <v>-104.8953516694263</v>
+        <v>-68.81256144264277</v>
       </c>
       <c r="H8" t="n">
-        <v>-56.56512049529766</v>
+        <v>-33.88062441914683</v>
       </c>
     </row>
     <row r="9">
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-41.18598221430284</v>
+        <v>-17.27302026953314</v>
       </c>
       <c r="C9" t="n">
-        <v>-18.14147829162237</v>
+        <v>-7.661599577180545</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.32756588650834</v>
+        <v>-38.89421211697222</v>
       </c>
       <c r="E9" t="n">
-        <v>-48.27407687097192</v>
+        <v>-29.55467328896987</v>
       </c>
       <c r="F9" t="n">
-        <v>-86.45144876933742</v>
+        <v>-40.97286054996568</v>
       </c>
       <c r="G9" t="n">
-        <v>-103.7654529545033</v>
+        <v>-67.6826627277197</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.35766749787436</v>
+        <v>-33.67317142172353</v>
       </c>
     </row>
   </sheetData>
@@ -2405,25 +2405,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3480532912462272</v>
+        <v>-0.4551434008296718</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2132636410766668</v>
+        <v>-1.681983363928292</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.205656322986426</v>
+        <v>-1.551573574807702</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.793636259727542</v>
+        <v>-4.781837501348137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2631707070295851</v>
+        <v>-7.140584501121635</v>
       </c>
       <c r="G2" t="n">
-        <v>-5.718973675322125</v>
+        <v>-5.779914091563469</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.553384316806158</v>
+        <v>-3.565172738933151</v>
       </c>
     </row>
     <row r="3">
@@ -2433,25 +2433,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1397241396086451</v>
+        <v>0.1812104427770674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2968477070975669</v>
+        <v>0.4345896124719994</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0376946800061283</v>
+        <v>0.03671255914538701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07152480074250341</v>
+        <v>0.04921993020186143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01992660810786835</v>
+        <v>0.06350723652777251</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03319766965881988</v>
+        <v>0.02695485750569221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.099819267536922</v>
+        <v>0.13203243977163</v>
       </c>
     </row>
     <row r="4">
@@ -2461,25 +2461,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02787413199725327</v>
+        <v>0.07916018789502065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1705323520885527</v>
+        <v>0.4438820177149124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00244614439077019</v>
+        <v>0.002208607130938658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005180434307191849</v>
+        <v>0.00294994808892305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004999336674632673</v>
+        <v>0.005532850630306924</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001215994923272078</v>
+        <v>0.001252808911206843</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03462483189575054</v>
+        <v>0.08916440339521807</v>
       </c>
     </row>
     <row r="5">
@@ -2489,25 +2489,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1669554790872503</v>
+        <v>0.2813542036206686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4129556296850216</v>
+        <v>0.6662447130858994</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04945851181313678</v>
+        <v>0.04699582035605569</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07197523398497464</v>
+        <v>0.05431342457370048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02235919648518853</v>
+        <v>0.07438313404466718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03487111875567055</v>
+        <v>0.03539504077136857</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1264291949685404</v>
+        <v>0.1931143894087266</v>
       </c>
     </row>
     <row r="6">
@@ -2517,25 +2517,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.00923238164275</v>
+        <v>64.81973312141692</v>
       </c>
       <c r="C6" t="n">
-        <v>86.06422743285805</v>
+        <v>87.2665197891786</v>
       </c>
       <c r="D6" t="n">
-        <v>50.3295594138931</v>
+        <v>45.16511309852391</v>
       </c>
       <c r="E6" t="n">
-        <v>208.8792291887194</v>
+        <v>5051.846803943985</v>
       </c>
       <c r="F6" t="n">
-        <v>1548.130758259048</v>
+        <v>1724.130637510116</v>
       </c>
       <c r="G6" t="n">
-        <v>509.1357703951458</v>
+        <v>228.5686192727566</v>
       </c>
       <c r="H6" t="n">
-        <v>412.5914628452178</v>
+        <v>1200.299571122663</v>
       </c>
     </row>
     <row r="7">
@@ -2545,25 +2545,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2160959050242092</v>
+        <v>0.9859103035508321</v>
       </c>
       <c r="C7" t="n">
-        <v>0.968703477569974</v>
+        <v>2.232624843157852</v>
       </c>
       <c r="D7" t="n">
-        <v>1.928818395938934</v>
+        <v>1.536036194867935</v>
       </c>
       <c r="E7" t="n">
-        <v>5.285434363866594</v>
+        <v>3.475232428133375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2223987414583488</v>
+        <v>4.894096691555411</v>
       </c>
       <c r="G7" t="n">
-        <v>4.035086598085856</v>
+        <v>4.071702387413771</v>
       </c>
       <c r="H7" t="n">
-        <v>2.109422913657319</v>
+        <v>2.865933808113196</v>
       </c>
     </row>
     <row r="8">
@@ -2573,25 +2573,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-28.22050569918809</v>
+        <v>-18.82653606175927</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.612981511631265</v>
+        <v>-0.8731788663716031</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.07945327244056</v>
+        <v>-32.69235931785224</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.57719829882891</v>
+        <v>-30.95580623456284</v>
       </c>
       <c r="F8" t="n">
-        <v>-87.21242160099604</v>
+        <v>-58.36462533895623</v>
       </c>
       <c r="G8" t="n">
-        <v>-83.25850471503882</v>
+        <v>-82.87077255636976</v>
       </c>
       <c r="H8" t="n">
-        <v>-44.16017751635395</v>
+        <v>-37.43054639597866</v>
       </c>
     </row>
     <row r="9">
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-27.82605654451565</v>
+        <v>-18.43208690708683</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.029462573175155</v>
+        <v>-1.289659927915493</v>
       </c>
       <c r="D9" t="n">
-        <v>-32.49593433398445</v>
+        <v>-33.10884037939613</v>
       </c>
       <c r="E9" t="n">
-        <v>-27.9936793603728</v>
+        <v>-31.37228729610673</v>
       </c>
       <c r="F9" t="n">
-        <v>-86.24260830142003</v>
+        <v>-57.39481203938023</v>
       </c>
       <c r="G9" t="n">
-        <v>-82.12860600011575</v>
+        <v>-81.74087384144669</v>
       </c>
       <c r="H9" t="n">
-        <v>-43.95272451893064</v>
+        <v>-37.22309339855536</v>
       </c>
     </row>
   </sheetData>
@@ -2680,25 +2680,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9275111181595805</v>
+        <v>-0.8033774924625521</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5788632556129019</v>
+        <v>-0.8429219541454953</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.283736586439407</v>
+        <v>-1.155837126317685</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.286718821732013</v>
+        <v>-3.404090113642207</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3124070951458252</v>
+        <v>-0.03161047198630351</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.410536700666531</v>
+        <v>-1.967071214259471</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.360368439986607</v>
+        <v>-1.367484728802286</v>
       </c>
     </row>
     <row r="3">
@@ -2708,25 +2708,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04820945988894363</v>
+        <v>0.2124418327735671</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1841896676640685</v>
+        <v>0.3772994038041378</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0589585404926166</v>
+        <v>0.03768683857068847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04305483727682308</v>
+        <v>0.04166975553534746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01859118280720281</v>
+        <v>0.01654095318151167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01632468861341083</v>
+        <v>0.01906515598921837</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06155472945717758</v>
+        <v>0.1174506566424118</v>
       </c>
     </row>
     <row r="4">
@@ -2736,25 +2736,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00309927887298573</v>
+        <v>0.09810421506745831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05919359745052249</v>
+        <v>0.3050130461283069</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004794939149832645</v>
+        <v>0.001866063082537757</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002525356359244451</v>
+        <v>0.002247008362160724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004665271127586282</v>
+        <v>0.0007011470305816754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0004362571624796546</v>
+        <v>0.000548262589644758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01175265935130393</v>
+        <v>0.06807995704344835</v>
       </c>
     </row>
     <row r="5">
@@ -2764,25 +2764,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05567116733988726</v>
+        <v>0.3132159240323811</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2432973436980406</v>
+        <v>0.5522798621426521</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06924549913050411</v>
+        <v>0.04319795229565583</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05025292388751575</v>
+        <v>0.04740261978161886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02159923870784867</v>
+        <v>0.02647918107838072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02088677003463328</v>
+        <v>0.02341500778656198</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07682549046640495</v>
+        <v>0.1676650911862084</v>
       </c>
     </row>
     <row r="6">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33.04490160227337</v>
+        <v>65.75791918321801</v>
       </c>
       <c r="C6" t="n">
-        <v>45.86809328673292</v>
+        <v>100.7116535616644</v>
       </c>
       <c r="D6" t="n">
-        <v>161.286453775993</v>
+        <v>86.42559223400002</v>
       </c>
       <c r="E6" t="n">
-        <v>98.15921919181805</v>
+        <v>4551.009004715298</v>
       </c>
       <c r="F6" t="n">
-        <v>625.1855894472036</v>
+        <v>81.2786067418354</v>
       </c>
       <c r="G6" t="n">
-        <v>121.4365682159989</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>180.83013758667</v>
+        <v>830.8637960726693</v>
       </c>
     </row>
     <row r="7">
@@ -2820,25 +2820,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02491615976321585</v>
+        <v>1.221372396571973</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1687765415314952</v>
+        <v>1.534771437066927</v>
       </c>
       <c r="D7" t="n">
-        <v>3.778954866673411</v>
+        <v>1.298114764106164</v>
       </c>
       <c r="E7" t="n">
-        <v>2.57756679194215</v>
+        <v>2.647599879892349</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2076044404351835</v>
+        <v>0.6219478890345965</v>
       </c>
       <c r="G7" t="n">
-        <v>1.448932780427391</v>
+        <v>1.783010296181185</v>
       </c>
       <c r="H7" t="n">
-        <v>1.367791930128808</v>
+        <v>1.517802777142199</v>
       </c>
     </row>
     <row r="8">
@@ -2848,25 +2848,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-47.98927234552233</v>
+        <v>-16.89552451656835</v>
       </c>
       <c r="C8" t="n">
-        <v>-12.96165136468726</v>
+        <v>-3.12440437459007</v>
       </c>
       <c r="D8" t="n">
-        <v>-28.04116556638735</v>
+        <v>-33.70354622502845</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.88823856303407</v>
+        <v>-32.58893338584813</v>
       </c>
       <c r="F8" t="n">
-        <v>-88.04233303808346</v>
+        <v>-83.15351538642977</v>
       </c>
       <c r="G8" t="n">
-        <v>-96.58462266178228</v>
+        <v>-93.61383069882078</v>
       </c>
       <c r="H8" t="n">
-        <v>-50.91788058991612</v>
+        <v>-43.84662576454759</v>
       </c>
     </row>
     <row r="9">
@@ -2876,25 +2876,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-47.59482319084989</v>
+        <v>-16.50107536189591</v>
       </c>
       <c r="C9" t="n">
-        <v>-13.37813242623115</v>
+        <v>-3.54088543613396</v>
       </c>
       <c r="D9" t="n">
-        <v>-28.45764662793124</v>
+        <v>-34.12002728657234</v>
       </c>
       <c r="E9" t="n">
-        <v>-32.30471962457796</v>
+        <v>-33.00541444739202</v>
       </c>
       <c r="F9" t="n">
-        <v>-87.07251973850745</v>
+        <v>-82.18370208685377</v>
       </c>
       <c r="G9" t="n">
-        <v>-95.4547239468592</v>
+        <v>-92.4839319838977</v>
       </c>
       <c r="H9" t="n">
-        <v>-50.71042759249281</v>
+        <v>-43.63917276712429</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9272751743469008</v>
+        <v>-0.1943510027829487</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7899330418961297</v>
+        <v>-0.2873119755468914</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8227764258141734</v>
+        <v>-0.8214484172010497</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9268635983857173</v>
+        <v>-10.06833566790795</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5103050973376433</v>
+        <v>-0.1400386893752441</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7401201751621067</v>
+        <v>-0.5517362746814767</v>
       </c>
       <c r="H2" t="n">
-        <v>0.786212252157112</v>
+        <v>-2.010537004582593</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1510871578328812</v>
+        <v>0.5590425424463831</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2395264281865523</v>
+        <v>0.5320707322367445</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03239014546472665</v>
+        <v>0.125507839433398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01286032850058901</v>
+        <v>0.1958090001078886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08578126154898645</v>
+        <v>0.1235350413503498</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07715952171508557</v>
+        <v>0.1871722712293892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09980080720813685</v>
+        <v>0.2871895711340255</v>
       </c>
     </row>
     <row r="4">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03858166203886906</v>
+        <v>0.6336219623950697</v>
       </c>
       <c r="C4" t="n">
-        <v>0.107574036651189</v>
+        <v>0.6592247866536056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001566023594043838</v>
+        <v>0.01609510026967265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002647877994208529</v>
+        <v>0.04007252448942385</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01073727081228648</v>
+        <v>0.02499700135279173</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007522280549273975</v>
+        <v>0.04491535887374254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02770767690751387</v>
+        <v>0.2364877890057177</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1964221526174404</v>
+        <v>0.796003745214223</v>
       </c>
       <c r="C5" t="n">
-        <v>0.327984811616619</v>
+        <v>0.8119265894485816</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03957301598367047</v>
+        <v>0.126866466292999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01627230160182796</v>
+        <v>0.2001812291135806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1036208029899715</v>
+        <v>0.1581044001689761</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08673108179467136</v>
+        <v>0.2119324394087478</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1284340277673668</v>
+        <v>0.3841691449411846</v>
       </c>
     </row>
     <row r="6">
@@ -594,25 +594,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.39602426906206</v>
+        <v>52.37165783000029</v>
       </c>
       <c r="C6" t="n">
-        <v>28.60909375082988</v>
+        <v>42.8094066687361</v>
       </c>
       <c r="D6" t="n">
-        <v>15.84226648506834</v>
+        <v>67.07915078634312</v>
       </c>
       <c r="E6" t="n">
-        <v>8.427357157098779</v>
+        <v>138.1828850544591</v>
       </c>
       <c r="F6" t="n">
-        <v>24.71661342952434</v>
+        <v>42.6047688683479</v>
       </c>
       <c r="G6" t="n">
-        <v>30.5626463921788</v>
+        <v>77.40607379677765</v>
       </c>
       <c r="H6" t="n">
-        <v>22.42566691396037</v>
+        <v>70.07565716744404</v>
       </c>
     </row>
     <row r="7">
@@ -622,25 +622,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05032461112313812</v>
+        <v>1.605681349022867</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1398219130869934</v>
+        <v>1.697301886643183</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05576328877157867</v>
+        <v>1.117402190698172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02362627194387941</v>
+        <v>6.699102935029963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1559245603673076</v>
+        <v>0.721019015519055</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08472954383585979</v>
+        <v>0.9959232672321257</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08503169818812617</v>
+        <v>2.139405107357561</v>
       </c>
     </row>
     <row r="8">
@@ -650,25 +650,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.29480372898356</v>
+        <v>-0.1067249859049211</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.377455732604538</v>
+        <v>1.49985580011456</v>
       </c>
       <c r="D8" t="n">
-        <v>-32.75529369052674</v>
+        <v>-20.77544230631631</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.41949085794533</v>
+        <v>-15.30238612601899</v>
       </c>
       <c r="F8" t="n">
-        <v>-52.9424463745803</v>
+        <v>-43.95699229355255</v>
       </c>
       <c r="G8" t="n">
-        <v>-62.45840291450534</v>
+        <v>-39.44165663975883</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.04131554985764</v>
+        <v>-19.68055775857284</v>
       </c>
     </row>
     <row r="9">
@@ -678,25 +678,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.7031299969749</v>
+        <v>0.2877241687675181</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.002177324920373</v>
+        <v>1.08337473857067</v>
       </c>
       <c r="D9" t="n">
-        <v>-33.38001528284258</v>
+        <v>-21.19192336786021</v>
       </c>
       <c r="E9" t="n">
-        <v>-44.04421245026117</v>
+        <v>-15.71886718756288</v>
       </c>
       <c r="F9" t="n">
-        <v>-51.24759830219569</v>
+        <v>-42.82709357862948</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.54123092565957</v>
+        <v>-38.16354198052831</v>
       </c>
       <c r="H9" t="n">
-        <v>-36.65306071380905</v>
+        <v>-19.42172120120711</v>
       </c>
     </row>
   </sheetData>
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-7.666320548891625e+214</v>
+        <v>-0.7653764709583708</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8551421722155526</v>
+        <v>-0.8556248077595245</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2040908055946826</v>
+        <v>-0.2040907884742515</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.777664341957919</v>
+        <v>-3.777665883881784</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.008058627144031</v>
+        <v>-1.008058917688206</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2274979437073321</v>
+        <v>-0.227497361559114</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.277720091481938e+214</v>
+        <v>-1.139719038386875</v>
       </c>
     </row>
     <row r="3">
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.722353621221882e+106</v>
+        <v>0.7076851719714904</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6742554220776626</v>
+        <v>0.6743451117177943</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09092877591365227</v>
+        <v>0.09092877542883311</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1169482919431624</v>
+        <v>0.1169483133704101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1767812831972742</v>
+        <v>0.176781290711323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1329416552858683</v>
+        <v>0.1329416347089239</v>
       </c>
       <c r="H3" t="n">
-        <v>1.120392270203647e+106</v>
+        <v>0.3166050496514625</v>
       </c>
     </row>
     <row r="4">
@@ -813,25 +813,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.067103438787944e+214</v>
+        <v>0.9365599403260245</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9500072444920381</v>
+        <v>0.9502543992762319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01063986334546755</v>
+        <v>0.01063986319418407</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01729736765216327</v>
+        <v>0.01729737323464502</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04402959714175333</v>
+        <v>0.04402960351235566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03553020674838129</v>
+        <v>0.0355301898979689</v>
       </c>
       <c r="H4" t="n">
-        <v>6.778505731313241e+213</v>
+        <v>0.332385228240235</v>
       </c>
     </row>
     <row r="5">
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.016706086366564e+107</v>
+        <v>0.9677602700700336</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9746831508198128</v>
+        <v>0.9748099298202865</v>
       </c>
       <c r="D5" t="n">
-        <v>0.10314971325926</v>
+        <v>0.10314971252594</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1315194573139779</v>
+        <v>0.1315194785370023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2098323071925611</v>
+        <v>0.2098323223727833</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1884945801565162</v>
+        <v>0.1884945354591716</v>
       </c>
       <c r="H5" t="n">
-        <v>3.36117681061094e+106</v>
+        <v>0.4292610414642029</v>
       </c>
     </row>
     <row r="6">
@@ -869,25 +869,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.15095548641602</v>
+        <v>68.88832817650103</v>
       </c>
       <c r="C6" t="n">
-        <v>59.23611020408869</v>
+        <v>59.24246574047237</v>
       </c>
       <c r="D6" t="n">
-        <v>58.17640671197193</v>
+        <v>58.17640644469365</v>
       </c>
       <c r="E6" t="n">
-        <v>113.5272157601976</v>
+        <v>113.5272337262645</v>
       </c>
       <c r="F6" t="n">
-        <v>57.11682990849836</v>
+        <v>57.11683107985552</v>
       </c>
       <c r="G6" t="n">
-        <v>59.52863997695312</v>
+        <v>59.5286349064703</v>
       </c>
       <c r="H6" t="n">
-        <v>67.62269300802095</v>
+        <v>69.41331667904289</v>
       </c>
     </row>
     <row r="7">
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.02937371436381e+215</v>
+        <v>2.371409799031457</v>
       </c>
       <c r="C7" t="n">
-        <v>2.453095445618185</v>
+        <v>2.444731043642439</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7473502920404643</v>
+        <v>0.7383502815564087</v>
       </c>
       <c r="E7" t="n">
-        <v>2.90081491988778</v>
+        <v>2.891815852857574</v>
       </c>
       <c r="F7" t="n">
-        <v>1.276476612284874</v>
+        <v>1.267476795530222</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7962410556721332</v>
+        <v>0.787240682792625</v>
       </c>
       <c r="H7" t="n">
-        <v>1.715622857273016e+214</v>
+        <v>1.750170742568454</v>
       </c>
     </row>
     <row r="8">
@@ -925,25 +925,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4467.405268649092</v>
+        <v>1.410124209258362</v>
       </c>
       <c r="C8" t="n">
-        <v>19.6922859881868</v>
+        <v>1.693846750851651</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.258885831733267</v>
+        <v>-25.2588859170446</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.34320568734136</v>
+        <v>-22.34320375092619</v>
       </c>
       <c r="F8" t="n">
-        <v>-20.59761171553347</v>
+        <v>-38.59760983457544</v>
       </c>
       <c r="G8" t="n">
-        <v>-26.72320869979722</v>
+        <v>-44.72321533938226</v>
       </c>
       <c r="H8" t="n">
-        <v>738.0291071171456</v>
+        <v>-21.30315731363642</v>
       </c>
     </row>
     <row r="9">
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4469.377514422455</v>
+        <v>1.607348786594582</v>
       </c>
       <c r="C9" t="n">
-        <v>17.60988068046735</v>
+        <v>1.485606220079706</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.341291139452718</v>
+        <v>-25.46712644781655</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.425610995060811</v>
+        <v>-22.55144428169814</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.94811814091811</v>
+        <v>-38.03266047711391</v>
       </c>
       <c r="G9" t="n">
-        <v>-20.33263540364463</v>
+        <v>-44.084158009767</v>
       </c>
       <c r="H9" t="n">
-        <v>739.3232899039743</v>
+        <v>-21.17373903495355</v>
       </c>
     </row>
   </sheetData>
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5043588249552997</v>
+        <v>0.7521805961360201</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4852156074442451</v>
+        <v>0.821051020933881</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4264195590175275</v>
+        <v>-2.380094059969498</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05747795886204021</v>
+        <v>-4.667434451342429</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2082541334290542</v>
+        <v>-0.4119749944707751</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6463992284489573</v>
+        <v>-0.5617694145496819</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3688615657388405</v>
+        <v>-1.074673550543747</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3326765539162289</v>
+        <v>0.2448747019963725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3625835095794821</v>
+        <v>0.2293203748329558</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0638932411516894</v>
+        <v>0.1584220873278238</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0516709782138243</v>
+        <v>0.1328765812869198</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1065148357276109</v>
+        <v>0.1622611023992138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08100198306087854</v>
+        <v>0.1937837676579939</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1663901836082857</v>
+        <v>0.1869231025835466</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2629454266324202</v>
+        <v>0.1314720853668572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2636180178553867</v>
+        <v>0.09163870513721151</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005068403048449849</v>
+        <v>0.02986796238772051</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003828562186308776</v>
+        <v>0.02051874939988609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01736017617839537</v>
+        <v>0.03095959915732005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01023505463614134</v>
+        <v>0.04520577038577824</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09384260675618371</v>
+        <v>0.05827714530579559</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5127820459341572</v>
+        <v>0.3625907960316384</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5134374527197901</v>
+        <v>0.3027188549416959</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0711927176644483</v>
+        <v>0.1728235006812456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06187537625185625</v>
+        <v>0.1432436714130369</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1317580213057079</v>
+        <v>0.1759534005278672</v>
       </c>
       <c r="G5" t="n">
-        <v>0.10116844684061</v>
+        <v>0.2126164866273973</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2320356767860949</v>
+        <v>0.2283244517038136</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.48785108225678</v>
+        <v>25.93326327064546</v>
       </c>
       <c r="C6" t="n">
-        <v>41.14633413205107</v>
+        <v>30.58950214517655</v>
       </c>
       <c r="D6" t="n">
-        <v>31.06975549341835</v>
+        <v>72.82755339631949</v>
       </c>
       <c r="E6" t="n">
-        <v>29.81070345095522</v>
+        <v>84.07583105890407</v>
       </c>
       <c r="F6" t="n">
-        <v>31.59297658962645</v>
+        <v>45.7492021328875</v>
       </c>
       <c r="G6" t="n">
-        <v>32.51843485848638</v>
+        <v>72.9866083357049</v>
       </c>
       <c r="H6" t="n">
-        <v>33.10434260113237</v>
+        <v>55.360326723273</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3332541511561042</v>
+        <v>0.168376280915994</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3394679302654972</v>
+        <v>0.1198317873158837</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1761220144286567</v>
+        <v>2.073871583324508</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6408467623780565</v>
+        <v>3.433186919965299</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2501758832961605</v>
+        <v>0.8945284355027132</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1137447697106118</v>
+        <v>1.004349727269899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3089352518725145</v>
+        <v>1.282357455715716</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.02227894471449</v>
+        <v>-10.26064655629874</v>
       </c>
       <c r="C8" t="n">
-        <v>-5.999524754034075</v>
+        <v>-6.339409308298343</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.70837694946639</v>
+        <v>-13.06581319055783</v>
       </c>
       <c r="E8" t="n">
-        <v>-31.39159572728428</v>
+        <v>-15.31849723576882</v>
       </c>
       <c r="F8" t="n">
-        <v>-50.69649347659254</v>
+        <v>-37.17593830697234</v>
       </c>
       <c r="G8" t="n">
-        <v>-62.14711410402299</v>
+        <v>-35.3514275164608</v>
       </c>
       <c r="H8" t="n">
-        <v>-31.66089732601913</v>
+        <v>-19.58528868572614</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.82505436737827</v>
+        <v>-9.47174824695386</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.207765284806021</v>
+        <v>-7.172371431386123</v>
       </c>
       <c r="D9" t="n">
-        <v>-29.91661748023834</v>
+        <v>-13.89877531364561</v>
       </c>
       <c r="E9" t="n">
-        <v>-31.59983625805623</v>
+        <v>-16.15145935885661</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.13154411913101</v>
+        <v>-34.9161408771262</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.50805677440773</v>
+        <v>-32.79519819799976</v>
       </c>
       <c r="H9" t="n">
-        <v>-31.53147904733627</v>
+        <v>-19.06761557099469</v>
       </c>
     </row>
   </sheetData>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8033806824022012</v>
+        <v>-0.1127094150891652</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1562427850466899</v>
+        <v>-0.2402696418220431</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7471208766565163</v>
+        <v>-0.4616355628790303</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1277366910547593</v>
+        <v>-8.775435998057157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2038231748195076</v>
+        <v>0.2342529187151345</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.04905537711722108</v>
+        <v>-0.2147760234693841</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2889625751254891</v>
+        <v>-1.595095620433608</v>
       </c>
     </row>
     <row r="3">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2651743976968265</v>
+        <v>0.5458470452132586</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4699694230951552</v>
+        <v>0.533580525876541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03955585303407903</v>
+        <v>0.112579284873324</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05989011127589866</v>
+        <v>0.181984998050626</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1105428814281747</v>
+        <v>0.1036909703172262</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1410672420358862</v>
+        <v>0.1763334820455804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1810333180943367</v>
+        <v>0.2756693843960927</v>
       </c>
     </row>
     <row r="4">
@@ -1363,25 +1363,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1043096355851909</v>
+        <v>0.5903098180697844</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4320830385957793</v>
+        <v>0.6351346880586041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002234548509792377</v>
+        <v>0.01291563939999336</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004082931483632478</v>
+        <v>0.03539162618303409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01745733137092458</v>
+        <v>0.01679011511202643</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03036514613368905</v>
+        <v>0.03516196787791481</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09842210527983476</v>
+        <v>0.2209506424502262</v>
       </c>
     </row>
     <row r="5">
@@ -1391,25 +1391,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3229700227346045</v>
+        <v>0.768316222703767</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6573302355709641</v>
+        <v>0.7969533788488534</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04727101130494647</v>
+        <v>0.1136469946808685</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06389782064853604</v>
+        <v>0.1881266227386068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.132126194870376</v>
+        <v>0.1295766765742448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1742559787602395</v>
+        <v>0.1875152470545124</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2329752106482778</v>
+        <v>0.3640225237668088</v>
       </c>
     </row>
     <row r="6">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32.90025536430965</v>
+        <v>51.73052974370744</v>
       </c>
       <c r="C6" t="n">
-        <v>42.45571874984169</v>
+        <v>44.70944065158943</v>
       </c>
       <c r="D6" t="n">
-        <v>21.7837044374181</v>
+        <v>60.5207116272715</v>
       </c>
       <c r="E6" t="n">
-        <v>54.13014605997862</v>
+        <v>129.0636296878456</v>
       </c>
       <c r="F6" t="n">
-        <v>34.24912460061064</v>
+        <v>46.46010450507712</v>
       </c>
       <c r="G6" t="n">
-        <v>95.20392091570979</v>
+        <v>87.9574524456672</v>
       </c>
       <c r="H6" t="n">
-        <v>46.78714502131141</v>
+        <v>70.07364477685972</v>
       </c>
     </row>
     <row r="7">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1380025401889733</v>
+        <v>1.496059394351198</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5615852915030386</v>
+        <v>1.635350348375272</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0834279209598998</v>
+        <v>0.897063232887409</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6943581187099411</v>
+        <v>5.916809875490543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2570731795137949</v>
+        <v>0.2424772049638782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6839444308574973</v>
+        <v>0.7800923691107112</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4030652469555243</v>
+        <v>1.827975404196502</v>
       </c>
     </row>
     <row r="8">
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.656476159121691</v>
+        <v>-0.7439698808121742</v>
       </c>
       <c r="C8" t="n">
-        <v>18.96517505857191</v>
+        <v>1.276490827587468</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.62229648218774</v>
+        <v>-22.09589807202014</v>
       </c>
       <c r="E8" t="n">
-        <v>-9.005640286043665</v>
+        <v>-16.04768021195768</v>
       </c>
       <c r="F8" t="n">
-        <v>-28.62394257505398</v>
+        <v>-49.13054437507583</v>
       </c>
       <c r="G8" t="n">
-        <v>-24.92243771903804</v>
+        <v>-42.86906333910373</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.758777640771639</v>
+        <v>-21.60177750856368</v>
       </c>
     </row>
     <row r="9">
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.023171087156324</v>
+        <v>-0.3495207261397351</v>
       </c>
       <c r="C9" t="n">
-        <v>16.46628868930857</v>
+        <v>0.8600097660435777</v>
       </c>
       <c r="D9" t="n">
-        <v>-15.12118285145107</v>
+        <v>-22.51237913356403</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.504526655307</v>
+        <v>-16.46416127350157</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.84455028551554</v>
+        <v>-48.00064566015276</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.25374976365494</v>
+        <v>-41.59094867987321</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.205758296577277</v>
+        <v>-21.34294095119796</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7411938879029136</v>
+        <v>0.1578548429797424</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1499010930423933</v>
+        <v>-0.03066971837282151</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6755926571079325</v>
+        <v>-8.272964801537301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4014552037747708</v>
+        <v>-38.12332057972097</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03500795347427987</v>
+        <v>0.1655117575768797</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01736220131969302</v>
+        <v>0.3012084563403606</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3309647656637661</v>
+        <v>-7.633730007122352</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3282094815075619</v>
+        <v>0.4734224644069233</v>
       </c>
       <c r="C3" t="n">
-        <v>0.47565926947092</v>
+        <v>0.4935326642702909</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03847765446708584</v>
+        <v>0.2325405351711791</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03942319444802182</v>
+        <v>0.3092561954538979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.125456852219076</v>
+        <v>0.1130521059005169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.137883658181957</v>
+        <v>0.09934646696437337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1908516850491037</v>
+        <v>0.2868584053611969</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1373007066136282</v>
+        <v>0.4467712303747711</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4353305812567409</v>
+        <v>0.5277998170692119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002866602569008999</v>
+        <v>0.08193989841734509</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002167010626023615</v>
+        <v>0.1416446220170315</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02115884988574888</v>
+        <v>0.01829736474660427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0294477799626322</v>
+        <v>0.02022667992848972</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1047119218189638</v>
+        <v>0.206113268758909</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3705410997630738</v>
+        <v>0.6684094780707192</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6597958633219375</v>
+        <v>0.7264983255790834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05354066276213807</v>
+        <v>0.2862514601139095</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04655116138211392</v>
+        <v>0.3763570406104176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1454608190742403</v>
+        <v>0.1352677520571857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1716035546328578</v>
+        <v>0.1422205327246728</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2412488601560602</v>
+        <v>0.389167431525998</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.39897674608656</v>
+        <v>44.35283886431273</v>
       </c>
       <c r="C6" t="n">
-        <v>43.77425034575962</v>
+        <v>44.26196873361221</v>
       </c>
       <c r="D6" t="n">
-        <v>18.79042038537044</v>
+        <v>90.86785144875938</v>
       </c>
       <c r="E6" t="n">
-        <v>40.30392755042767</v>
+        <v>175.05820581276</v>
       </c>
       <c r="F6" t="n">
-        <v>37.3893360430037</v>
+        <v>35.63921457677734</v>
       </c>
       <c r="G6" t="n">
-        <v>93.02388989926199</v>
+        <v>34.64963851834092</v>
       </c>
       <c r="H6" t="n">
-        <v>44.94680016165166</v>
+        <v>70.8049529924271</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1797523282586657</v>
+        <v>0.566883408368417</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5657610789670007</v>
+        <v>1.360321574920589</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1053288246659266</v>
+        <v>5.681494738706665</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1870803463057853</v>
+        <v>23.67529481865643</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3103088088777403</v>
+        <v>0.2646546280495591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6636442127395009</v>
+        <v>0.2252961390478346</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3353125999691032</v>
+        <v>5.295657551291582</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.129763622453037</v>
+        <v>-1.251377438231564</v>
       </c>
       <c r="C8" t="n">
-        <v>19.01010252238535</v>
+        <v>2.165770790975496</v>
       </c>
       <c r="D8" t="n">
-        <v>-11.12776634573273</v>
+        <v>-9.010615479504946</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.80643991725444</v>
+        <v>-5.726604120754525</v>
       </c>
       <c r="F8" t="n">
-        <v>-26.12406134703119</v>
+        <v>-46.0129770214857</v>
       </c>
       <c r="G8" t="n">
-        <v>-25.35191456997556</v>
+        <v>-48.61053860513712</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.378386005859257</v>
+        <v>-18.07439031235639</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.49645855048767</v>
+        <v>-0.6597037062229054</v>
       </c>
       <c r="C9" t="n">
-        <v>16.51121615312201</v>
+        <v>1.541049198659661</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.62665271499607</v>
+        <v>-9.63533707182078</v>
       </c>
       <c r="E9" t="n">
-        <v>-15.30532628651778</v>
+        <v>-6.351325713070359</v>
       </c>
       <c r="F9" t="n">
-        <v>-19.34466905749275</v>
+        <v>-44.31812894910109</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.68322661459246</v>
+        <v>-46.69336661629135</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.825366661664898</v>
+        <v>-17.6861354763078</v>
       </c>
     </row>
   </sheetData>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9525715193735552</v>
+        <v>-0.4376468958180517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7047834800271938</v>
+        <v>-0.2282583374655112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8675092467480994</v>
+        <v>-2.379578185106574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9483884003520955</v>
+        <v>-2.380380539653331</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6477240832882309</v>
+        <v>-0.5605471875780041</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7657652849022745</v>
+        <v>-0.8798003533875582</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8144570024485748</v>
+        <v>-1.144368583168172</v>
       </c>
     </row>
     <row r="3">
@@ -1885,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1072687247938568</v>
+        <v>0.6255966434180582</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2744751245158821</v>
+        <v>0.5022969679229335</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02781901587907543</v>
+        <v>0.1711130971983255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01152762457731128</v>
+        <v>0.09948502191312819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06368404869980758</v>
+        <v>0.1622357550932418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05639151797990453</v>
+        <v>0.2226569677659954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09019434274097295</v>
+        <v>0.2972307422186138</v>
       </c>
     </row>
     <row r="4">
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02516155376260509</v>
+        <v>0.7626942542325292</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1511786195518105</v>
+        <v>0.628983770719004</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00117074518183208</v>
+        <v>0.02986340389593619</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001868580022221092</v>
+        <v>0.0122385502231912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007724160283916112</v>
+        <v>0.03421725992506459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006779977023777938</v>
+        <v>0.05441124813604133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0320336523010273</v>
+        <v>0.2537347478552944</v>
       </c>
     </row>
     <row r="5">
@@ -1941,25 +1941,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1586239381764464</v>
+        <v>0.8733236823953243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3888169486426878</v>
+        <v>0.79308497068032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03421615381412821</v>
+        <v>0.1728103118912069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0136696013922173</v>
+        <v>0.1106279811945929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0878872020485128</v>
+        <v>0.1849790796956904</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08234061588170165</v>
+        <v>0.2332621875402041</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1275924099926157</v>
+        <v>0.3946813688995565</v>
       </c>
     </row>
     <row r="6">
@@ -1969,25 +1969,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.6702211208709</v>
+        <v>60.72308867924158</v>
       </c>
       <c r="C6" t="n">
-        <v>30.74822206532212</v>
+        <v>42.69597387811764</v>
       </c>
       <c r="D6" t="n">
-        <v>11.45478695387808</v>
+        <v>88.06354363297476</v>
       </c>
       <c r="E6" t="n">
-        <v>7.433740199092158</v>
+        <v>63.18747661132524</v>
       </c>
       <c r="F6" t="n">
-        <v>16.82509533042748</v>
+        <v>48.69045152178397</v>
       </c>
       <c r="G6" t="n">
-        <v>21.28217661883519</v>
+        <v>111.1474368475984</v>
       </c>
       <c r="H6" t="n">
-        <v>16.73570704807099</v>
+        <v>69.08466186184026</v>
       </c>
     </row>
     <row r="7">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03434163182175699</v>
+        <v>1.934360093416372</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1968899896781092</v>
+        <v>1.621532281485912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04306674760285265</v>
+        <v>2.073555676518255</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01811428049592683</v>
+        <v>2.049362294104466</v>
       </c>
       <c r="F7" t="n">
-        <v>0.113589687212272</v>
+        <v>0.988232476441893</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07751639844596224</v>
+        <v>1.208055959422993</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08058645587614667</v>
+        <v>1.645849796898315</v>
       </c>
     </row>
     <row r="8">
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.14194284407583</v>
+        <v>5.561917610326274</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.335759381895782</v>
+        <v>5.218101054001033</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.50068895217931</v>
+        <v>-13.06672898915615</v>
       </c>
       <c r="E8" t="n">
-        <v>-41.5109694557902</v>
+        <v>-18.41898672838557</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.22422812183276</v>
+        <v>-35.87532611862773</v>
       </c>
       <c r="G8" t="n">
-        <v>-59.91294192202443</v>
+        <v>-32.75658131001787</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.93775511296639</v>
+        <v>-14.88960074697667</v>
       </c>
     </row>
     <row r="9">
@@ -2053,25 +2053,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.15581995739473</v>
+        <v>6.350815919671152</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.376962035755508</v>
+        <v>4.385138930913253</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.54189160603904</v>
+        <v>-13.89969111224393</v>
       </c>
       <c r="E9" t="n">
-        <v>-42.55217210964993</v>
+        <v>-19.25194885147335</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.39948133452508</v>
+        <v>-33.61552868878158</v>
       </c>
       <c r="G9" t="n">
-        <v>-56.71765527394814</v>
+        <v>-30.20035199155684</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.29066371955207</v>
+        <v>-14.37192763224522</v>
       </c>
     </row>
   </sheetData>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9524408922734999</v>
+        <v>0.09921604814828777</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9000348946539971</v>
+        <v>-0.267522991279497</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8646559605863093</v>
+        <v>-2.24533737687479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9117092237752962</v>
+        <v>-2.536597231027211</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6476041840976594</v>
+        <v>-0.4976577363445214</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7590675841769878</v>
+        <v>-0.6775113851408787</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8392521232606249</v>
+        <v>-1.020901778753102</v>
       </c>
     </row>
     <row r="3">
@@ -2160,25 +2160,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1066522172254237</v>
+        <v>0.4674314408768186</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1854334600851726</v>
+        <v>0.513057365680992</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0275898018782428</v>
+        <v>0.1679630575330034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01492338579357512</v>
+        <v>0.1043101213803214</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0626185518442223</v>
+        <v>0.157950508094157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0592616749683854</v>
+        <v>0.209106789576667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07607984863250365</v>
+        <v>0.2699698805236599</v>
       </c>
     </row>
     <row r="4">
@@ -2188,25 +2188,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02523085349047922</v>
+        <v>0.477880031863625</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05119153437264321</v>
+        <v>0.6490909658086449</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001195958043441772</v>
+        <v>0.02867719447689999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003196536858484539</v>
+        <v>0.01280412732335876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0077267892475266</v>
+        <v>0.03283831751529322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006973843492335506</v>
+        <v>0.04855594800982384</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01543977205537913</v>
+        <v>0.2083077641662743</v>
       </c>
     </row>
     <row r="5">
@@ -2216,25 +2216,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.158842228297387</v>
+        <v>0.6912886747688154</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2262554626360283</v>
+        <v>0.8056618185123612</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03458262632365812</v>
+        <v>0.169343421711326</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01787886142483502</v>
+        <v>0.1131553238842909</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08790215724046026</v>
+        <v>0.1812134584276047</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08350954132514143</v>
+        <v>0.2203541422570128</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1014951462079184</v>
+        <v>0.3635028065935685</v>
       </c>
     </row>
     <row r="6">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.38975489566647</v>
+        <v>57.62316915669285</v>
       </c>
       <c r="C6" t="n">
-        <v>31.64362470574052</v>
+        <v>44.19355541868633</v>
       </c>
       <c r="D6" t="n">
-        <v>11.03323070959616</v>
+        <v>87.35595511990034</v>
       </c>
       <c r="E6" t="n">
-        <v>9.244016550559849</v>
+        <v>68.58055723211778</v>
       </c>
       <c r="F6" t="n">
-        <v>16.66082791689321</v>
+        <v>46.9337615603834</v>
       </c>
       <c r="G6" t="n">
-        <v>23.20359601326017</v>
+        <v>104.497197637336</v>
       </c>
       <c r="H6" t="n">
-        <v>17.36250846528607</v>
+        <v>68.19736602085278</v>
       </c>
     </row>
     <row r="7">
@@ -2272,25 +2272,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03442932976128548</v>
+        <v>0.6067512078600512</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06832360566465112</v>
+        <v>1.673241146899801</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04394038245451645</v>
+        <v>1.991350498392534</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02921099044750507</v>
+        <v>2.143884116869029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1136274972439708</v>
+        <v>0.9485682863281235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07966141519153852</v>
+        <v>1.078485158298281</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06153220346057792</v>
+        <v>1.407046735774637</v>
       </c>
     </row>
     <row r="8">
@@ -2300,25 +2300,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.11718919653087</v>
+        <v>1.354439983795335</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.833086629351165</v>
+        <v>5.406905545600304</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.37284622882007</v>
+        <v>-13.30991853773219</v>
       </c>
       <c r="E8" t="n">
-        <v>-38.28963427957814</v>
+        <v>-18.14792627736441</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.21980424779233</v>
+        <v>-36.41006997045835</v>
       </c>
       <c r="G8" t="n">
-        <v>-59.5182428160187</v>
+        <v>-34.35054010142544</v>
       </c>
       <c r="H8" t="n">
-        <v>-35.39180056634854</v>
+        <v>-15.90951822626413</v>
       </c>
     </row>
     <row r="9">
@@ -2328,25 +2328,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.13106630984977</v>
+        <v>2.143338293140213</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.87428928321089</v>
+        <v>4.573943422512524</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.4140488826798</v>
+        <v>-14.14288066081997</v>
       </c>
       <c r="E9" t="n">
-        <v>-39.33083693343787</v>
+        <v>-18.98088840045219</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.39505746048464</v>
+        <v>-34.15027254061221</v>
       </c>
       <c r="G9" t="n">
-        <v>-56.32295616794241</v>
+        <v>-31.7943107829644</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.74470917293423</v>
+        <v>-15.39184511153267</v>
       </c>
     </row>
   </sheetData>
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9525647423592521</v>
+        <v>-0.3759457747922252</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6887206687517342</v>
+        <v>-0.3323559612383253</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8666678782265775</v>
+        <v>-2.317464700632679</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9422753530303651</v>
+        <v>-2.690316061025977</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6478975785669014</v>
+        <v>-0.4851658278922812</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7650430545925573</v>
+        <v>-0.875438567528273</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8105282125878981</v>
+        <v>-1.179447815518294</v>
       </c>
     </row>
     <row r="3">
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1066552056765563</v>
+        <v>0.609220782137069</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2819705382847071</v>
+        <v>0.534364313602671</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02784189808676102</v>
+        <v>0.1696711392749135</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01192250549334264</v>
+        <v>0.1061067931621869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06332892902720916</v>
+        <v>0.1570867055247478</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05673626599772387</v>
+        <v>0.2224788750751538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09140922376105003</v>
+        <v>0.2998214347961237</v>
       </c>
     </row>
     <row r="4">
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02516514907511531</v>
+        <v>0.729960840608507</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1594042894261418</v>
+        <v>0.6822915431365076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001178179875337401</v>
+        <v>0.02931454247814083</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00020899007752728</v>
+        <v>0.01336066100325713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007720356148358217</v>
+        <v>0.03256441430885843</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006800882144112964</v>
+        <v>0.05428499525377213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0334129744577655</v>
+        <v>0.2569628327981738</v>
       </c>
     </row>
     <row r="5">
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1586352705898512</v>
+        <v>0.8543774579239009</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3992546673817876</v>
+        <v>0.8260094086246885</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03432462491182389</v>
+        <v>0.1712149014488541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01445648911483283</v>
+        <v>0.1155883255491537</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08786555723580325</v>
+        <v>0.180456128487947</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08246746112323917</v>
+        <v>0.2329914059654822</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1295006783928896</v>
+        <v>0.3967729380000044</v>
       </c>
     </row>
     <row r="6">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.42130583613077</v>
+        <v>58.60908055755929</v>
       </c>
       <c r="C6" t="n">
-        <v>31.23788920275843</v>
+        <v>45.72662195579644</v>
       </c>
       <c r="D6" t="n">
-        <v>11.44348516451166</v>
+        <v>87.73216218496542</v>
       </c>
       <c r="E6" t="n">
-        <v>7.516217964954302</v>
+        <v>69.14721649112967</v>
       </c>
       <c r="F6" t="n">
-        <v>16.78435325179073</v>
+        <v>46.55471360287191</v>
       </c>
       <c r="G6" t="n">
-        <v>21.51051119949047</v>
+        <v>111.384714159912</v>
       </c>
       <c r="H6" t="n">
-        <v>16.81896043660606</v>
+        <v>69.85908482537245</v>
       </c>
     </row>
     <row r="7">
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03434618164480507</v>
+        <v>1.851512641727245</v>
       </c>
       <c r="C7" t="n">
-        <v>0.207466801972779</v>
+        <v>1.758621737134106</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04332436244476293</v>
+        <v>2.035519179849005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01996368714515956</v>
+        <v>2.236894562020147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1135349757337803</v>
+        <v>0.9406896767677707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0777477011231119</v>
+        <v>1.205262133872245</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08273061834406648</v>
+        <v>1.67141665522842</v>
       </c>
     </row>
     <row r="8">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-23.14065693378079</v>
+        <v>5.167120496474755</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.017869618977127</v>
+        <v>5.706210620729105</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.46270705926152</v>
+        <v>-13.17802933466974</v>
       </c>
       <c r="E8" t="n">
-        <v>-40.83934269843506</v>
+        <v>-17.89264381483509</v>
       </c>
       <c r="F8" t="n">
-        <v>-53.23063217643293</v>
+        <v>-36.51895724173058</v>
       </c>
       <c r="G8" t="n">
-        <v>-59.86984127393858</v>
+        <v>-32.78910389021985</v>
       </c>
       <c r="H8" t="n">
-        <v>-34.76017496013767</v>
+        <v>-14.9175671940419</v>
       </c>
     </row>
     <row r="9">
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.15453404709969</v>
+        <v>5.956018805819633</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.059072272836852</v>
+        <v>4.873248497641325</v>
       </c>
       <c r="D9" t="n">
-        <v>-31.50390971312125</v>
+        <v>-14.01099145775752</v>
       </c>
       <c r="E9" t="n">
-        <v>-41.88054535229479</v>
+        <v>-18.72560593792286</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.40588538912525</v>
+        <v>-34.25915981188443</v>
       </c>
       <c r="G9" t="n">
-        <v>-56.67455462586229</v>
+        <v>-30.23287457175881</v>
       </c>
       <c r="H9" t="n">
-        <v>-34.11308356672335</v>
+        <v>-14.39989407931044</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8680194737066456</v>
+        <v>-0.6354627461796065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7277040609937483</v>
+        <v>-0.3094398289261184</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4904533324499896</v>
+        <v>0.6495061499424486</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5173866195833334</v>
+        <v>0.6617410362426884</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07781203628706901</v>
+        <v>0.2807900229245729</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6687393654379066</v>
+        <v>0.5729159236886213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3858902748820043</v>
+        <v>0.2033417596154344</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1721012003750548</v>
+        <v>0.6552404345970708</v>
       </c>
       <c r="C3" t="n">
-        <v>0.300133039532388</v>
+        <v>0.5100507388664046</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05868254135418735</v>
+        <v>0.04194388137150675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06296930440944103</v>
+        <v>0.03338401928148547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1054056158830662</v>
+        <v>0.1022476582344802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07578887482283155</v>
+        <v>0.09650837408837731</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1291800960628282</v>
+        <v>0.2398958510732208</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07001774174683449</v>
+        <v>0.8676386692385726</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1394411267103923</v>
+        <v>0.6705563284244542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004502573132923223</v>
+        <v>0.003097114146800034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005493645503495126</v>
+        <v>0.001224654818540939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02022030830295167</v>
+        <v>0.01576972162212143</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00958841429749668</v>
+        <v>0.01236204558066674</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04154396828234891</v>
+        <v>0.261774755638526</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2646086577321961</v>
+        <v>0.9314712390828676</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3734181660155171</v>
+        <v>0.8188750383449567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06710121558454231</v>
+        <v>0.05565172186734238</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07411913048258949</v>
+        <v>0.03499506848887338</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1421981304481591</v>
+        <v>0.1255775522222082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09792044882197323</v>
+        <v>0.1111847362755641</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1698942915141629</v>
+        <v>0.3462925593803021</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.37978636588105</v>
+        <v>57.3764491585127</v>
       </c>
       <c r="C6" t="n">
-        <v>40.83152781754911</v>
+        <v>38.20402920860752</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23479615900303</v>
+        <v>15.82258385267801</v>
       </c>
       <c r="E6" t="n">
-        <v>39.13505787244345</v>
+        <v>25.45442738136979</v>
       </c>
       <c r="F6" t="n">
-        <v>30.69132206714707</v>
+        <v>33.75210225146218</v>
       </c>
       <c r="G6" t="n">
-        <v>27.29457241613908</v>
+        <v>42.59844680454389</v>
       </c>
       <c r="H6" t="n">
-        <v>32.92784378302714</v>
+        <v>35.53467310952902</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08910657711079048</v>
+        <v>2.199971784641766</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1797975703991501</v>
+        <v>1.728442757149907</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1565158014580494</v>
+        <v>0.1093161349200255</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9191230754548934</v>
+        <v>0.1043349475001722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2913106049259455</v>
+        <v>0.2288017982581132</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1065900803768757</v>
+        <v>0.1387786547998804</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2904072849542841</v>
+        <v>0.7516076795449772</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-21.93105953968441</v>
+        <v>6.722180623976396</v>
       </c>
       <c r="C8" t="n">
-        <v>-9.820676785303801</v>
+        <v>5.602114578755456</v>
       </c>
       <c r="D8" t="n">
-        <v>-30.41863742985461</v>
+        <v>-26.66370712872166</v>
       </c>
       <c r="E8" t="n">
-        <v>-29.22497930614576</v>
+        <v>-32.23057753285611</v>
       </c>
       <c r="F8" t="n">
-        <v>-48.713881635042</v>
+        <v>-45.94562589693196</v>
       </c>
       <c r="G8" t="n">
-        <v>-63.06079654678499</v>
+        <v>-53.50374076829181</v>
       </c>
       <c r="H8" t="n">
-        <v>-33.86167187380259</v>
+        <v>-24.33655935401161</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.73383496234819</v>
+        <v>7.511078933321274</v>
       </c>
       <c r="C9" t="n">
-        <v>-10.02891731607575</v>
+        <v>4.769152455667676</v>
       </c>
       <c r="D9" t="n">
-        <v>-30.62687796062656</v>
+        <v>-27.49666925180944</v>
       </c>
       <c r="E9" t="n">
-        <v>-29.4332198369177</v>
+        <v>-33.06353965594389</v>
       </c>
       <c r="F9" t="n">
-        <v>-48.14893227758046</v>
+        <v>-43.68582846708581</v>
       </c>
       <c r="G9" t="n">
-        <v>-62.42173921716973</v>
+        <v>-50.94751144983077</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.73225359511974</v>
+        <v>-23.81888623928016</v>
       </c>
     </row>
   </sheetData>
@@ -2957,25 +2957,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9040507967306693</v>
+        <v>-0.8278485696172848</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7332745110916674</v>
+        <v>-0.3399414311813032</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8890414935777775</v>
+        <v>-0.2410251105615473</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8377473403681093</v>
+        <v>-0.1684797413266812</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6109853223352485</v>
+        <v>0.4222811631153882</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5933263320823771</v>
+        <v>0.1885394506670052</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7614042993643082</v>
+        <v>-0.1610790398174038</v>
       </c>
     </row>
     <row r="3">
@@ -2985,25 +2985,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1601589553549223</v>
+        <v>0.7202798051897756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2658434310656714</v>
+        <v>0.5303022263425873</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02859055367781719</v>
+        <v>0.0785628319678668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02009328947721578</v>
+        <v>0.0470448760442926</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06016354722329346</v>
+        <v>0.09097638558796858</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1019523881753146</v>
+        <v>0.1486233778770613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1061336941623725</v>
+        <v>0.2692982505015921</v>
       </c>
     </row>
     <row r="4">
@@ -3013,25 +3013,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05090255906688863</v>
+        <v>0.9697023696914001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1365885324309013</v>
+        <v>0.68617601706343</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009804770037809224</v>
+        <v>0.01096623072223128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005874301134022285</v>
+        <v>0.004230440280689409</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008529710890049372</v>
+        <v>0.01266732320729562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01177126167445602</v>
+        <v>0.02348790988511058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03489332852991307</v>
+        <v>0.2845383818083595</v>
       </c>
     </row>
     <row r="5">
@@ -3041,25 +3041,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2256159548145668</v>
+        <v>0.9847346696909783</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3695788582033627</v>
+        <v>0.8283574210830914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0313125694215745</v>
+        <v>0.1047197723557079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02423695759377048</v>
+        <v>0.06504183485026702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09235643393965237</v>
+        <v>0.1125492034947188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1084954454088098</v>
+        <v>0.1532576584876285</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1419327032302894</v>
+        <v>0.3747767599937319</v>
       </c>
     </row>
     <row r="6">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.37132330545734</v>
+        <v>67.85164374605071</v>
       </c>
       <c r="C6" t="n">
-        <v>32.20587531248118</v>
+        <v>47.89358231293986</v>
       </c>
       <c r="D6" t="n">
-        <v>13.82129876076696</v>
+        <v>34.61133393540707</v>
       </c>
       <c r="E6" t="n">
-        <v>13.44660546341749</v>
+        <v>54.99720576331772</v>
       </c>
       <c r="F6" t="n">
-        <v>15.44088220240316</v>
+        <v>50.1770111687131</v>
       </c>
       <c r="G6" t="n">
-        <v>47.96060627796152</v>
+        <v>89.19439568991407</v>
       </c>
       <c r="H6" t="n">
-        <v>24.54109855374794</v>
+        <v>57.45419543605709</v>
       </c>
     </row>
     <row r="7">
@@ -3097,25 +3097,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06541655232762124</v>
+        <v>2.456292459338331</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1766296193741307</v>
+        <v>1.766611282597584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0349738858293134</v>
+        <v>0.7619677893480523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05008699896894878</v>
+        <v>0.709010461188974</v>
       </c>
       <c r="F7" t="n">
-        <v>0.12367520092246</v>
+        <v>0.1831827773104905</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1312419835474061</v>
+        <v>0.2608797017194759</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09700404016164671</v>
+        <v>1.022990745250485</v>
       </c>
     </row>
     <row r="8">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-22.80057872293616</v>
+        <v>3.723105190557976</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.944693712177084</v>
+        <v>1.740273402832645</v>
       </c>
       <c r="D8" t="n">
-        <v>-37.56482819699887</v>
+        <v>-23.0776079746476</v>
       </c>
       <c r="E8" t="n">
-        <v>-40.63851964959726</v>
+        <v>-28.7926952364265</v>
       </c>
       <c r="F8" t="n">
-        <v>-57.93459754774312</v>
+        <v>-52.79348450245839</v>
       </c>
       <c r="G8" t="n">
-        <v>-58.18931837108769</v>
+        <v>-48.51777248469738</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.5120893667567</v>
+        <v>-24.61969693413988</v>
       </c>
     </row>
     <row r="9">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-22.40612956826372</v>
+        <v>4.117554345230415</v>
       </c>
       <c r="C9" t="n">
-        <v>-8.361174773720975</v>
+        <v>1.323792341288755</v>
       </c>
       <c r="D9" t="n">
-        <v>-37.98130925854277</v>
+        <v>-23.49408903619149</v>
       </c>
       <c r="E9" t="n">
-        <v>-41.05500071114115</v>
+        <v>-29.20917629797039</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.80469883282004</v>
+        <v>-51.66358578753532</v>
       </c>
       <c r="G9" t="n">
-        <v>-56.91120371185718</v>
+        <v>-47.23965782546686</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.25325280939097</v>
+        <v>-24.36086037677414</v>
       </c>
     </row>
   </sheetData>
@@ -3232,25 +3232,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9171806556177599</v>
+        <v>0.1296460226453366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8985435757962208</v>
+        <v>-0.3337786411585948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8916167211214187</v>
+        <v>-2.441865443938378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7635230242753717</v>
+        <v>-9.685527773220151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5927612185529699</v>
+        <v>-10.26810120104276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8061712428332802</v>
+        <v>-2.231698956537778</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8116327396995037</v>
+        <v>-4.13855433220872</v>
       </c>
     </row>
     <row r="3">
@@ -3260,25 +3260,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1688431672839849</v>
+        <v>0.4838888816144886</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1875373327992628</v>
+        <v>0.5519138358212657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0286616713486065</v>
+        <v>0.1485994090103033</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02517367298769639</v>
+        <v>0.1745693481162154</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07645542554247836</v>
+        <v>0.3949335614383693</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04222911004439787</v>
+        <v>0.2870207970143124</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08815006333440446</v>
+        <v>0.3401543055024925</v>
       </c>
     </row>
     <row r="4">
@@ -3288,25 +3288,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04393696274334242</v>
+        <v>0.461736452537677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05195522986722795</v>
+        <v>0.6830200890404775</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009577211875081672</v>
+        <v>0.03041380085856963</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008561566693704356</v>
+        <v>0.03868658181521501</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008929300790940087</v>
+        <v>0.2470694578972737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005610417395173521</v>
+        <v>0.09354226022368975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01870763144226043</v>
+        <v>0.2590781070621505</v>
       </c>
     </row>
     <row r="5">
@@ -3316,25 +3316,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2096114566128064</v>
+        <v>0.679511922292521</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2279368988716569</v>
+        <v>0.8264502943556119</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03094707074196469</v>
+        <v>0.1743955299271447</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02926015497857856</v>
+        <v>0.1966890485390964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09449497759637857</v>
+        <v>0.4970608191129871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07490271954457675</v>
+        <v>0.3058467920768334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1111922130576603</v>
+        <v>0.4466590677173658</v>
       </c>
     </row>
     <row r="6">
@@ -3344,25 +3344,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.13845906376226</v>
+        <v>49.98227290487793</v>
       </c>
       <c r="C6" t="n">
-        <v>26.52009371744333</v>
+        <v>47.35048259698063</v>
       </c>
       <c r="D6" t="n">
-        <v>14.22265756131277</v>
+        <v>60.38508350300341</v>
       </c>
       <c r="E6" t="n">
-        <v>16.54953878135785</v>
+        <v>109.8951991594961</v>
       </c>
       <c r="F6" t="n">
-        <v>21.12845959934862</v>
+        <v>133.4658145505627</v>
       </c>
       <c r="G6" t="n">
-        <v>11.22380125308801</v>
+        <v>106.1345525283269</v>
       </c>
       <c r="H6" t="n">
-        <v>20.96383499605214</v>
+        <v>84.53556754054127</v>
       </c>
     </row>
     <row r="7">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05710167723501174</v>
+        <v>0.5853217099827729</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06830558816819333</v>
+        <v>1.758495309351825</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03468538849483013</v>
+        <v>2.109698587565024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07304240238594782</v>
+        <v>6.467477878473392</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1299221449877671</v>
+        <v>7.108757961681838</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06357591932663741</v>
+        <v>2.071978538235833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07110552009973126</v>
+        <v>3.350288330881781</v>
       </c>
     </row>
     <row r="8">
@@ -3400,25 +3400,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-22.12499403510198</v>
+        <v>-2.954848997489087</v>
       </c>
       <c r="C8" t="n">
-        <v>-11.7442373720096</v>
+        <v>1.712613958598194</v>
       </c>
       <c r="D8" t="n">
-        <v>-35.70572315013966</v>
+        <v>-16.95715278784922</v>
       </c>
       <c r="E8" t="n">
-        <v>-36.37834304162457</v>
+        <v>-15.51357477313891</v>
       </c>
       <c r="F8" t="n">
-        <v>-55.33942341859976</v>
+        <v>-14.17511508570338</v>
       </c>
       <c r="G8" t="n">
-        <v>-66.56382224312912</v>
+        <v>-29.17078749317356</v>
       </c>
       <c r="H8" t="n">
-        <v>-37.97609054343412</v>
+        <v>-12.84314419645933</v>
       </c>
     </row>
     <row r="9">
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21.53332030309333</v>
+        <v>-2.560399842816648</v>
       </c>
       <c r="C9" t="n">
-        <v>-12.36895896432543</v>
+        <v>1.296132897054304</v>
       </c>
       <c r="D9" t="n">
-        <v>-36.3304447424555</v>
+        <v>-17.37363384939311</v>
       </c>
       <c r="E9" t="n">
-        <v>-37.00306463394041</v>
+        <v>-15.9300558346828</v>
       </c>
       <c r="F9" t="n">
-        <v>-53.64457534621516</v>
+        <v>-13.04521637078031</v>
       </c>
       <c r="G9" t="n">
-        <v>-64.64665025428334</v>
+        <v>-27.89267283394305</v>
       </c>
       <c r="H9" t="n">
-        <v>-37.58783570738553</v>
+        <v>-12.5843076390936</v>
       </c>
     </row>
   </sheetData>

--- a/results/cross_validation/induction/metrics_summary.xlsx
+++ b/results/cross_validation/induction/metrics_summary.xlsx
@@ -1032,25 +1032,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7521805961360201</v>
+        <v>-0.2296722997206231</v>
       </c>
       <c r="C2" t="n">
-        <v>0.821051020933881</v>
+        <v>0.8572301686222082</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.380094059969498</v>
+        <v>-5.401704030653022</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.667434451342429</v>
+        <v>0.2924101701730866</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4119749944707751</v>
+        <v>-0.8650043205015101</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5617694145496819</v>
+        <v>-2.313422414334903</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.074673550543747</v>
+        <v>-1.276693787735794</v>
       </c>
     </row>
     <row r="3">
@@ -1060,25 +1060,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2448747019963725</v>
+        <v>0.5219753177183087</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2293203748329558</v>
+        <v>0.1820152077753594</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1584220873278238</v>
+        <v>0.2157318388970369</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1328765812869198</v>
+        <v>0.04065399770996696</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1622611023992138</v>
+        <v>0.1704535821199933</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1937837676579939</v>
+        <v>0.2808543337846114</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1869231025835466</v>
+        <v>0.2352807130008795</v>
       </c>
     </row>
     <row r="4">
@@ -1088,25 +1088,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1314720853668572</v>
+        <v>0.6523604650863556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09163870513721151</v>
+        <v>0.07311157933616824</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02986796238772051</v>
+        <v>0.05656820544413745</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02051874939988609</v>
+        <v>0.002561804379173267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03095959915732005</v>
+        <v>0.04089292403583844</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04520577038577824</v>
+        <v>0.09590776426922383</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05827714530579559</v>
+        <v>0.1535671237584828</v>
       </c>
     </row>
     <row r="5">
@@ -1116,25 +1116,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3625907960316384</v>
+        <v>0.8076883465089463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3027188549416959</v>
+        <v>0.270391529704923</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1728235006812456</v>
+        <v>0.2378407144374938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1432436714130369</v>
+        <v>0.05061427050914858</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1759534005278672</v>
+        <v>0.2022199892093718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2126164866273973</v>
+        <v>0.3096897871567996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2283244517038136</v>
+        <v>0.3130741062544472</v>
       </c>
     </row>
     <row r="6">
@@ -1144,25 +1144,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.93326327064546</v>
+        <v>42.12190838629537</v>
       </c>
       <c r="C6" t="n">
-        <v>30.58950214517655</v>
+        <v>20.98300008208993</v>
       </c>
       <c r="D6" t="n">
-        <v>72.82755339631949</v>
+        <v>98.66149052851495</v>
       </c>
       <c r="E6" t="n">
-        <v>84.07583105890407</v>
+        <v>26.160019827878</v>
       </c>
       <c r="F6" t="n">
-        <v>45.7492021328875</v>
+        <v>45.75148278213786</v>
       </c>
       <c r="G6" t="n">
-        <v>72.9866083357049</v>
+        <v>98.1157126864007</v>
       </c>
       <c r="H6" t="n">
-        <v>55.360326723273</v>
+        <v>55.2989357155528</v>
       </c>
     </row>
     <row r="7">
@@ -1172,25 +1172,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.168376280915994</v>
+        <v>1.655108030953272</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1198317873158837</v>
+        <v>0.0960090549486553</v>
       </c>
       <c r="D7" t="n">
-        <v>2.073871583324508</v>
+        <v>3.924217906013606</v>
       </c>
       <c r="E7" t="n">
-        <v>3.433186919965299</v>
+        <v>0.2160702120134954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8945284355027132</v>
+        <v>1.18025268595108</v>
       </c>
       <c r="G7" t="n">
-        <v>1.004349727269899</v>
+        <v>2.126324318577856</v>
       </c>
       <c r="H7" t="n">
-        <v>1.282357455715716</v>
+        <v>1.532997034742994</v>
       </c>
     </row>
     <row r="8">
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-10.26064655629874</v>
+        <v>4.155577916617839</v>
       </c>
       <c r="C8" t="n">
-        <v>-6.339409308298343</v>
+        <v>-7.694611124316712</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.06581319055783</v>
+        <v>-9.233849157270367</v>
       </c>
       <c r="E8" t="n">
-        <v>-15.31849723576882</v>
+        <v>-27.80226059893644</v>
       </c>
       <c r="F8" t="n">
-        <v>-37.17593830697234</v>
+        <v>-33.55837708567275</v>
       </c>
       <c r="G8" t="n">
-        <v>-35.3514275164608</v>
+        <v>-24.82115673522034</v>
       </c>
       <c r="H8" t="n">
-        <v>-19.58528868572614</v>
+        <v>-16.4924461307998</v>
       </c>
     </row>
     <row r="9">
@@ -1228,25 +1228,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-9.47174824695386</v>
+        <v>4.944476225962717</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.172371431386123</v>
+        <v>-8.527573247404492</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.89877531364561</v>
+        <v>-10.06681128035815</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.15145935885661</v>
+        <v>-28.63522272202422</v>
       </c>
       <c r="F9" t="n">
-        <v>-34.9161408771262</v>
+        <v>-31.29857965582661</v>
       </c>
       <c r="G9" t="n">
-        <v>-32.79519819799976</v>
+        <v>-22.26492741675931</v>
       </c>
       <c r="H9" t="n">
-        <v>-19.06761557099469</v>
+        <v>-15.97477301606834</v>
       </c>
     </row>
   </sheetData>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1127094150891652</v>
+        <v>0.09531089541809745</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2402696418220431</v>
+        <v>-426737606.5564479</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4616355628790303</v>
+        <v>-1.810858743965297</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.775435998057157</v>
+        <v>-9.59174540847218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2342529187151345</v>
+        <v>-0.2195402004038953</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2147760234693841</v>
+        <v>-0.1438330590265666</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.595095620433608</v>
+        <v>-71122936.37118573</v>
       </c>
     </row>
     <row r="3">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5458470452132586</v>
+        <v>0.4737809744043921</v>
       </c>
       <c r="C3" t="n">
-        <v>0.533580525876541</v>
+        <v>8815.530323736064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.112579284873324</v>
+        <v>0.1374525404773278</v>
       </c>
       <c r="E3" t="n">
-        <v>0.181984998050626</v>
+        <v>0.1875019076994996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1036909703172262</v>
+        <v>0.1452920894332769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1763334820455804</v>
+        <v>0.1494315117271365</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2756693843960927</v>
+        <v>1469.437297126634</v>
       </c>
     </row>
     <row r="4">
@@ -1363,25 +1363,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5903098180697844</v>
+        <v>0.4799517767113206</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6351346880586041</v>
+        <v>218529784.2653545</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01291563939999336</v>
+        <v>0.0248379547291972</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03539162618303409</v>
+        <v>0.0383470460240359</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01679011511202643</v>
+        <v>0.0267401872615272</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03516196787791481</v>
+        <v>0.03310850766079745</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2209506424502262</v>
+        <v>36421630.81138999</v>
       </c>
     </row>
     <row r="5">
@@ -1391,25 +1391,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.768316222703767</v>
+        <v>0.6927855199925302</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7969533788488534</v>
+        <v>14782.75293256823</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1136469946808685</v>
+        <v>0.1576006177944655</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1881266227386068</v>
+        <v>0.1958240179958421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1295766765742448</v>
+        <v>0.1635242711695337</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1875152470545124</v>
+        <v>0.1819574336508334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3640225237668088</v>
+        <v>2464.024104071471</v>
       </c>
     </row>
     <row r="6">
@@ -1419,25 +1419,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.73052974370744</v>
+        <v>46.53448827418781</v>
       </c>
       <c r="C6" t="n">
-        <v>44.70944065158943</v>
+        <v>580901.8526809269</v>
       </c>
       <c r="D6" t="n">
-        <v>60.5207116272715</v>
+        <v>92.57778785142686</v>
       </c>
       <c r="E6" t="n">
-        <v>129.0636296878456</v>
+        <v>165.1359749079163</v>
       </c>
       <c r="F6" t="n">
-        <v>46.46010450507712</v>
+        <v>42.51942089880828</v>
       </c>
       <c r="G6" t="n">
-        <v>87.9574524456672</v>
+        <v>101.4717738286489</v>
       </c>
       <c r="H6" t="n">
-        <v>70.07364477685972</v>
+        <v>96891.68202111463</v>
       </c>
     </row>
     <row r="7">
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.496059394351198</v>
+        <v>0.6118729750724952</v>
       </c>
       <c r="C7" t="n">
-        <v>1.635350348375272</v>
+        <v>561984262.5143651</v>
       </c>
       <c r="D7" t="n">
-        <v>0.897063232887409</v>
+        <v>1.730288383000054</v>
       </c>
       <c r="E7" t="n">
-        <v>5.916809875490543</v>
+        <v>6.41773310951696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2424772049638782</v>
+        <v>0.7781603824084754</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7800923691107112</v>
+        <v>0.7416517461410566</v>
       </c>
       <c r="H7" t="n">
-        <v>1.827975404196502</v>
+        <v>93664045.46567862</v>
       </c>
     </row>
     <row r="8">
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.7439698808121742</v>
+        <v>11.39337319219277</v>
       </c>
       <c r="C8" t="n">
-        <v>1.276490827587468</v>
+        <v>133.2145972538249</v>
       </c>
       <c r="D8" t="n">
-        <v>-22.09589807202014</v>
+        <v>-4.172294178604769</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.04768021195768</v>
+        <v>-1.566466685329402</v>
       </c>
       <c r="F8" t="n">
-        <v>-49.13054437507583</v>
+        <v>-29.08064015569168</v>
       </c>
       <c r="G8" t="n">
-        <v>-42.86906333910373</v>
+        <v>-29.71151000837631</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.60177750856368</v>
+        <v>13.34617656966925</v>
       </c>
     </row>
     <row r="9">
@@ -1503,25 +1503,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3495207261397351</v>
+        <v>13.16839438821875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8600097660435777</v>
+        <v>131.3404324768774</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.51237913356403</v>
+        <v>-6.046458955552275</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.46416127350157</v>
+        <v>-3.440631462276908</v>
       </c>
       <c r="F9" t="n">
-        <v>-48.00064566015276</v>
+        <v>-23.99609593853785</v>
       </c>
       <c r="G9" t="n">
-        <v>-41.59094867987321</v>
+        <v>-23.95999404183898</v>
       </c>
       <c r="H9" t="n">
-        <v>-21.34294095119796</v>
+        <v>14.51094107781502</v>
       </c>
     </row>
   </sheetData>
@@ -1582,25 +1582,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1578548429797424</v>
+        <v>-0.3574061486854199</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03066971837282151</v>
+        <v>-0.3745751929116807</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.272964801537301</v>
+        <v>-0.4746280813217585</v>
       </c>
       <c r="E2" t="n">
-        <v>-38.12332057972097</v>
+        <v>-2.81646000105846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1655117575768797</v>
+        <v>-1.101692881830024</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3012084563403606</v>
+        <v>-2.895955178777544</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.633730007122352</v>
+        <v>-1.336786247430815</v>
       </c>
     </row>
     <row r="3">
@@ -1610,25 +1610,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4734224644069233</v>
+        <v>0.6060814145283717</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4935326642702909</v>
+        <v>0.5582620423669563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2325405351711791</v>
+        <v>0.09190211916733741</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3092561954538979</v>
+        <v>0.08917591135719648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1130521059005169</v>
+        <v>0.1935188857359059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09934646696437337</v>
+        <v>0.2685092439700904</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2868584053611969</v>
+        <v>0.3012416028543097</v>
       </c>
     </row>
     <row r="4">
@@ -1638,25 +1638,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4467712303747711</v>
+        <v>0.7201252778229497</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5277998170692119</v>
+        <v>0.7039117599302829</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08193989841734509</v>
+        <v>0.01303044687140812</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1416446220170315</v>
+        <v>0.01381736075268744</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01829736474660427</v>
+        <v>0.04608266394805275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02022667992848972</v>
+        <v>0.1127693074306256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.206113268758909</v>
+        <v>0.2682894694593344</v>
       </c>
     </row>
     <row r="5">
@@ -1666,25 +1666,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6684094780707192</v>
+        <v>0.8486019548781099</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7264983255790834</v>
+        <v>0.8389944933849584</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2862514601139095</v>
+        <v>0.1141509827877453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3763570406104176</v>
+        <v>0.117547270290243</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1352677520571857</v>
+        <v>0.2146687307179431</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1422205327246728</v>
+        <v>0.3358114164685674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.389167431525998</v>
+        <v>0.4116291414212611</v>
       </c>
     </row>
     <row r="6">
@@ -1694,25 +1694,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.35283886431273</v>
+        <v>59.00360983576467</v>
       </c>
       <c r="C6" t="n">
-        <v>44.26196873361221</v>
+        <v>46.67684337887276</v>
       </c>
       <c r="D6" t="n">
-        <v>90.86785144875938</v>
+        <v>35.1130329261696</v>
       </c>
       <c r="E6" t="n">
-        <v>175.05820581276</v>
+        <v>52.62963154236986</v>
       </c>
       <c r="F6" t="n">
-        <v>35.63921457677734</v>
+        <v>52.48600154875983</v>
       </c>
       <c r="G6" t="n">
-        <v>34.64963851834092</v>
+        <v>94.17403111623159</v>
       </c>
       <c r="H6" t="n">
-        <v>70.8049529924271</v>
+        <v>56.68052505802805</v>
       </c>
     </row>
     <row r="7">
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.566883408368417</v>
+        <v>1.826619078163382</v>
       </c>
       <c r="C7" t="n">
-        <v>1.360321574920589</v>
+        <v>1.814221579649405</v>
       </c>
       <c r="D7" t="n">
-        <v>5.681494738706665</v>
+        <v>0.9070194744130265</v>
       </c>
       <c r="E7" t="n">
-        <v>23.67529481865643</v>
+        <v>2.313220305688839</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2646546280495591</v>
+        <v>1.329531458625289</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2252961390478346</v>
+        <v>2.499450137669402</v>
       </c>
       <c r="H7" t="n">
-        <v>5.295657551291582</v>
+        <v>1.781677005701557</v>
       </c>
     </row>
     <row r="8">
@@ -1750,25 +1750,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.251377438231564</v>
+        <v>5.045029233817083</v>
       </c>
       <c r="C8" t="n">
-        <v>2.165770790975496</v>
+        <v>5.893386369871663</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.010615479504946</v>
+        <v>-18.04279955712045</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.726604120754525</v>
+        <v>-17.69097671147819</v>
       </c>
       <c r="F8" t="n">
-        <v>-46.0129770214857</v>
+        <v>-32.00513988760694</v>
       </c>
       <c r="G8" t="n">
-        <v>-48.61053860513712</v>
+        <v>-22.55375503865409</v>
       </c>
       <c r="H8" t="n">
-        <v>-18.07439031235639</v>
+        <v>-13.22570926519515</v>
       </c>
     </row>
     <row r="9">
@@ -1778,25 +1778,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.6597037062229054</v>
+        <v>5.833927543161961</v>
       </c>
       <c r="C9" t="n">
-        <v>1.541049198659661</v>
+        <v>5.060424246783882</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.63533707182078</v>
+        <v>-18.87576168020823</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.351325713070359</v>
+        <v>-18.52393883456597</v>
       </c>
       <c r="F9" t="n">
-        <v>-44.31812894910109</v>
+        <v>-29.7453424577608</v>
       </c>
       <c r="G9" t="n">
-        <v>-46.69336661629135</v>
+        <v>-19.99752572019305</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.6861354763078</v>
+        <v>-12.7080361504637</v>
       </c>
     </row>
   </sheetData>
@@ -2682,25 +2682,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6354627461796065</v>
+        <v>-0.5910375410762458</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3094398289261184</v>
+        <v>-0.3480893548022475</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6495061499424486</v>
+        <v>0.7937853821252155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6617410362426884</v>
+        <v>-0.60580314857666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2807900229245729</v>
+        <v>0.6936872399451174</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5729159236886213</v>
+        <v>0.7931436225157023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2033417596154344</v>
+        <v>0.1226143666884803</v>
       </c>
     </row>
     <row r="3">
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6552404345970708</v>
+        <v>0.6584292398481674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5100507388664046</v>
+        <v>0.5464189940019196</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04194388137150675</v>
+        <v>0.03134900482887237</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03338401928148547</v>
+        <v>0.07296990333599705</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1022476582344802</v>
+        <v>0.07400537857817069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09650837408837731</v>
+        <v>0.07120837150114687</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2398958510732208</v>
+        <v>0.2423968153490457</v>
       </c>
     </row>
     <row r="4">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8676386692385726</v>
+        <v>0.844070400302719</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6705563284244542</v>
+        <v>0.6903485201650228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003097114146800034</v>
+        <v>0.001822200903645208</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001224654818540939</v>
+        <v>0.00581375447287052</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01576972162212143</v>
+        <v>0.006716351426340935</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01236204558066674</v>
+        <v>0.005987504823870116</v>
       </c>
       <c r="H4" t="n">
-        <v>0.261774755638526</v>
+        <v>0.2591264553490781</v>
       </c>
     </row>
     <row r="5">
@@ -2766,25 +2766,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9314712390828676</v>
+        <v>0.9187330408245471</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8188750383449567</v>
+        <v>0.8308721442947903</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05565172186734238</v>
+        <v>0.04268724521031086</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03499506848887338</v>
+        <v>0.07624798012321717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1255775522222082</v>
+        <v>0.08195334908556778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1111847362755641</v>
+        <v>0.07737896887313837</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3462925593803021</v>
+        <v>0.3379787880685953</v>
       </c>
     </row>
     <row r="6">
@@ -2794,25 +2794,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57.3764491585127</v>
+        <v>61.44014986105132</v>
       </c>
       <c r="C6" t="n">
-        <v>38.20402920860752</v>
+        <v>46.1016683359764</v>
       </c>
       <c r="D6" t="n">
-        <v>15.82258385267801</v>
+        <v>11.42202892196013</v>
       </c>
       <c r="E6" t="n">
-        <v>25.45442738136979</v>
+        <v>48.9210740190102</v>
       </c>
       <c r="F6" t="n">
-        <v>33.75210225146218</v>
+        <v>26.34146619470194</v>
       </c>
       <c r="G6" t="n">
-        <v>42.59844680454389</v>
+        <v>30.72508853126678</v>
       </c>
       <c r="H6" t="n">
-        <v>35.53467310952902</v>
+        <v>37.49191264399446</v>
       </c>
     </row>
     <row r="7">
@@ -2822,25 +2822,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.199971784641766</v>
+        <v>2.141321085069554</v>
       </c>
       <c r="C7" t="n">
-        <v>1.728442757149907</v>
+        <v>1.78034154111238</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1093161349200255</v>
+        <v>0.065639925994987</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1043349475001722</v>
+        <v>0.9766211454080148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2288017982581132</v>
+        <v>0.09909527401490345</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1387786547998804</v>
+        <v>0.06874816662199842</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7516076795449772</v>
+        <v>0.855294523036973</v>
       </c>
     </row>
     <row r="8">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.722180623976396</v>
+        <v>8.474325623345102</v>
       </c>
       <c r="C8" t="n">
-        <v>5.602114578755456</v>
+        <v>7.776647756660127</v>
       </c>
       <c r="D8" t="n">
-        <v>-26.66370712872166</v>
+        <v>-27.8462613246544</v>
       </c>
       <c r="E8" t="n">
-        <v>-32.23057753285611</v>
+        <v>-20.88517224839364</v>
       </c>
       <c r="F8" t="n">
-        <v>-45.94562589693196</v>
+        <v>-55.04173278723282</v>
       </c>
       <c r="G8" t="n">
-        <v>-53.50374076829181</v>
+        <v>-61.65312714824073</v>
       </c>
       <c r="H8" t="n">
-        <v>-24.33655935401161</v>
+        <v>-24.86255335475273</v>
       </c>
     </row>
     <row r="9">
@@ -2878,25 +2878,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.511078933321274</v>
+        <v>9.4604485100262</v>
       </c>
       <c r="C9" t="n">
-        <v>4.769152455667676</v>
+        <v>6.735445102800401</v>
       </c>
       <c r="D9" t="n">
-        <v>-27.49666925180944</v>
+        <v>-28.88746397851413</v>
       </c>
       <c r="E9" t="n">
-        <v>-33.06353965594389</v>
+        <v>-21.92637490225336</v>
       </c>
       <c r="F9" t="n">
-        <v>-43.68582846708581</v>
+        <v>-52.21698599992514</v>
       </c>
       <c r="G9" t="n">
-        <v>-50.94751144983077</v>
+        <v>-58.45784050016444</v>
       </c>
       <c r="H9" t="n">
-        <v>-23.81888623928016</v>
+        <v>-24.21546196133841</v>
       </c>
     </row>
   </sheetData>
